--- a/VerveStacks_BRA_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF7BFB89-3F47-47D3-8F27-98E4CC485C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C1ED26B-EB79-46C9-B489-636B32A6FDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1767,6 +1767,162 @@
     <t>connecting solar to buses in cluster 42</t>
   </si>
   <si>
+    <t>distr_solelc_spv_BRA_112</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 112</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_104</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 104</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_100</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 100</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_098</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 98</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_085</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_109</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 109</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_115</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 115</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_BRA_114</t>
   </si>
   <si>
@@ -1803,6 +1959,264 @@
     <t>connecting solar to buses in cluster 37</t>
   </si>
   <si>
+    <t>distr_solelc_spv_BRA_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_101</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 101</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_108</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_106</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 106</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_096</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_113</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 113</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_BRA_103</t>
   </si>
   <si>
@@ -1851,6 +2265,48 @@
     <t>connecting solar to buses in cluster 46</t>
   </si>
   <si>
+    <t>distr_solelc_spv_BRA_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_BRA_111</t>
   </si>
   <si>
@@ -1947,462 +2403,6 @@
     <t>connecting solar to buses in cluster 43</t>
   </si>
   <si>
-    <t>distr_solelc_spv_BRA_112</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 112</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_104</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 104</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_100</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 100</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_098</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 98</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_085</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_106</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 106</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_096</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_115</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 115</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_113</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 113</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_110</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 110</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_101</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 101</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_108</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_109</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 109</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -2436,6 +2436,54 @@
     <t>e_BR273-230_BRA</t>
   </si>
   <si>
+    <t>e_BR273-230_BRA,e_BR357-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w32300871-500_BRA,e_w188465343-500_BRA,e_w125761912-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w515552863-500_BRA,e_BR357-500_BRA,e_BR141-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA,e_w537470701-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR141-500_BRA,e_w515552863-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR282-500_BRA,e_BR254-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w466973262-525_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA,e_BR435-500_BRA,e_BR485-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR485-500_BRA,e_w537470701-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w954122148-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR21-500_BRA,e_BR273-230_BRA</t>
+  </si>
+  <si>
+    <t>e_w188465343-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w188465343-500_BRA,e_w466973262-525_BRA</t>
+  </si>
+  <si>
+    <t>e_BR141-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR141-500_BRA,e_w271191830-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR580-500_BRA,e_w954122148-500_BRA</t>
+  </si>
+  <si>
     <t>e_BR273-230_BRA,e_BR21-500_BRA</t>
   </si>
   <si>
@@ -2445,16 +2493,79 @@
     <t>e_BR254-500_BRA,e_BR141-500_BRA</t>
   </si>
   <si>
-    <t>e_BR580-500_BRA,e_w954122148-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR273-230_BRA,e_BR357-500_BRA</t>
+    <t>e_w32300871-500_BRA,e_w466973262-525_BRA,e_w188465343-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA,e_BR357-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w188465343-500_BRA,e_w202622375-765_BRA</t>
+  </si>
+  <si>
+    <t>e_w537470701-500_BRA,e_BR580-500_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR21-500_BRA,e_BR357-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR21-500_BRA,e_w515552863-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w202622375-765_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR580-500_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w954122148-500_BRA,e_BR485-500_BRA,e_BR580-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR141-500_BRA,e_BR72-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR669-500_BRA,e_BR580-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w954122148-500_BRA,e_BR254-500_BRA,e_BR282-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w125761912-500_BRA,e_w537470701-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA,e_w537470701-500_BRA,e_BR485-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR435-500_BRA,e_w271191830-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w188465343-500_BRA,e_w125761912-500_BRA,e_w202622375-765_BRA</t>
   </si>
   <si>
     <t>e_w32300871-500_BRA,e_w125761912-500_BRA</t>
   </si>
   <si>
-    <t>e_w125761912-500_BRA,e_w537470701-500_BRA</t>
+    <t>e_w537470701-500_BRA,e_BR580-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA,e_BR357-500_BRA,e_BR435-500_BRA,e_w271191830-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w515552863-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR141-500_BRA,e_BR72-500_BRA,e_BR254-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR254-500_BRA,e_w954122148-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR254-500_BRA,e_BR72-500_BRA,e_BR282-500_BRA</t>
   </si>
   <si>
     <t>e_w466973262-525_BRA,e_w188465343-500_BRA</t>
@@ -2472,30 +2583,33 @@
     <t>e_BR282-500_BRA,e_BR204-500_BRA</t>
   </si>
   <si>
+    <t>e_w32300871-500_BRA,e_BR357-500_BRA,e_BR487-500_BRA,e_w125761912-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA,e_BR357-500_BRA,e_w125761912-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w202622375-765_BRA,e_w537470701-500_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR435-500_BRA,e_BR254-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR72-500_BRA,e_BR148-500_BRA,e_BR282-500_BRA</t>
+  </si>
+  <si>
     <t>e_BR357-500_BRA,e_BR273-230_BRA,e_BR487-500_BRA</t>
   </si>
   <si>
     <t>e_w32300871-500_BRA,e_w466973262-525_BRA</t>
   </si>
   <si>
-    <t>e_BR21-500_BRA,e_w515552863-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w188465343-500_BRA</t>
-  </si>
-  <si>
     <t>e_w537470701-500_BRA,e_w202622375-765_BRA</t>
   </si>
   <si>
     <t>e_BR435-500_BRA,e_w271191830-500_BRA,e_BR254-500_BRA</t>
   </si>
   <si>
-    <t>e_BR141-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR141-500_BRA,e_BR72-500_BRA</t>
-  </si>
-  <si>
     <t>e_w954122148-500_BRA,e_BR669-500_BRA</t>
   </si>
   <si>
@@ -2508,118 +2622,34 @@
     <t>e_BR282-500_BRA,e_BR204-500_BRA,e_BR148-500_BRA</t>
   </si>
   <si>
-    <t>e_w32300871-500_BRA,e_w188465343-500_BRA,e_w125761912-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w515552863-500_BRA,e_BR357-500_BRA,e_BR141-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR487-500_BRA,e_w537470701-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR141-500_BRA,e_w515552863-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR282-500_BRA,e_BR254-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR487-500_BRA,e_BR357-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR487-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w188465343-500_BRA,e_w125761912-500_BRA,e_w202622375-765_BRA</t>
-  </si>
-  <si>
-    <t>e_w188465343-500_BRA,e_w202622375-765_BRA</t>
-  </si>
-  <si>
-    <t>e_BR487-500_BRA,e_BR435-500_BRA,e_BR485-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w954122148-500_BRA,e_BR485-500_BRA,e_BR580-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR669-500_BRA,e_BR580-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w954122148-500_BRA,e_BR254-500_BRA,e_BR282-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR487-500_BRA,e_BR357-500_BRA,e_BR435-500_BRA,e_w271191830-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w515552863-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR141-500_BRA,e_BR72-500_BRA,e_BR254-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR254-500_BRA,e_w954122148-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR254-500_BRA,e_BR72-500_BRA,e_BR282-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR487-500_BRA,e_w537470701-500_BRA,e_BR485-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR435-500_BRA,e_w271191830-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR141-500_BRA,e_w271191830-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w537470701-500_BRA,e_BR580-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w466973262-525_BRA</t>
-  </si>
-  <si>
-    <t>e_BR485-500_BRA,e_w537470701-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w954122148-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w32300871-500_BRA,e_w466973262-525_BRA,e_w188465343-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w537470701-500_BRA,e_BR580-500_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w32300871-500_BRA,e_BR357-500_BRA,e_BR487-500_BRA,e_w125761912-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR487-500_BRA,e_BR357-500_BRA,e_w125761912-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w202622375-765_BRA,e_w537470701-500_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR435-500_BRA,e_BR254-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR72-500_BRA,e_BR148-500_BRA,e_BR282-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR21-500_BRA,e_BR357-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w202622375-765_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR580-500_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR21-500_BRA,e_BR273-230_BRA</t>
-  </si>
-  <si>
-    <t>e_w188465343-500_BRA,e_w466973262-525_BRA</t>
+    <t>distr_wonelc_won_BRA_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
   </si>
   <si>
     <t>distr_wonelc_won_BRA_011</t>
@@ -2652,6 +2682,318 @@
     <t>connecting wind onshore to buses in cluster 50</t>
   </si>
   <si>
+    <t>distr_wonelc_won_BRA_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_BRA_048</t>
   </si>
   <si>
@@ -2670,208 +3012,16 @@
     <t>connecting wind onshore to buses in cluster 52</t>
   </si>
   <si>
-    <t>distr_wonelc_won_BRA_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
+    <t>distr_wonelc_won_BRA_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
   </si>
   <si>
     <t>distr_wonelc_won_BRA_013</t>
@@ -2886,154 +3036,31 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wonelc_won_BRA_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
+    <t>elc_won_BRA_032</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_020</t>
+  </si>
+  <si>
+    <t>e_w125761912-500_BRA,e_w537470701-500_BRA,e_w202622375-765_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_057</t>
+  </si>
+  <si>
+    <t>e_BR435-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_045</t>
+  </si>
+  <si>
+    <t>e_BR72-500_BRA,e_BR148-500_BRA,e_BR204-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_040</t>
+  </si>
+  <si>
+    <t>e_BR282-500_BRA</t>
   </si>
   <si>
     <t>elc_won_BRA_011</t>
@@ -3057,6 +3084,207 @@
     <t>elc_won_BRA_050</t>
   </si>
   <si>
+    <t>elc_won_BRA_017</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_059</t>
+  </si>
+  <si>
+    <t>e_BR254-500_BRA,e_BR72-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_038</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_003</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_001</t>
+  </si>
+  <si>
+    <t>e_w32300871-500_BRA,e_BR357-500_BRA,e_BR487-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_042</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_055</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_034</t>
+  </si>
+  <si>
+    <t>e_w954122148-500_BRA,e_BR254-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_024</t>
+  </si>
+  <si>
+    <t>e_w537470701-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_006</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_023</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_061</t>
+  </si>
+  <si>
+    <t>e_BR254-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_039</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_004</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_028</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_027</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_063</t>
+  </si>
+  <si>
+    <t>e_BR485-500_BRA,e_BR435-500_BRA,e_w954122148-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_062</t>
+  </si>
+  <si>
+    <t>e_w954122148-500_BRA,e_BR485-500_BRA,e_BR435-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_035</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_025</t>
+  </si>
+  <si>
+    <t>e_w125761912-500_BRA,e_BR487-500_BRA,e_w537470701-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_031</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_021</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_056</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_065</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_046</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_014</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_026</t>
+  </si>
+  <si>
+    <t>e_w125761912-500_BRA,e_w537470701-500_BRA,e_BR487-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_029</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_068</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_069</t>
+  </si>
+  <si>
+    <t>e_BR485-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_058</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_019</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_036</t>
+  </si>
+  <si>
+    <t>e_BR254-500_BRA,e_BR282-500_BRA,e_BR204-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_005</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_012</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_030</t>
+  </si>
+  <si>
+    <t>e_w32300871-500_BRA,e_w125761912-500_BRA,e_w188465343-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_066</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_037</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_047</t>
+  </si>
+  <si>
+    <t>e_BR72-500_BRA,e_BR254-500_BRA,e_BR148-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_051</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_033</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_015</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_067</t>
+  </si>
+  <si>
+    <t>e_w537470701-500_BRA,e_BR485-500_BRA,e_BR580-500_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_060</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_043</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_010</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_007</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_022</t>
+  </si>
+  <si>
+    <t>e_w537470701-500_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_002</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_008</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_009</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_064</t>
+  </si>
+  <si>
     <t>elc_won_BRA_048</t>
   </si>
   <si>
@@ -3069,148 +3297,10 @@
     <t>elc_won_BRA_052</t>
   </si>
   <si>
-    <t>elc_won_BRA_060</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_043</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_003</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_001</t>
-  </si>
-  <si>
-    <t>e_w32300871-500_BRA,e_BR357-500_BRA,e_BR487-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_042</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_055</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_034</t>
-  </si>
-  <si>
-    <t>e_w954122148-500_BRA,e_BR254-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_010</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_007</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_022</t>
-  </si>
-  <si>
-    <t>e_w537470701-500_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_032</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_020</t>
-  </si>
-  <si>
-    <t>e_w125761912-500_BRA,e_w537470701-500_BRA,e_w202622375-765_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_057</t>
-  </si>
-  <si>
-    <t>e_BR435-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_045</t>
-  </si>
-  <si>
-    <t>e_BR72-500_BRA,e_BR148-500_BRA,e_BR204-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_040</t>
-  </si>
-  <si>
-    <t>e_BR282-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_017</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_059</t>
-  </si>
-  <si>
-    <t>e_BR254-500_BRA,e_BR72-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_038</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_033</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_015</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_067</t>
-  </si>
-  <si>
-    <t>e_w537470701-500_BRA,e_BR485-500_BRA,e_BR580-500_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_004</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_028</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_027</t>
-  </si>
-  <si>
-    <t>e_w537470701-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_063</t>
-  </si>
-  <si>
-    <t>e_BR485-500_BRA,e_BR435-500_BRA,e_w954122148-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_062</t>
-  </si>
-  <si>
-    <t>e_w954122148-500_BRA,e_BR485-500_BRA,e_BR435-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_035</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_005</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_012</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_030</t>
-  </si>
-  <si>
-    <t>e_w32300871-500_BRA,e_w125761912-500_BRA,e_w188465343-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_066</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_037</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_047</t>
-  </si>
-  <si>
-    <t>e_BR72-500_BRA,e_BR254-500_BRA,e_BR148-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_051</t>
+    <t>elc_won_BRA_049</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_044</t>
   </si>
   <si>
     <t>elc_won_BRA_013</t>
@@ -3219,94 +3309,28 @@
     <t>elc_won_BRA_016</t>
   </si>
   <si>
-    <t>elc_won_BRA_049</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_044</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_002</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_008</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_009</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_064</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_014</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_026</t>
-  </si>
-  <si>
-    <t>e_w125761912-500_BRA,e_w537470701-500_BRA,e_BR487-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_029</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_068</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_069</t>
-  </si>
-  <si>
-    <t>e_BR485-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_058</t>
-  </si>
-  <si>
-    <t>e_BR254-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_019</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_036</t>
-  </si>
-  <si>
-    <t>e_BR254-500_BRA,e_BR282-500_BRA,e_BR204-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_025</t>
-  </si>
-  <si>
-    <t>e_w125761912-500_BRA,e_BR487-500_BRA,e_w537470701-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_031</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_021</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_056</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_065</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_046</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_024</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_006</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_023</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_061</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_039</t>
+    <t>distr_wofelc_wof_BRA_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_wofelc_wof_BRA_005</t>
@@ -3333,6 +3357,114 @@
     <t>connecting wind offshore to buses in cluster 28</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_BRA_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_BRA_003</t>
   </si>
   <si>
@@ -3357,142 +3489,22 @@
     <t>connecting wind offshore to buses in cluster 27</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_BRA_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_BRA_008</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_BRA_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
+    <t>elc_wof_BRA_006</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_011</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_014</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_022</t>
   </si>
   <si>
     <t>elc_wof_BRA_005</t>
@@ -3510,6 +3522,69 @@
     <t>e_BR204-500_BRA,e_BR148-500_BRA</t>
   </si>
   <si>
+    <t>elc_wof_BRA_001</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_016</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_009</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_020</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_019</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_017</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_012</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_030</t>
+  </si>
+  <si>
+    <t>e_BR148-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_023</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_018</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_024</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_025</t>
+  </si>
+  <si>
+    <t>e_BR72-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_026</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_029</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_002</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_010</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_004</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_013</t>
+  </si>
+  <si>
+    <t>e_w188465343-500_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
     <t>elc_wof_BRA_003</t>
   </si>
   <si>
@@ -3519,85 +3594,10 @@
     <t>elc_wof_BRA_031</t>
   </si>
   <si>
-    <t>e_BR148-500_BRA</t>
-  </si>
-  <si>
     <t>elc_wof_BRA_027</t>
   </si>
   <si>
-    <t>elc_wof_BRA_024</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_025</t>
-  </si>
-  <si>
-    <t>e_BR72-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_026</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_029</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_023</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_018</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_016</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_009</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_020</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_019</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_001</t>
-  </si>
-  <si>
     <t>elc_wof_BRA_008</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_004</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_013</t>
-  </si>
-  <si>
-    <t>e_w188465343-500_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_002</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_010</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_011</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_014</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_022</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_017</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_012</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_030</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_006</t>
   </si>
   <si>
     <t>e_won_BRA_001</t>
@@ -9025,7 +9025,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA27DD2E-9EC1-4CFB-81BF-2EB967153F54}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11ACA86D-CB5A-4FBF-A51B-700F06B5D5AD}">
   <dimension ref="B9:BD125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9302,13 +9302,13 @@
         <v>969</v>
       </c>
       <c r="AN11" t="s">
-        <v>970</v>
+        <v>805</v>
       </c>
       <c r="AO11">
-        <v>0.99473480482648013</v>
+        <v>0.98674094240398891</v>
       </c>
       <c r="AP11">
-        <v>96.528578181196991</v>
+        <v>243.0827225935364</v>
       </c>
       <c r="AR11" t="s">
         <v>525</v>
@@ -9338,13 +9338,13 @@
         <v>1122</v>
       </c>
       <c r="BB11" t="s">
-        <v>776</v>
+        <v>807</v>
       </c>
       <c r="BC11">
-        <v>0.99203097418485064</v>
+        <v>0.99314574070258299</v>
       </c>
       <c r="BD11">
-        <v>146.09880661107059</v>
+        <v>125.66142045264445</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -9445,16 +9445,16 @@
         <v>833</v>
       </c>
       <c r="AM12" t="s">
+        <v>970</v>
+      </c>
+      <c r="AN12" t="s">
         <v>971</v>
       </c>
-      <c r="AN12" t="s">
-        <v>972</v>
-      </c>
       <c r="AO12">
-        <v>0.98589595763902149</v>
+        <v>0.99776894175014486</v>
       </c>
       <c r="AP12">
-        <v>258.57410995127316</v>
+        <v>40.90273458067751</v>
       </c>
       <c r="AR12" t="s">
         <v>525</v>
@@ -9484,13 +9484,13 @@
         <v>1123</v>
       </c>
       <c r="BB12" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="BC12">
-        <v>0.99481196273061234</v>
+        <v>0.99098965084511315</v>
       </c>
       <c r="BD12">
-        <v>95.114016605440895</v>
+        <v>165.18973450625904</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -9591,16 +9591,16 @@
         <v>835</v>
       </c>
       <c r="AM13" t="s">
+        <v>972</v>
+      </c>
+      <c r="AN13" t="s">
         <v>973</v>
       </c>
-      <c r="AN13" t="s">
-        <v>784</v>
-      </c>
       <c r="AO13">
-        <v>0.99681451207345617</v>
+        <v>0.99374536027070226</v>
       </c>
       <c r="AP13">
-        <v>58.400611986637742</v>
+        <v>114.668395037126</v>
       </c>
       <c r="AR13" t="s">
         <v>525</v>
@@ -9630,13 +9630,13 @@
         <v>1124</v>
       </c>
       <c r="BB13" t="s">
-        <v>815</v>
+        <v>790</v>
       </c>
       <c r="BC13">
-        <v>0.98775115723917273</v>
+        <v>0.99053278045305837</v>
       </c>
       <c r="BD13">
-        <v>224.56211728183334</v>
+        <v>173.56569169392964</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -9740,13 +9740,13 @@
         <v>974</v>
       </c>
       <c r="AN14" t="s">
-        <v>815</v>
+        <v>975</v>
       </c>
       <c r="AO14">
-        <v>0.9976320377495026</v>
+        <v>0.99733068647604728</v>
       </c>
       <c r="AP14">
-        <v>43.412641259119624</v>
+        <v>48.937414605800647</v>
       </c>
       <c r="AR14" t="s">
         <v>525</v>
@@ -9776,13 +9776,13 @@
         <v>1125</v>
       </c>
       <c r="BB14" t="s">
-        <v>1126</v>
+        <v>807</v>
       </c>
       <c r="BC14">
-        <v>0.99538398111052984</v>
+        <v>0.99420451954813838</v>
       </c>
       <c r="BD14">
-        <v>84.627012973619784</v>
+        <v>106.25047495079694</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9883,16 +9883,16 @@
         <v>839</v>
       </c>
       <c r="AM15" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="AN15" t="s">
-        <v>779</v>
+        <v>977</v>
       </c>
       <c r="AO15">
-        <v>0.99274560110857168</v>
+        <v>0.99671693937496686</v>
       </c>
       <c r="AP15">
-        <v>132.99731300951822</v>
+        <v>60.189444792275019</v>
       </c>
       <c r="AR15" t="s">
         <v>525</v>
@@ -9919,16 +9919,16 @@
         <v>1068</v>
       </c>
       <c r="BA15" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="BB15" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="BC15">
-        <v>0.99054926914187857</v>
+        <v>0.99203097418485064</v>
       </c>
       <c r="BD15">
-        <v>173.26339906555947</v>
+        <v>146.09880661107059</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -10029,16 +10029,16 @@
         <v>841</v>
       </c>
       <c r="AM16" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="AN16" t="s">
-        <v>760</v>
+        <v>979</v>
       </c>
       <c r="AO16">
-        <v>0.95532613069733086</v>
+        <v>0.99473480482648013</v>
       </c>
       <c r="AP16">
-        <v>819.02093721560016</v>
+        <v>96.528578181196991</v>
       </c>
       <c r="AR16" t="s">
         <v>525</v>
@@ -10065,16 +10065,16 @@
         <v>1070</v>
       </c>
       <c r="BA16" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="BB16" t="s">
-        <v>815</v>
+        <v>780</v>
       </c>
       <c r="BC16">
-        <v>0.98574436213546524</v>
+        <v>0.99481196273061234</v>
       </c>
       <c r="BD16">
-        <v>261.35336084980423</v>
+        <v>95.114016605440895</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -10175,16 +10175,16 @@
         <v>843</v>
       </c>
       <c r="AM17" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="AN17" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="AO17">
-        <v>0.9961850470371636</v>
+        <v>0.98589595763902149</v>
       </c>
       <c r="AP17">
-        <v>69.94080431866837</v>
+        <v>258.57410995127316</v>
       </c>
       <c r="AR17" t="s">
         <v>525</v>
@@ -10211,16 +10211,16 @@
         <v>1072</v>
       </c>
       <c r="BA17" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="BB17" t="s">
-        <v>1130</v>
+        <v>807</v>
       </c>
       <c r="BC17">
-        <v>0.99374755699184159</v>
+        <v>0.98775115723917273</v>
       </c>
       <c r="BD17">
-        <v>114.62812181623703</v>
+        <v>224.56211728183334</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -10321,16 +10321,16 @@
         <v>845</v>
       </c>
       <c r="AM18" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="AN18" t="s">
-        <v>815</v>
+        <v>780</v>
       </c>
       <c r="AO18">
-        <v>0.99765219450274578</v>
+        <v>0.99681451207345617</v>
       </c>
       <c r="AP18">
-        <v>43.043100782993086</v>
+        <v>58.400611986637742</v>
       </c>
       <c r="AR18" t="s">
         <v>525</v>
@@ -10357,16 +10357,16 @@
         <v>1074</v>
       </c>
       <c r="BA18" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="BB18" t="s">
-        <v>780</v>
+        <v>1130</v>
       </c>
       <c r="BC18">
-        <v>0.99542890407822671</v>
+        <v>0.99538398111052984</v>
       </c>
       <c r="BD18">
-        <v>83.803425232511387</v>
+        <v>84.627012973619784</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -10467,16 +10467,16 @@
         <v>847</v>
       </c>
       <c r="AM19" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="AN19" t="s">
-        <v>824</v>
+        <v>807</v>
       </c>
       <c r="AO19">
-        <v>0.99414234808301016</v>
+        <v>0.9976320377495026</v>
       </c>
       <c r="AP19">
-        <v>107.39028514481463</v>
+        <v>43.412641259119624</v>
       </c>
       <c r="AR19" t="s">
         <v>525</v>
@@ -10503,16 +10503,16 @@
         <v>1076</v>
       </c>
       <c r="BA19" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="BB19" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="BC19">
-        <v>0.98027195861782945</v>
+        <v>0.98890025255868685</v>
       </c>
       <c r="BD19">
-        <v>361.68075867312689</v>
+        <v>203.49536975740753</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -10577,16 +10577,16 @@
         <v>546</v>
       </c>
       <c r="Y20" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="Z20" t="s">
         <v>768</v>
       </c>
       <c r="AA20">
-        <v>0.98313106622136326</v>
+        <v>0.99506650442525857</v>
       </c>
       <c r="AB20">
-        <v>309.26378594167363</v>
+        <v>90.447418870259696</v>
       </c>
       <c r="AD20" t="s">
         <v>525</v>
@@ -10613,16 +10613,16 @@
         <v>849</v>
       </c>
       <c r="AM20" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="AN20" t="s">
-        <v>788</v>
+        <v>816</v>
       </c>
       <c r="AO20">
-        <v>0.99676376447003934</v>
+        <v>0.99274560110857168</v>
       </c>
       <c r="AP20">
-        <v>59.330984715944624</v>
+        <v>132.99731300951822</v>
       </c>
       <c r="AR20" t="s">
         <v>525</v>
@@ -10649,16 +10649,16 @@
         <v>1078</v>
       </c>
       <c r="BA20" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="BB20" t="s">
-        <v>1134</v>
+        <v>762</v>
       </c>
       <c r="BC20">
-        <v>0.98488330873784669</v>
+        <v>0.95713629889852414</v>
       </c>
       <c r="BD20">
-        <v>277.13933980614473</v>
+        <v>785.83452019372396</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -10723,16 +10723,16 @@
         <v>548</v>
       </c>
       <c r="Y21" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="Z21" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="AA21">
-        <v>0.98061830542009054</v>
+        <v>0.99751736863660534</v>
       </c>
       <c r="AB21">
-        <v>355.3310672983406</v>
+        <v>45.514908328903012</v>
       </c>
       <c r="AD21" t="s">
         <v>525</v>
@@ -10759,16 +10759,16 @@
         <v>851</v>
       </c>
       <c r="AM21" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="AN21" t="s">
-        <v>761</v>
+        <v>794</v>
       </c>
       <c r="AO21">
-        <v>0.99244513691456471</v>
+        <v>0.99729761494442914</v>
       </c>
       <c r="AP21">
-        <v>138.50582323297994</v>
+        <v>49.543726018799653</v>
       </c>
       <c r="AR21" t="s">
         <v>525</v>
@@ -10795,16 +10795,16 @@
         <v>1080</v>
       </c>
       <c r="BA21" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="BB21" t="s">
-        <v>1001</v>
+        <v>807</v>
       </c>
       <c r="BC21">
-        <v>0.99665799830099</v>
+        <v>0.99232494426983575</v>
       </c>
       <c r="BD21">
-        <v>61.270031148516708</v>
+        <v>140.70935505301131</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10869,16 +10869,16 @@
         <v>550</v>
       </c>
       <c r="Y22" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="Z22" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="AA22">
-        <v>0.99107116626800151</v>
+        <v>0.95679886695043703</v>
       </c>
       <c r="AB22">
-        <v>163.69528508663959</v>
+        <v>792.02077257532187</v>
       </c>
       <c r="AD22" t="s">
         <v>525</v>
@@ -10905,16 +10905,16 @@
         <v>853</v>
       </c>
       <c r="AM22" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="AN22" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="AO22">
-        <v>0.97020178001960844</v>
+        <v>0.99478775228549088</v>
       </c>
       <c r="AP22">
-        <v>546.30069964051177</v>
+        <v>95.557874766001078</v>
       </c>
       <c r="AR22" t="s">
         <v>525</v>
@@ -10941,16 +10941,16 @@
         <v>1082</v>
       </c>
       <c r="BA22" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="BB22" t="s">
-        <v>1134</v>
+        <v>807</v>
       </c>
       <c r="BC22">
-        <v>0.99401640271965719</v>
+        <v>0.99418931598784899</v>
       </c>
       <c r="BD22">
-        <v>109.69928347295183</v>
+        <v>106.52920688943452</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -11015,16 +11015,16 @@
         <v>552</v>
       </c>
       <c r="Y23" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="Z23" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AA23">
-        <v>0.99464340805826168</v>
+        <v>0.98820023878766372</v>
       </c>
       <c r="AB23">
-        <v>98.204185598535332</v>
+        <v>216.32895555949756</v>
       </c>
       <c r="AD23" t="s">
         <v>525</v>
@@ -11051,16 +11051,16 @@
         <v>855</v>
       </c>
       <c r="AM23" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="AN23" t="s">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="AO23">
-        <v>0.99083036293819104</v>
+        <v>0.99481362508126103</v>
       </c>
       <c r="AP23">
-        <v>168.11001279983091</v>
+        <v>95.083540176881584</v>
       </c>
       <c r="AR23" t="s">
         <v>525</v>
@@ -11087,16 +11087,16 @@
         <v>1084</v>
       </c>
       <c r="BA23" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="BB23" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="BC23">
-        <v>0.9933934749176847</v>
+        <v>0.97821242976023937</v>
       </c>
       <c r="BD23">
-        <v>121.11962650911367</v>
+        <v>399.43878772894504</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -11161,16 +11161,16 @@
         <v>554</v>
       </c>
       <c r="Y24" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="Z24" t="s">
-        <v>771</v>
+        <v>760</v>
       </c>
       <c r="AA24">
-        <v>0.99480863709915346</v>
+        <v>0.97404342257401955</v>
       </c>
       <c r="AB24">
-        <v>95.174986515519862</v>
+        <v>475.8705861429753</v>
       </c>
       <c r="AD24" t="s">
         <v>525</v>
@@ -11197,16 +11197,16 @@
         <v>857</v>
       </c>
       <c r="AM24" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="AN24" t="s">
-        <v>824</v>
+        <v>761</v>
       </c>
       <c r="AO24">
-        <v>0.99175391794306234</v>
+        <v>0.99244513691456471</v>
       </c>
       <c r="AP24">
-        <v>151.17817104385733</v>
+        <v>138.50582323297994</v>
       </c>
       <c r="AR24" t="s">
         <v>525</v>
@@ -11233,16 +11233,16 @@
         <v>1086</v>
       </c>
       <c r="BA24" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="BB24" t="s">
-        <v>818</v>
+        <v>782</v>
       </c>
       <c r="BC24">
-        <v>0.98163861082146986</v>
+        <v>0.96863461872110523</v>
       </c>
       <c r="BD24">
-        <v>336.62546827305243</v>
+        <v>575.0319901130714</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -11307,16 +11307,16 @@
         <v>556</v>
       </c>
       <c r="Y25" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="Z25" t="s">
-        <v>772</v>
+        <v>761</v>
       </c>
       <c r="AA25">
-        <v>0.99377462362826907</v>
+        <v>0.98784519281324712</v>
       </c>
       <c r="AB25">
-        <v>114.13190014840048</v>
+        <v>222.83813175713675</v>
       </c>
       <c r="AD25" t="s">
         <v>525</v>
@@ -11343,16 +11343,16 @@
         <v>859</v>
       </c>
       <c r="AM25" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="AN25" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="AO25">
-        <v>0.99694189558126134</v>
+        <v>0.97020178001960844</v>
       </c>
       <c r="AP25">
-        <v>56.065247676874698</v>
+        <v>546.30069964051177</v>
       </c>
       <c r="AR25" t="s">
         <v>525</v>
@@ -11379,16 +11379,16 @@
         <v>1088</v>
       </c>
       <c r="BA25" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="BB25" t="s">
-        <v>762</v>
+        <v>807</v>
       </c>
       <c r="BC25">
-        <v>0.95713629889852414</v>
+        <v>0.98946506962487613</v>
       </c>
       <c r="BD25">
-        <v>785.83452019372396</v>
+        <v>193.14039021060518</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -11453,16 +11453,16 @@
         <v>558</v>
       </c>
       <c r="Y26" t="s">
-        <v>511</v>
+        <v>415</v>
       </c>
       <c r="Z26" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="AA26">
-        <v>0.99008735429887684</v>
+        <v>0.99679666622099095</v>
       </c>
       <c r="AB26">
-        <v>181.7318378539255</v>
+        <v>58.72778594849845</v>
       </c>
       <c r="AD26" t="s">
         <v>525</v>
@@ -11489,16 +11489,16 @@
         <v>861</v>
       </c>
       <c r="AM26" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="AN26" t="s">
-        <v>970</v>
+        <v>797</v>
       </c>
       <c r="AO26">
-        <v>0.99424679200457</v>
+        <v>0.99083036293819104</v>
       </c>
       <c r="AP26">
-        <v>105.47547991621673</v>
+        <v>168.11001279983091</v>
       </c>
       <c r="AR26" t="s">
         <v>525</v>
@@ -11525,16 +11525,16 @@
         <v>1090</v>
       </c>
       <c r="BA26" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="BB26" t="s">
-        <v>815</v>
+        <v>1139</v>
       </c>
       <c r="BC26">
-        <v>0.99232494426983575</v>
+        <v>0.98125520899414764</v>
       </c>
       <c r="BD26">
-        <v>140.70935505301131</v>
+        <v>343.65450177395917</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -11599,16 +11599,16 @@
         <v>560</v>
       </c>
       <c r="Y27" t="s">
-        <v>431</v>
+        <v>493</v>
       </c>
       <c r="Z27" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="AA27">
-        <v>0.98622431616682615</v>
+        <v>0.98775140142897844</v>
       </c>
       <c r="AB27">
-        <v>252.55420360818721</v>
+        <v>224.55764046872929</v>
       </c>
       <c r="AD27" t="s">
         <v>525</v>
@@ -11635,16 +11635,16 @@
         <v>863</v>
       </c>
       <c r="AM27" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="AN27" t="s">
-        <v>784</v>
+        <v>821</v>
       </c>
       <c r="AO27">
-        <v>0.99567626923235475</v>
+        <v>0.99175391794306234</v>
       </c>
       <c r="AP27">
-        <v>79.268397406829976</v>
+        <v>151.17817104385733</v>
       </c>
       <c r="AR27" t="s">
         <v>525</v>
@@ -11671,16 +11671,16 @@
         <v>1092</v>
       </c>
       <c r="BA27" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="BB27" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="BC27">
-        <v>0.99418931598784899</v>
+        <v>0.9933934749176847</v>
       </c>
       <c r="BD27">
-        <v>106.52920688943452</v>
+        <v>121.11962650911367</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -11745,16 +11745,16 @@
         <v>562</v>
       </c>
       <c r="Y28" t="s">
-        <v>433</v>
+        <v>473</v>
       </c>
       <c r="Z28" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="AA28">
-        <v>0.98732531824996883</v>
+        <v>0.99149332428826786</v>
       </c>
       <c r="AB28">
-        <v>232.36916541723792</v>
+        <v>155.95572138175513</v>
       </c>
       <c r="AD28" t="s">
         <v>525</v>
@@ -11781,16 +11781,16 @@
         <v>865</v>
       </c>
       <c r="AM28" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="AN28" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="AO28">
-        <v>0.99766813121902409</v>
+        <v>0.99694189558126134</v>
       </c>
       <c r="AP28">
-        <v>42.750927651225993</v>
+        <v>56.065247676874698</v>
       </c>
       <c r="AR28" t="s">
         <v>525</v>
@@ -11817,16 +11817,16 @@
         <v>1094</v>
       </c>
       <c r="BA28" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="BB28" t="s">
-        <v>789</v>
+        <v>778</v>
       </c>
       <c r="BC28">
-        <v>0.97821242976023937</v>
+        <v>0.98163861082146986</v>
       </c>
       <c r="BD28">
-        <v>399.43878772894504</v>
+        <v>336.62546827305243</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11891,16 +11891,16 @@
         <v>564</v>
       </c>
       <c r="Y29" t="s">
-        <v>409</v>
+        <v>479</v>
       </c>
       <c r="Z29" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="AA29">
-        <v>0.99468658155318235</v>
+        <v>0.99563753295513335</v>
       </c>
       <c r="AB29">
-        <v>97.412671524990884</v>
+        <v>79.978562489222767</v>
       </c>
       <c r="AD29" t="s">
         <v>525</v>
@@ -11927,16 +11927,16 @@
         <v>867</v>
       </c>
       <c r="AM29" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="AN29" t="s">
-        <v>774</v>
+        <v>997</v>
       </c>
       <c r="AO29">
-        <v>0.98674094240398891</v>
+        <v>0.99760255773158468</v>
       </c>
       <c r="AP29">
-        <v>243.0827225935364</v>
+        <v>43.953108254279897</v>
       </c>
       <c r="AR29" t="s">
         <v>525</v>
@@ -11963,16 +11963,16 @@
         <v>1096</v>
       </c>
       <c r="BA29" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="BB29" t="s">
-        <v>816</v>
+        <v>797</v>
       </c>
       <c r="BC29">
-        <v>0.98890025255868685</v>
+        <v>0.98027195861782945</v>
       </c>
       <c r="BD29">
-        <v>203.49536975740753</v>
+        <v>361.68075867312689</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -12037,16 +12037,16 @@
         <v>566</v>
       </c>
       <c r="Y30" t="s">
-        <v>435</v>
+        <v>478</v>
       </c>
       <c r="Z30" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="AA30">
-        <v>0.99713964204801786</v>
+        <v>0.99338737982948611</v>
       </c>
       <c r="AB30">
-        <v>52.439895786339292</v>
+        <v>121.23136979275419</v>
       </c>
       <c r="AD30" t="s">
         <v>525</v>
@@ -12073,16 +12073,16 @@
         <v>869</v>
       </c>
       <c r="AM30" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="AN30" t="s">
-        <v>995</v>
+        <v>804</v>
       </c>
       <c r="AO30">
-        <v>0.99776894175014486</v>
+        <v>0.99694661611560498</v>
       </c>
       <c r="AP30">
-        <v>40.90273458067751</v>
+        <v>55.978704547242401</v>
       </c>
       <c r="AR30" t="s">
         <v>525</v>
@@ -12109,16 +12109,16 @@
         <v>1098</v>
       </c>
       <c r="BA30" t="s">
+        <v>1143</v>
+      </c>
+      <c r="BB30" t="s">
         <v>1144</v>
       </c>
-      <c r="BB30" t="s">
-        <v>815</v>
-      </c>
       <c r="BC30">
-        <v>0.9959052853503485</v>
+        <v>0.98488330873784669</v>
       </c>
       <c r="BD30">
-        <v>75.06976857694373</v>
+        <v>277.13933980614473</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -12183,16 +12183,16 @@
         <v>568</v>
       </c>
       <c r="Y31" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="Z31" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="AA31">
-        <v>0.99321915112555448</v>
+        <v>0.99488652924851917</v>
       </c>
       <c r="AB31">
-        <v>124.31556269816713</v>
+        <v>93.746963777149261</v>
       </c>
       <c r="AD31" t="s">
         <v>525</v>
@@ -12219,16 +12219,16 @@
         <v>871</v>
       </c>
       <c r="AM31" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="AN31" t="s">
         <v>997</v>
       </c>
       <c r="AO31">
-        <v>0.99374536027070226</v>
+        <v>0.9959346869215373</v>
       </c>
       <c r="AP31">
-        <v>114.668395037126</v>
+        <v>74.530739771815789</v>
       </c>
       <c r="AR31" t="s">
         <v>525</v>
@@ -12258,13 +12258,13 @@
         <v>1145</v>
       </c>
       <c r="BB31" t="s">
-        <v>816</v>
+        <v>977</v>
       </c>
       <c r="BC31">
-        <v>0.99032129621526932</v>
+        <v>0.99665799830099</v>
       </c>
       <c r="BD31">
-        <v>177.44290272006148</v>
+        <v>61.270031148516708</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -12329,16 +12329,16 @@
         <v>570</v>
       </c>
       <c r="Y32" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="Z32" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="AA32">
-        <v>0.99651573552934036</v>
+        <v>0.99634407688349669</v>
       </c>
       <c r="AB32">
-        <v>63.878181962093116</v>
+        <v>67.025257135894208</v>
       </c>
       <c r="AD32" t="s">
         <v>525</v>
@@ -12365,16 +12365,16 @@
         <v>873</v>
       </c>
       <c r="AM32" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="AO32">
-        <v>0.99733068647604728</v>
+        <v>0.99512778152424219</v>
       </c>
       <c r="AP32">
-        <v>48.937414605800647</v>
+        <v>89.324005388893795</v>
       </c>
       <c r="AR32" t="s">
         <v>525</v>
@@ -12404,13 +12404,13 @@
         <v>1146</v>
       </c>
       <c r="BB32" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="BC32">
-        <v>0.98691003029105739</v>
+        <v>0.99401640271965719</v>
       </c>
       <c r="BD32">
-        <v>239.98277799728109</v>
+        <v>109.69928347295183</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -12475,16 +12475,16 @@
         <v>572</v>
       </c>
       <c r="Y33" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="Z33" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="AA33">
-        <v>0.99710492314704047</v>
+        <v>0.9882785445805562</v>
       </c>
       <c r="AB33">
-        <v>53.07640897092412</v>
+        <v>214.89334935647034</v>
       </c>
       <c r="AD33" t="s">
         <v>525</v>
@@ -12511,16 +12511,16 @@
         <v>875</v>
       </c>
       <c r="AM33" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="AN33" t="s">
-        <v>1001</v>
+        <v>977</v>
       </c>
       <c r="AO33">
-        <v>0.99671693937496686</v>
+        <v>0.99759498179797546</v>
       </c>
       <c r="AP33">
-        <v>60.189444792275019</v>
+        <v>44.092000370450322</v>
       </c>
       <c r="AR33" t="s">
         <v>525</v>
@@ -12547,10 +12547,10 @@
         <v>1104</v>
       </c>
       <c r="BA33" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="BB33" t="s">
-        <v>816</v>
+        <v>775</v>
       </c>
       <c r="BC33">
         <v>0.99834679070917032</v>
@@ -12621,16 +12621,16 @@
         <v>574</v>
       </c>
       <c r="Y34" t="s">
-        <v>519</v>
+        <v>441</v>
       </c>
       <c r="Z34" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="AA34">
-        <v>0.98823673546715696</v>
+        <v>0.99633066933811909</v>
       </c>
       <c r="AB34">
-        <v>215.65984976878829</v>
+        <v>67.271062134483344</v>
       </c>
       <c r="AD34" t="s">
         <v>525</v>
@@ -12657,16 +12657,16 @@
         <v>877</v>
       </c>
       <c r="AM34" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="AN34" t="s">
-        <v>827</v>
+        <v>803</v>
       </c>
       <c r="AO34">
-        <v>0.99729761494442914</v>
+        <v>0.98134982200735632</v>
       </c>
       <c r="AP34">
-        <v>49.543726018799653</v>
+        <v>341.91992986513412</v>
       </c>
       <c r="AR34" t="s">
         <v>525</v>
@@ -12693,10 +12693,10 @@
         <v>1106</v>
       </c>
       <c r="BA34" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="BB34" t="s">
-        <v>776</v>
+        <v>813</v>
       </c>
       <c r="BC34">
         <v>0.98806872821788805</v>
@@ -12767,16 +12767,16 @@
         <v>576</v>
       </c>
       <c r="Y35" t="s">
-        <v>503</v>
+        <v>449</v>
       </c>
       <c r="Z35" t="s">
-        <v>760</v>
+        <v>778</v>
       </c>
       <c r="AA35">
-        <v>0.96316770855847034</v>
+        <v>0.99497952870756723</v>
       </c>
       <c r="AB35">
-        <v>675.25867642804383</v>
+        <v>92.041973694600031</v>
       </c>
       <c r="AD35" t="s">
         <v>525</v>
@@ -12803,16 +12803,16 @@
         <v>879</v>
       </c>
       <c r="AM35" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="AN35" t="s">
-        <v>1004</v>
+        <v>772</v>
       </c>
       <c r="AO35">
-        <v>0.99478775228549088</v>
+        <v>0.98934663566509429</v>
       </c>
       <c r="AP35">
-        <v>95.557874766001078</v>
+        <v>195.31167947327185</v>
       </c>
       <c r="AR35" t="s">
         <v>525</v>
@@ -12839,16 +12839,16 @@
         <v>1108</v>
       </c>
       <c r="BA35" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="BB35" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="BC35">
-        <v>0.99098965084511315</v>
+        <v>0.99032129621526932</v>
       </c>
       <c r="BD35">
-        <v>165.18973450625904</v>
+        <v>177.44290272006148</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -12913,16 +12913,16 @@
         <v>578</v>
       </c>
       <c r="Y36" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="Z36" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="AA36">
-        <v>0.97244982574001193</v>
+        <v>0.97432735774114165</v>
       </c>
       <c r="AB36">
-        <v>505.08652809978111</v>
+        <v>470.66510807906917</v>
       </c>
       <c r="AD36" t="s">
         <v>525</v>
@@ -12952,13 +12952,13 @@
         <v>1005</v>
       </c>
       <c r="AN36" t="s">
-        <v>805</v>
+        <v>997</v>
       </c>
       <c r="AO36">
-        <v>0.99481362508126103</v>
+        <v>0.99105808324017197</v>
       </c>
       <c r="AP36">
-        <v>95.083540176881584</v>
+        <v>163.93514059684662</v>
       </c>
       <c r="AR36" t="s">
         <v>525</v>
@@ -12985,16 +12985,16 @@
         <v>1110</v>
       </c>
       <c r="BA36" t="s">
+        <v>1150</v>
+      </c>
+      <c r="BB36" t="s">
         <v>1151</v>
       </c>
-      <c r="BB36" t="s">
-        <v>801</v>
-      </c>
       <c r="BC36">
-        <v>0.99053278045305837</v>
+        <v>0.98691003029105739</v>
       </c>
       <c r="BD36">
-        <v>173.56569169392964</v>
+        <v>239.98277799728109</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -13059,16 +13059,16 @@
         <v>580</v>
       </c>
       <c r="Y37" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Z37" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="AA37">
-        <v>0.97762911532019692</v>
+        <v>0.98092062608337349</v>
       </c>
       <c r="AB37">
-        <v>410.13288579638987</v>
+        <v>349.78852180481954</v>
       </c>
       <c r="AD37" t="s">
         <v>525</v>
@@ -13098,13 +13098,13 @@
         <v>1006</v>
       </c>
       <c r="AN37" t="s">
-        <v>970</v>
+        <v>1007</v>
       </c>
       <c r="AO37">
-        <v>0.99551365545858539</v>
+        <v>0.99445933293330402</v>
       </c>
       <c r="AP37">
-        <v>82.249649925934918</v>
+        <v>101.57889622275951</v>
       </c>
       <c r="AR37" t="s">
         <v>525</v>
@@ -13134,13 +13134,13 @@
         <v>1152</v>
       </c>
       <c r="BB37" t="s">
-        <v>815</v>
+        <v>775</v>
       </c>
       <c r="BC37">
-        <v>0.99420451954813838</v>
+        <v>0.99054926914187857</v>
       </c>
       <c r="BD37">
-        <v>106.25047495079694</v>
+        <v>173.26339906555947</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -13205,16 +13205,16 @@
         <v>582</v>
       </c>
       <c r="Y38" t="s">
-        <v>510</v>
+        <v>410</v>
       </c>
       <c r="Z38" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AA38">
-        <v>0.98810065757436949</v>
+        <v>0.99511502462858281</v>
       </c>
       <c r="AB38">
-        <v>218.15461113655846</v>
+        <v>89.557881809315646</v>
       </c>
       <c r="AD38" t="s">
         <v>525</v>
@@ -13241,16 +13241,16 @@
         <v>885</v>
       </c>
       <c r="AM38" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="AN38" t="s">
-        <v>823</v>
+        <v>1009</v>
       </c>
       <c r="AO38">
-        <v>0.9972012891192491</v>
+        <v>0.99336049451151065</v>
       </c>
       <c r="AP38">
-        <v>51.309699480432613</v>
+        <v>121.72426728897108</v>
       </c>
       <c r="AR38" t="s">
         <v>525</v>
@@ -13280,13 +13280,13 @@
         <v>1153</v>
       </c>
       <c r="BB38" t="s">
-        <v>787</v>
+        <v>807</v>
       </c>
       <c r="BC38">
-        <v>0.96863461872110523</v>
+        <v>0.98574436213546524</v>
       </c>
       <c r="BD38">
-        <v>575.0319901130714</v>
+        <v>261.35336084980423</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -13351,16 +13351,16 @@
         <v>584</v>
       </c>
       <c r="Y39" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Z39" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AA39">
-        <v>0.98762529884261907</v>
+        <v>0.99569496806116964</v>
       </c>
       <c r="AB39">
-        <v>226.8695212186509</v>
+        <v>78.92558554522391</v>
       </c>
       <c r="AD39" t="s">
         <v>525</v>
@@ -13387,16 +13387,16 @@
         <v>887</v>
       </c>
       <c r="AM39" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="AN39" t="s">
-        <v>1009</v>
+        <v>977</v>
       </c>
       <c r="AO39">
-        <v>0.99554924619735208</v>
+        <v>0.99569050067699549</v>
       </c>
       <c r="AP39">
-        <v>81.597153048545437</v>
+        <v>79.007487588415231</v>
       </c>
       <c r="AR39" t="s">
         <v>525</v>
@@ -13426,13 +13426,13 @@
         <v>1154</v>
       </c>
       <c r="BB39" t="s">
-        <v>815</v>
+        <v>1139</v>
       </c>
       <c r="BC39">
-        <v>0.98946506962487613</v>
+        <v>0.99374755699184159</v>
       </c>
       <c r="BD39">
-        <v>193.14039021060518</v>
+        <v>114.62812181623703</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -13497,16 +13497,16 @@
         <v>586</v>
       </c>
       <c r="Y40" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="Z40" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AA40">
-        <v>0.97765910024833902</v>
+        <v>0.99324534320140812</v>
       </c>
       <c r="AB40">
-        <v>409.58316211378531</v>
+        <v>123.83537464085195</v>
       </c>
       <c r="AD40" t="s">
         <v>525</v>
@@ -13533,16 +13533,16 @@
         <v>889</v>
       </c>
       <c r="AM40" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="AN40" t="s">
-        <v>799</v>
+        <v>1012</v>
       </c>
       <c r="AO40">
-        <v>0.98134982200735632</v>
+        <v>0.97651207122624506</v>
       </c>
       <c r="AP40">
-        <v>341.91992986513412</v>
+        <v>430.61202751883985</v>
       </c>
       <c r="AR40" t="s">
         <v>525</v>
@@ -13572,13 +13572,13 @@
         <v>1155</v>
       </c>
       <c r="BB40" t="s">
-        <v>1130</v>
+        <v>817</v>
       </c>
       <c r="BC40">
-        <v>0.98125520899414764</v>
+        <v>0.99542890407822671</v>
       </c>
       <c r="BD40">
-        <v>343.65450177395917</v>
+        <v>83.803425232511387</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -13643,16 +13643,16 @@
         <v>588</v>
       </c>
       <c r="Y41" t="s">
-        <v>419</v>
+        <v>515</v>
       </c>
       <c r="Z41" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="AA41">
-        <v>0.99660741093787208</v>
+        <v>0.96260810713044742</v>
       </c>
       <c r="AB41">
-        <v>62.197466139011929</v>
+        <v>685.51803594179648</v>
       </c>
       <c r="AD41" t="s">
         <v>525</v>
@@ -13679,16 +13679,16 @@
         <v>891</v>
       </c>
       <c r="AM41" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="AN41" t="s">
-        <v>795</v>
+        <v>805</v>
       </c>
       <c r="AO41">
-        <v>0.98934663566509429</v>
+        <v>0.99620534810300254</v>
       </c>
       <c r="AP41">
-        <v>195.31167947327185</v>
+        <v>69.568618111619969</v>
       </c>
       <c r="AR41" t="s">
         <v>525</v>
@@ -13718,13 +13718,13 @@
         <v>1156</v>
       </c>
       <c r="BB41" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="BC41">
-        <v>0.99314574070258299</v>
+        <v>0.9959052853503485</v>
       </c>
       <c r="BD41">
-        <v>125.66142045264445</v>
+        <v>75.06976857694373</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -13789,16 +13789,16 @@
         <v>590</v>
       </c>
       <c r="Y42" t="s">
-        <v>436</v>
+        <v>523</v>
       </c>
       <c r="Z42" t="s">
-        <v>785</v>
+        <v>768</v>
       </c>
       <c r="AA42">
-        <v>0.99755601192869059</v>
+        <v>0.9952199348493368</v>
       </c>
       <c r="AB42">
-        <v>44.806447974006502</v>
+        <v>87.634527762158285</v>
       </c>
       <c r="AD42" t="s">
         <v>525</v>
@@ -13825,16 +13825,16 @@
         <v>893</v>
       </c>
       <c r="AM42" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="AN42" t="s">
-        <v>1013</v>
+        <v>800</v>
       </c>
       <c r="AO42">
-        <v>0.99105808324017197</v>
+        <v>0.99503039970536677</v>
       </c>
       <c r="AP42">
-        <v>163.93514059684662</v>
+        <v>91.109338734942796</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -13899,16 +13899,16 @@
         <v>592</v>
       </c>
       <c r="Y43" t="s">
-        <v>456</v>
+        <v>500</v>
       </c>
       <c r="Z43" t="s">
-        <v>786</v>
+        <v>760</v>
       </c>
       <c r="AA43">
-        <v>0.9938212728279423</v>
+        <v>0.99458146009165993</v>
       </c>
       <c r="AB43">
-        <v>113.27666482105715</v>
+        <v>99.339898319567055</v>
       </c>
       <c r="AD43" t="s">
         <v>525</v>
@@ -13935,16 +13935,16 @@
         <v>895</v>
       </c>
       <c r="AM43" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="AN43" t="s">
-        <v>1015</v>
+        <v>973</v>
       </c>
       <c r="AO43">
-        <v>0.99445933293330402</v>
+        <v>0.99648541839873139</v>
       </c>
       <c r="AP43">
-        <v>101.57889622275951</v>
+        <v>64.433996023258757</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -14009,16 +14009,16 @@
         <v>594</v>
       </c>
       <c r="Y44" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="Z44" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="AA44">
-        <v>0.99529213309817555</v>
+        <v>0.99379518324865879</v>
       </c>
       <c r="AB44">
-        <v>86.310893200114194</v>
+        <v>113.75497377458942</v>
       </c>
       <c r="AD44" t="s">
         <v>525</v>
@@ -14048,13 +14048,13 @@
         <v>1016</v>
       </c>
       <c r="AN44" t="s">
-        <v>1017</v>
+        <v>766</v>
       </c>
       <c r="AO44">
-        <v>0.99336049451151065</v>
+        <v>0.99681149341412811</v>
       </c>
       <c r="AP44">
-        <v>121.72426728897108</v>
+        <v>58.455954074317894</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -14119,16 +14119,16 @@
         <v>596</v>
       </c>
       <c r="Y45" t="s">
-        <v>469</v>
+        <v>442</v>
       </c>
       <c r="Z45" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="AA45">
-        <v>0.99156696838886027</v>
+        <v>0.99572772883333938</v>
       </c>
       <c r="AB45">
-        <v>154.60557953756208</v>
+        <v>78.324971388777698</v>
       </c>
       <c r="AD45" t="s">
         <v>525</v>
@@ -14155,16 +14155,16 @@
         <v>899</v>
       </c>
       <c r="AM45" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="AN45" t="s">
-        <v>1001</v>
+        <v>829</v>
       </c>
       <c r="AO45">
-        <v>0.99569050067699549</v>
+        <v>0.99641899952784574</v>
       </c>
       <c r="AP45">
-        <v>79.007487588415231</v>
+        <v>65.65167532282868</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -14229,16 +14229,16 @@
         <v>598</v>
       </c>
       <c r="Y46" t="s">
-        <v>444</v>
+        <v>522</v>
       </c>
       <c r="Z46" t="s">
-        <v>789</v>
+        <v>768</v>
       </c>
       <c r="AA46">
-        <v>0.99401688555089329</v>
+        <v>0.98313106622136326</v>
       </c>
       <c r="AB46">
-        <v>109.69043156695554</v>
+        <v>309.26378594167363</v>
       </c>
       <c r="AD46" t="s">
         <v>525</v>
@@ -14265,16 +14265,16 @@
         <v>901</v>
       </c>
       <c r="AM46" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="AN46" t="s">
-        <v>761</v>
+        <v>788</v>
       </c>
       <c r="AO46">
-        <v>0.98599828568941739</v>
+        <v>0.99000303435887327</v>
       </c>
       <c r="AP46">
-        <v>256.69809569401372</v>
+        <v>183.27770342065742</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -14339,16 +14339,16 @@
         <v>600</v>
       </c>
       <c r="Y47" t="s">
-        <v>453</v>
+        <v>496</v>
       </c>
       <c r="Z47" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="AA47">
-        <v>0.99519181845511939</v>
+        <v>0.98061830542009054</v>
       </c>
       <c r="AB47">
-        <v>88.149994989478557</v>
+        <v>355.3310672983406</v>
       </c>
       <c r="AD47" t="s">
         <v>525</v>
@@ -14375,16 +14375,16 @@
         <v>903</v>
       </c>
       <c r="AM47" t="s">
+        <v>1019</v>
+      </c>
+      <c r="AN47" t="s">
         <v>1020</v>
       </c>
-      <c r="AN47" t="s">
-        <v>816</v>
-      </c>
       <c r="AO47">
-        <v>0.99679484751730962</v>
+        <v>0.98452519237182756</v>
       </c>
       <c r="AP47">
-        <v>58.761128849323015</v>
+        <v>283.70480651649393</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -14449,16 +14449,16 @@
         <v>602</v>
       </c>
       <c r="Y48" t="s">
-        <v>452</v>
+        <v>490</v>
       </c>
       <c r="Z48" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="AA48">
-        <v>0.99559756506177444</v>
+        <v>0.99107116626800151</v>
       </c>
       <c r="AB48">
-        <v>80.711307200801741</v>
+        <v>163.69528508663959</v>
       </c>
       <c r="AD48" t="s">
         <v>525</v>
@@ -14488,13 +14488,13 @@
         <v>1021</v>
       </c>
       <c r="AN48" t="s">
-        <v>1022</v>
+        <v>763</v>
       </c>
       <c r="AO48">
-        <v>0.9968708897783195</v>
+        <v>0.9974675531234084</v>
       </c>
       <c r="AP48">
-        <v>57.367020730809493</v>
+        <v>46.428192737512276</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -14559,16 +14559,16 @@
         <v>604</v>
       </c>
       <c r="Y49" t="s">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="Z49" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="AA49">
-        <v>0.99703099037584386</v>
+        <v>0.99464340805826168</v>
       </c>
       <c r="AB49">
-        <v>54.431843109528238</v>
+        <v>98.204185598535332</v>
       </c>
       <c r="AD49" t="s">
         <v>525</v>
@@ -14595,16 +14595,16 @@
         <v>907</v>
       </c>
       <c r="AM49" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="AN49" t="s">
         <v>764</v>
       </c>
       <c r="AO49">
-        <v>0.99352359657507616</v>
+        <v>0.99532453653339104</v>
       </c>
       <c r="AP49">
-        <v>118.7340627902709</v>
+        <v>85.716830221163534</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -14669,16 +14669,16 @@
         <v>606</v>
       </c>
       <c r="Y50" t="s">
-        <v>520</v>
+        <v>463</v>
       </c>
       <c r="Z50" t="s">
-        <v>768</v>
+        <v>787</v>
       </c>
       <c r="AA50">
-        <v>0.99506650442525857</v>
+        <v>0.99480863709915346</v>
       </c>
       <c r="AB50">
-        <v>90.447418870259696</v>
+        <v>95.174986515519862</v>
       </c>
       <c r="AD50" t="s">
         <v>525</v>
@@ -14705,16 +14705,16 @@
         <v>909</v>
       </c>
       <c r="AM50" t="s">
+        <v>1023</v>
+      </c>
+      <c r="AN50" t="s">
         <v>1024</v>
       </c>
-      <c r="AN50" t="s">
-        <v>772</v>
-      </c>
       <c r="AO50">
-        <v>0.99527349340380789</v>
+        <v>0.996795372708284</v>
       </c>
       <c r="AP50">
-        <v>86.652620930188576</v>
+        <v>58.751500348127372</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -14779,16 +14779,16 @@
         <v>608</v>
       </c>
       <c r="Y51" t="s">
-        <v>512</v>
+        <v>445</v>
       </c>
       <c r="Z51" t="s">
-        <v>768</v>
+        <v>784</v>
       </c>
       <c r="AA51">
-        <v>0.99751736863660534</v>
+        <v>0.99377462362826907</v>
       </c>
       <c r="AB51">
-        <v>45.514908328903012</v>
+        <v>114.13190014840048</v>
       </c>
       <c r="AD51" t="s">
         <v>525</v>
@@ -14818,13 +14818,13 @@
         <v>1025</v>
       </c>
       <c r="AN51" t="s">
-        <v>1026</v>
+        <v>1001</v>
       </c>
       <c r="AO51">
-        <v>0.9916381908130667</v>
+        <v>0.99534886842510228</v>
       </c>
       <c r="AP51">
-        <v>153.29983509377652</v>
+        <v>85.270745539791065</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -14889,16 +14889,16 @@
         <v>610</v>
       </c>
       <c r="Y52" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="Z52" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="AA52">
-        <v>0.95679886695043703</v>
+        <v>0.96988338866662871</v>
       </c>
       <c r="AB52">
-        <v>792.02077257532187</v>
+        <v>552.13787444514003</v>
       </c>
       <c r="AD52" t="s">
         <v>525</v>
@@ -14925,16 +14925,16 @@
         <v>913</v>
       </c>
       <c r="AM52" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AN52" t="s">
-        <v>815</v>
+        <v>795</v>
       </c>
       <c r="AO52">
-        <v>0.99729205446773184</v>
+        <v>0.99433447571906541</v>
       </c>
       <c r="AP52">
-        <v>49.645668091582088</v>
+        <v>103.86794515046822</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -14999,16 +14999,16 @@
         <v>612</v>
       </c>
       <c r="Y53" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="Z53" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="AA53">
-        <v>0.98820023878766372</v>
+        <v>0.99645766237006306</v>
       </c>
       <c r="AB53">
-        <v>216.32895555949756</v>
+        <v>64.942856548844617</v>
       </c>
       <c r="AD53" t="s">
         <v>525</v>
@@ -15035,16 +15035,16 @@
         <v>915</v>
       </c>
       <c r="AM53" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AN53" t="s">
         <v>1028</v>
       </c>
-      <c r="AN53" t="s">
-        <v>776</v>
-      </c>
       <c r="AO53">
-        <v>0.99403730604060547</v>
+        <v>0.99572830729593087</v>
       </c>
       <c r="AP53">
-        <v>109.31605592223302</v>
+        <v>78.31436624126674</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -15109,16 +15109,16 @@
         <v>614</v>
       </c>
       <c r="Y54" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="Z54" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="AA54">
-        <v>0.97404342257401955</v>
+        <v>0.98951603395057575</v>
       </c>
       <c r="AB54">
-        <v>475.8705861429753</v>
+        <v>192.20604423944565</v>
       </c>
       <c r="AD54" t="s">
         <v>525</v>
@@ -15148,13 +15148,13 @@
         <v>1029</v>
       </c>
       <c r="AN54" t="s">
-        <v>827</v>
+        <v>761</v>
       </c>
       <c r="AO54">
-        <v>0.99760247912344124</v>
+        <v>0.98599828568941739</v>
       </c>
       <c r="AP54">
-        <v>43.95454940357709</v>
+        <v>256.69809569401372</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -15219,16 +15219,16 @@
         <v>616</v>
       </c>
       <c r="Y55" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="Z55" t="s">
-        <v>761</v>
+        <v>788</v>
       </c>
       <c r="AA55">
-        <v>0.98784519281324712</v>
+        <v>0.99315041369049573</v>
       </c>
       <c r="AB55">
-        <v>222.83813175713675</v>
+        <v>125.57574900757763</v>
       </c>
       <c r="AD55" t="s">
         <v>525</v>
@@ -15258,13 +15258,13 @@
         <v>1030</v>
       </c>
       <c r="AN55" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="AO55">
-        <v>0.98829989485605374</v>
+        <v>0.99679484751730962</v>
       </c>
       <c r="AP55">
-        <v>214.50192763901472</v>
+        <v>58.761128849323015</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -15329,16 +15329,16 @@
         <v>618</v>
       </c>
       <c r="Y56" t="s">
-        <v>415</v>
+        <v>475</v>
       </c>
       <c r="Z56" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="AA56">
-        <v>0.99679666622099095</v>
+        <v>0.99417318459860438</v>
       </c>
       <c r="AB56">
-        <v>58.72778594849845</v>
+        <v>106.82494902558629</v>
       </c>
       <c r="AD56" t="s">
         <v>525</v>
@@ -15368,13 +15368,13 @@
         <v>1031</v>
       </c>
       <c r="AN56" t="s">
-        <v>780</v>
+        <v>1032</v>
       </c>
       <c r="AO56">
-        <v>0.99661420625883024</v>
+        <v>0.9968708897783195</v>
       </c>
       <c r="AP56">
-        <v>62.072885254778228</v>
+        <v>57.367020730809493</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -15439,16 +15439,16 @@
         <v>620</v>
       </c>
       <c r="Y57" t="s">
-        <v>493</v>
+        <v>418</v>
       </c>
       <c r="Z57" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="AA57">
-        <v>0.98775140142897844</v>
+        <v>0.99771856082351684</v>
       </c>
       <c r="AB57">
-        <v>224.55764046872929</v>
+        <v>41.826384902191116</v>
       </c>
       <c r="AD57" t="s">
         <v>525</v>
@@ -15475,16 +15475,16 @@
         <v>923</v>
       </c>
       <c r="AM57" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="AN57" t="s">
-        <v>822</v>
+        <v>764</v>
       </c>
       <c r="AO57">
-        <v>0.97416725971121887</v>
+        <v>0.99352359657507616</v>
       </c>
       <c r="AP57">
-        <v>473.60023862765331</v>
+        <v>118.7340627902709</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -15549,16 +15549,16 @@
         <v>622</v>
       </c>
       <c r="Y58" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="Z58" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="AA58">
-        <v>0.99149332428826786</v>
+        <v>0.9951333541612547</v>
       </c>
       <c r="AB58">
-        <v>155.95572138175513</v>
+        <v>89.221840376997676</v>
       </c>
       <c r="AD58" t="s">
         <v>525</v>
@@ -15585,16 +15585,16 @@
         <v>925</v>
       </c>
       <c r="AM58" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="AN58" t="s">
         <v>784</v>
       </c>
       <c r="AO58">
-        <v>0.99766717912296166</v>
+        <v>0.99527349340380789</v>
       </c>
       <c r="AP58">
-        <v>42.768382745703043</v>
+        <v>86.652620930188576</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -15659,16 +15659,16 @@
         <v>624</v>
       </c>
       <c r="Y59" t="s">
-        <v>479</v>
+        <v>516</v>
       </c>
       <c r="Z59" t="s">
-        <v>796</v>
+        <v>768</v>
       </c>
       <c r="AA59">
-        <v>0.99563753295513335</v>
+        <v>0.96192701971480499</v>
       </c>
       <c r="AB59">
-        <v>79.978562489222767</v>
+        <v>698.00463856190902</v>
       </c>
       <c r="AD59" t="s">
         <v>525</v>
@@ -15695,16 +15695,16 @@
         <v>927</v>
       </c>
       <c r="AM59" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="AN59" t="s">
-        <v>776</v>
+        <v>1036</v>
       </c>
       <c r="AO59">
-        <v>0.99498027772893805</v>
+        <v>0.9916381908130667</v>
       </c>
       <c r="AP59">
-        <v>92.02824163613559</v>
+        <v>153.29983509377652</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -15769,16 +15769,16 @@
         <v>626</v>
       </c>
       <c r="Y60" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="Z60" t="s">
-        <v>762</v>
+        <v>792</v>
       </c>
       <c r="AA60">
-        <v>0.99338737982948611</v>
+        <v>0.98117083928229931</v>
       </c>
       <c r="AB60">
-        <v>121.23136979275419</v>
+        <v>345.20127982451362</v>
       </c>
       <c r="AD60" t="s">
         <v>525</v>
@@ -15805,16 +15805,16 @@
         <v>929</v>
       </c>
       <c r="AM60" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="AN60" t="s">
-        <v>772</v>
+        <v>807</v>
       </c>
       <c r="AO60">
-        <v>0.9955955730654259</v>
+        <v>0.99729205446773184</v>
       </c>
       <c r="AP60">
-        <v>80.747827133859133</v>
+        <v>49.645668091582088</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -15879,16 +15879,16 @@
         <v>628</v>
       </c>
       <c r="Y61" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="Z61" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="AA61">
-        <v>0.99488652924851917</v>
+        <v>0.99395651765584936</v>
       </c>
       <c r="AB61">
-        <v>93.746963777149261</v>
+        <v>110.79717630942883</v>
       </c>
       <c r="AD61" t="s">
         <v>525</v>
@@ -15915,16 +15915,16 @@
         <v>931</v>
       </c>
       <c r="AM61" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="AN61" t="s">
-        <v>819</v>
+        <v>979</v>
       </c>
       <c r="AO61">
-        <v>0.99000303435887327</v>
+        <v>0.99551365545858539</v>
       </c>
       <c r="AP61">
-        <v>183.27770342065742</v>
+        <v>82.249649925934918</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -15989,16 +15989,16 @@
         <v>630</v>
       </c>
       <c r="Y62" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="Z62" t="s">
-        <v>798</v>
+        <v>783</v>
       </c>
       <c r="AA62">
-        <v>0.99283898738129273</v>
+        <v>0.98563153879963317</v>
       </c>
       <c r="AB62">
-        <v>131.2852313429664</v>
+        <v>263.42178867339101</v>
       </c>
       <c r="AD62" t="s">
         <v>525</v>
@@ -16025,16 +16025,16 @@
         <v>933</v>
       </c>
       <c r="AM62" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="AN62" t="s">
-        <v>1038</v>
+        <v>820</v>
       </c>
       <c r="AO62">
-        <v>0.98452519237182756</v>
+        <v>0.9972012891192491</v>
       </c>
       <c r="AP62">
-        <v>283.70480651649393</v>
+        <v>51.309699480432613</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -16099,16 +16099,16 @@
         <v>632</v>
       </c>
       <c r="Y63" t="s">
-        <v>474</v>
+        <v>421</v>
       </c>
       <c r="Z63" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="AA63">
-        <v>0.99380730657517002</v>
+        <v>0.99558181127270129</v>
       </c>
       <c r="AB63">
-        <v>113.53271278855006</v>
+        <v>81.000126667143434</v>
       </c>
       <c r="AD63" t="s">
         <v>525</v>
@@ -16135,16 +16135,16 @@
         <v>935</v>
       </c>
       <c r="AM63" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="AN63" t="s">
-        <v>763</v>
+        <v>1041</v>
       </c>
       <c r="AO63">
-        <v>0.9974675531234084</v>
+        <v>0.99554924619735208</v>
       </c>
       <c r="AP63">
-        <v>46.428192737512276</v>
+        <v>81.597153048545437</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -16209,16 +16209,16 @@
         <v>634</v>
       </c>
       <c r="Y64" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="Z64" t="s">
-        <v>795</v>
+        <v>784</v>
       </c>
       <c r="AA64">
-        <v>0.9826276473097606</v>
+        <v>0.99476729801312358</v>
       </c>
       <c r="AB64">
-        <v>318.4931326543898</v>
+        <v>95.932869759401342</v>
       </c>
       <c r="AD64" t="s">
         <v>525</v>
@@ -16245,16 +16245,16 @@
         <v>937</v>
       </c>
       <c r="AM64" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="AN64" t="s">
-        <v>764</v>
+        <v>821</v>
       </c>
       <c r="AO64">
-        <v>0.99532453653339104</v>
+        <v>0.99414234808301016</v>
       </c>
       <c r="AP64">
-        <v>85.716830221163534</v>
+        <v>107.39028514481463</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -16319,16 +16319,16 @@
         <v>636</v>
       </c>
       <c r="Y65" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="Z65" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="AA65">
-        <v>0.9946346679588659</v>
+        <v>0.99549647084304327</v>
       </c>
       <c r="AB65">
-        <v>98.364420754124808</v>
+        <v>82.564701210872954</v>
       </c>
       <c r="AD65" t="s">
         <v>525</v>
@@ -16355,16 +16355,16 @@
         <v>939</v>
       </c>
       <c r="AM65" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="AN65" t="s">
-        <v>1042</v>
+        <v>797</v>
       </c>
       <c r="AO65">
-        <v>0.996795372708284</v>
+        <v>0.99676376447003934</v>
       </c>
       <c r="AP65">
-        <v>58.751500348127372</v>
+        <v>59.330984715944624</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -16429,16 +16429,16 @@
         <v>638</v>
       </c>
       <c r="Y66" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="Z66" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="AA66">
-        <v>0.997058362423484</v>
+        <v>0.99219252851411011</v>
       </c>
       <c r="AB66">
-        <v>53.930022236127087</v>
+        <v>143.13697724131458</v>
       </c>
       <c r="AD66" t="s">
         <v>525</v>
@@ -16465,16 +16465,16 @@
         <v>941</v>
       </c>
       <c r="AM66" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="AN66" t="s">
-        <v>1044</v>
+        <v>979</v>
       </c>
       <c r="AO66">
-        <v>0.99534886842510228</v>
+        <v>0.99424679200457</v>
       </c>
       <c r="AP66">
-        <v>85.270745539791065</v>
+        <v>105.47547991621673</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -16539,16 +16539,16 @@
         <v>640</v>
       </c>
       <c r="Y67" t="s">
-        <v>427</v>
+        <v>470</v>
       </c>
       <c r="Z67" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="AA67">
-        <v>0.99219252851411011</v>
+        <v>0.98460718356608945</v>
       </c>
       <c r="AB67">
-        <v>143.13697724131458</v>
+        <v>282.20163462169398</v>
       </c>
       <c r="AD67" t="s">
         <v>525</v>
@@ -16578,13 +16578,13 @@
         <v>1045</v>
       </c>
       <c r="AN67" t="s">
-        <v>828</v>
+        <v>780</v>
       </c>
       <c r="AO67">
-        <v>0.99433447571906541</v>
+        <v>0.99567626923235475</v>
       </c>
       <c r="AP67">
-        <v>103.86794515046822</v>
+        <v>79.268397406829976</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -16649,16 +16649,16 @@
         <v>642</v>
       </c>
       <c r="Y68" t="s">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="Z68" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="AA68">
-        <v>0.98460718356608945</v>
+        <v>0.99472452677636702</v>
       </c>
       <c r="AB68">
-        <v>282.20163462169398</v>
+        <v>96.717009099937485</v>
       </c>
       <c r="AD68" t="s">
         <v>525</v>
@@ -16691,10 +16691,10 @@
         <v>1047</v>
       </c>
       <c r="AO68">
-        <v>0.99572830729593087</v>
+        <v>0.99766813121902409</v>
       </c>
       <c r="AP68">
-        <v>78.31436624126674</v>
+        <v>42.750927651225993</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -16759,16 +16759,16 @@
         <v>644</v>
       </c>
       <c r="Y69" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="Z69" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="AA69">
-        <v>0.99472452677636702</v>
+        <v>0.99427848954198372</v>
       </c>
       <c r="AB69">
-        <v>96.717009099937485</v>
+        <v>104.89435839696445</v>
       </c>
       <c r="AD69" t="s">
         <v>525</v>
@@ -16798,13 +16798,13 @@
         <v>1048</v>
       </c>
       <c r="AN69" t="s">
-        <v>1049</v>
+        <v>819</v>
       </c>
       <c r="AO69">
-        <v>0.97651207122624506</v>
+        <v>0.97416725971121887</v>
       </c>
       <c r="AP69">
-        <v>430.61202751883985</v>
+        <v>473.60023862765331</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -16869,16 +16869,16 @@
         <v>646</v>
       </c>
       <c r="Y70" t="s">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="Z70" t="s">
-        <v>788</v>
+        <v>798</v>
       </c>
       <c r="AA70">
-        <v>0.99427848954198372</v>
+        <v>0.99491123944448234</v>
       </c>
       <c r="AB70">
-        <v>104.89435839696445</v>
+        <v>93.293943517823692</v>
       </c>
       <c r="AD70" t="s">
         <v>525</v>
@@ -16905,16 +16905,16 @@
         <v>949</v>
       </c>
       <c r="AM70" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="AN70" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="AO70">
-        <v>0.99620534810300254</v>
+        <v>0.99766717912296166</v>
       </c>
       <c r="AP70">
-        <v>69.568618111619969</v>
+        <v>42.768382745703043</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -16979,16 +16979,16 @@
         <v>648</v>
       </c>
       <c r="Y71" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Z71" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="AA71">
-        <v>0.99491123944448234</v>
+        <v>0.99638451167998066</v>
       </c>
       <c r="AB71">
-        <v>93.293943517823692</v>
+        <v>66.283952533688392</v>
       </c>
       <c r="AD71" t="s">
         <v>525</v>
@@ -17015,16 +17015,16 @@
         <v>951</v>
       </c>
       <c r="AM71" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="AN71" t="s">
-        <v>775</v>
+        <v>813</v>
       </c>
       <c r="AO71">
-        <v>0.99503039970536677</v>
+        <v>0.99498027772893805</v>
       </c>
       <c r="AP71">
-        <v>91.109338734942796</v>
+        <v>92.02824163613559</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17089,16 +17089,16 @@
         <v>650</v>
       </c>
       <c r="Y72" t="s">
-        <v>448</v>
+        <v>514</v>
       </c>
       <c r="Z72" t="s">
-        <v>805</v>
+        <v>768</v>
       </c>
       <c r="AA72">
-        <v>0.99638451167998066</v>
+        <v>0.96942910386940295</v>
       </c>
       <c r="AB72">
-        <v>66.283952533688392</v>
+        <v>560.46642906094564</v>
       </c>
       <c r="AD72" t="s">
         <v>525</v>
@@ -17125,16 +17125,16 @@
         <v>953</v>
       </c>
       <c r="AM72" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AN72" t="s">
-        <v>997</v>
+        <v>784</v>
       </c>
       <c r="AO72">
-        <v>0.99648541839873139</v>
+        <v>0.9955955730654259</v>
       </c>
       <c r="AP72">
-        <v>64.433996023258757</v>
+        <v>80.747827133859133</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -17199,16 +17199,16 @@
         <v>652</v>
       </c>
       <c r="Y73" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="Z73" t="s">
-        <v>806</v>
+        <v>785</v>
       </c>
       <c r="AA73">
-        <v>0.98322768674096572</v>
+        <v>0.95261480241426988</v>
       </c>
       <c r="AB73">
-        <v>307.49240974896213</v>
+        <v>868.72862240505196</v>
       </c>
       <c r="AD73" t="s">
         <v>525</v>
@@ -17235,16 +17235,16 @@
         <v>955</v>
       </c>
       <c r="AM73" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AN73" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="AO73">
-        <v>0.99681149341412811</v>
+        <v>0.95532613069733086</v>
       </c>
       <c r="AP73">
-        <v>58.455954074317894</v>
+        <v>819.02093721560016</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -17309,16 +17309,16 @@
         <v>654</v>
       </c>
       <c r="Y74" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="Z74" t="s">
-        <v>807</v>
+        <v>760</v>
       </c>
       <c r="AA74">
-        <v>0.99530040212667992</v>
+        <v>0.93980266520001188</v>
       </c>
       <c r="AB74">
-        <v>86.159294344200944</v>
+        <v>1103.617804666449</v>
       </c>
       <c r="AD74" t="s">
         <v>525</v>
@@ -17345,16 +17345,16 @@
         <v>957</v>
       </c>
       <c r="AM74" t="s">
+        <v>1053</v>
+      </c>
+      <c r="AN74" t="s">
         <v>1054</v>
       </c>
-      <c r="AN74" t="s">
-        <v>791</v>
-      </c>
       <c r="AO74">
-        <v>0.99641899952784574</v>
+        <v>0.9961850470371636</v>
       </c>
       <c r="AP74">
-        <v>65.65167532282868</v>
+        <v>69.94080431866837</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -17419,16 +17419,16 @@
         <v>656</v>
       </c>
       <c r="Y75" t="s">
-        <v>464</v>
+        <v>504</v>
       </c>
       <c r="Z75" t="s">
-        <v>808</v>
+        <v>785</v>
       </c>
       <c r="AA75">
-        <v>0.99420043109362022</v>
+        <v>0.96520767961718001</v>
       </c>
       <c r="AB75">
-        <v>106.32542995029682</v>
+        <v>637.85920701836687</v>
       </c>
       <c r="AD75" t="s">
         <v>525</v>
@@ -17458,13 +17458,13 @@
         <v>1055</v>
       </c>
       <c r="AN75" t="s">
-        <v>1013</v>
+        <v>807</v>
       </c>
       <c r="AO75">
-        <v>0.99760255773158468</v>
+        <v>0.99765219450274578</v>
       </c>
       <c r="AP75">
-        <v>43.953108254279897</v>
+        <v>43.043100782993086</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -17529,16 +17529,16 @@
         <v>658</v>
       </c>
       <c r="Y76" t="s">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="Z76" t="s">
-        <v>809</v>
+        <v>761</v>
       </c>
       <c r="AA76">
-        <v>0.99583023752581945</v>
+        <v>0.9916427371040899</v>
       </c>
       <c r="AB76">
-        <v>76.445645359975842</v>
+        <v>153.21648642501913</v>
       </c>
       <c r="AD76" t="s">
         <v>525</v>
@@ -17568,13 +17568,13 @@
         <v>1056</v>
       </c>
       <c r="AN76" t="s">
-        <v>800</v>
+        <v>816</v>
       </c>
       <c r="AO76">
-        <v>0.99694661611560498</v>
+        <v>0.98829989485605374</v>
       </c>
       <c r="AP76">
-        <v>55.978704547242401</v>
+        <v>214.50192763901472</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -17639,16 +17639,16 @@
         <v>660</v>
       </c>
       <c r="Y77" t="s">
-        <v>466</v>
+        <v>434</v>
       </c>
       <c r="Z77" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="AA77">
-        <v>0.99239852233389214</v>
+        <v>0.99506721859763492</v>
       </c>
       <c r="AB77">
-        <v>139.36042387864416</v>
+        <v>90.434325710025817</v>
       </c>
       <c r="AD77" t="s">
         <v>525</v>
@@ -17678,13 +17678,13 @@
         <v>1057</v>
       </c>
       <c r="AN77" t="s">
-        <v>1013</v>
+        <v>817</v>
       </c>
       <c r="AO77">
-        <v>0.9959346869215373</v>
+        <v>0.99661420625883024</v>
       </c>
       <c r="AP77">
-        <v>74.530739771815789</v>
+        <v>62.072885254778228</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -17749,16 +17749,16 @@
         <v>662</v>
       </c>
       <c r="Y78" t="s">
-        <v>514</v>
+        <v>472</v>
       </c>
       <c r="Z78" t="s">
-        <v>768</v>
+        <v>801</v>
       </c>
       <c r="AA78">
-        <v>0.96942910386940295</v>
+        <v>0.99504955481764434</v>
       </c>
       <c r="AB78">
-        <v>560.46642906094564</v>
+        <v>90.758161676519606</v>
       </c>
       <c r="AD78" t="s">
         <v>525</v>
@@ -17788,13 +17788,13 @@
         <v>1058</v>
       </c>
       <c r="AN78" t="s">
-        <v>1044</v>
+        <v>813</v>
       </c>
       <c r="AO78">
-        <v>0.99512778152424219</v>
+        <v>0.99403730604060547</v>
       </c>
       <c r="AP78">
-        <v>89.324005388893795</v>
+        <v>109.31605592223302</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -17859,16 +17859,16 @@
         <v>664</v>
       </c>
       <c r="Y79" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="Z79" t="s">
-        <v>769</v>
+        <v>802</v>
       </c>
       <c r="AA79">
-        <v>0.95261480241426988</v>
+        <v>0.99267056664092235</v>
       </c>
       <c r="AB79">
-        <v>868.72862240505196</v>
+        <v>134.37294491642297</v>
       </c>
       <c r="AD79" t="s">
         <v>525</v>
@@ -17898,13 +17898,13 @@
         <v>1059</v>
       </c>
       <c r="AN79" t="s">
-        <v>1001</v>
+        <v>794</v>
       </c>
       <c r="AO79">
-        <v>0.99759498179797546</v>
+        <v>0.99760247912344124</v>
       </c>
       <c r="AP79">
-        <v>44.092000370450322</v>
+        <v>43.95454940357709</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -17969,16 +17969,16 @@
         <v>666</v>
       </c>
       <c r="Y80" t="s">
-        <v>501</v>
+        <v>476</v>
       </c>
       <c r="Z80" t="s">
-        <v>760</v>
+        <v>789</v>
       </c>
       <c r="AA80">
-        <v>0.93980266520001188</v>
+        <v>0.99283898738129273</v>
       </c>
       <c r="AB80">
-        <v>1103.617804666449</v>
+        <v>131.2852313429664</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -18043,16 +18043,16 @@
         <v>668</v>
       </c>
       <c r="Y81" t="s">
-        <v>504</v>
+        <v>474</v>
       </c>
       <c r="Z81" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="AA81">
-        <v>0.96520767961718001</v>
+        <v>0.99380730657517002</v>
       </c>
       <c r="AB81">
-        <v>637.85920701836687</v>
+        <v>113.53271278855006</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -18117,16 +18117,16 @@
         <v>670</v>
       </c>
       <c r="Y82" t="s">
-        <v>485</v>
+        <v>432</v>
       </c>
       <c r="Z82" t="s">
-        <v>761</v>
+        <v>772</v>
       </c>
       <c r="AA82">
-        <v>0.9916427371040899</v>
+        <v>0.9826276473097606</v>
       </c>
       <c r="AB82">
-        <v>153.21648642501913</v>
+        <v>318.4931326543898</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -18191,16 +18191,16 @@
         <v>672</v>
       </c>
       <c r="Y83" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="Z83" t="s">
-        <v>775</v>
+        <v>804</v>
       </c>
       <c r="AA83">
-        <v>0.99506721859763492</v>
+        <v>0.9946346679588659</v>
       </c>
       <c r="AB83">
-        <v>90.434325710025817</v>
+        <v>98.364420754124808</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -18265,16 +18265,16 @@
         <v>674</v>
       </c>
       <c r="Y84" t="s">
-        <v>472</v>
+        <v>422</v>
       </c>
       <c r="Z84" t="s">
-        <v>811</v>
+        <v>790</v>
       </c>
       <c r="AA84">
-        <v>0.99504955481764434</v>
+        <v>0.997058362423484</v>
       </c>
       <c r="AB84">
-        <v>90.758161676519606</v>
+        <v>53.930022236127087</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -18339,16 +18339,16 @@
         <v>676</v>
       </c>
       <c r="Y85" t="s">
-        <v>486</v>
+        <v>521</v>
       </c>
       <c r="Z85" t="s">
-        <v>812</v>
+        <v>768</v>
       </c>
       <c r="AA85">
-        <v>0.99267056664092235</v>
+        <v>0.99295369446862825</v>
       </c>
       <c r="AB85">
-        <v>134.37294491642297</v>
+        <v>129.18226807514921</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -18413,16 +18413,16 @@
         <v>678</v>
       </c>
       <c r="Y86" t="s">
-        <v>515</v>
+        <v>482</v>
       </c>
       <c r="Z86" t="s">
-        <v>768</v>
+        <v>793</v>
       </c>
       <c r="AA86">
-        <v>0.96260810713044742</v>
+        <v>0.99247189917622181</v>
       </c>
       <c r="AB86">
-        <v>685.51803594179648</v>
+        <v>138.01518176926754</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -18487,16 +18487,16 @@
         <v>680</v>
       </c>
       <c r="Y87" t="s">
-        <v>523</v>
+        <v>416</v>
       </c>
       <c r="Z87" t="s">
-        <v>768</v>
+        <v>805</v>
       </c>
       <c r="AA87">
-        <v>0.9952199348493368</v>
+        <v>0.99654635223367616</v>
       </c>
       <c r="AB87">
-        <v>87.634527762158285</v>
+        <v>63.316875715936199</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -18561,16 +18561,16 @@
         <v>682</v>
       </c>
       <c r="Y88" t="s">
-        <v>500</v>
+        <v>424</v>
       </c>
       <c r="Z88" t="s">
-        <v>760</v>
+        <v>806</v>
       </c>
       <c r="AA88">
-        <v>0.99458146009165993</v>
+        <v>0.99732405475730812</v>
       </c>
       <c r="AB88">
-        <v>99.339898319567055</v>
+        <v>49.058996116017695</v>
       </c>
     </row>
     <row r="89" spans="2:28">
@@ -18635,16 +18635,16 @@
         <v>684</v>
       </c>
       <c r="Y89" t="s">
-        <v>487</v>
+        <v>425</v>
       </c>
       <c r="Z89" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="AA89">
-        <v>0.99379518324865879</v>
+        <v>0.99730161188979438</v>
       </c>
       <c r="AB89">
-        <v>113.75497377458942</v>
+        <v>49.470448687103634</v>
       </c>
     </row>
     <row r="90" spans="2:28">
@@ -18709,16 +18709,16 @@
         <v>686</v>
       </c>
       <c r="Y90" t="s">
-        <v>442</v>
+        <v>484</v>
       </c>
       <c r="Z90" t="s">
-        <v>772</v>
+        <v>808</v>
       </c>
       <c r="AA90">
-        <v>0.99572772883333938</v>
+        <v>0.98322768674096572</v>
       </c>
       <c r="AB90">
-        <v>78.324971388777698</v>
+        <v>307.49240974896213</v>
       </c>
     </row>
     <row r="91" spans="2:28">
@@ -18783,16 +18783,16 @@
         <v>688</v>
       </c>
       <c r="Y91" t="s">
-        <v>521</v>
+        <v>480</v>
       </c>
       <c r="Z91" t="s">
-        <v>768</v>
+        <v>809</v>
       </c>
       <c r="AA91">
-        <v>0.99295369446862825</v>
+        <v>0.99530040212667992</v>
       </c>
       <c r="AB91">
-        <v>129.18226807514921</v>
+        <v>86.159294344200944</v>
       </c>
     </row>
     <row r="92" spans="2:28">
@@ -18857,16 +18857,16 @@
         <v>690</v>
       </c>
       <c r="Y92" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="Z92" t="s">
-        <v>783</v>
+        <v>810</v>
       </c>
       <c r="AA92">
-        <v>0.99247189917622181</v>
+        <v>0.99420043109362022</v>
       </c>
       <c r="AB92">
-        <v>138.01518176926754</v>
+        <v>106.32542995029682</v>
       </c>
     </row>
     <row r="93" spans="2:28">
@@ -18931,16 +18931,16 @@
         <v>692</v>
       </c>
       <c r="Y93" t="s">
-        <v>416</v>
+        <v>460</v>
       </c>
       <c r="Z93" t="s">
-        <v>774</v>
+        <v>811</v>
       </c>
       <c r="AA93">
-        <v>0.99654635223367616</v>
+        <v>0.99583023752581945</v>
       </c>
       <c r="AB93">
-        <v>63.316875715936199</v>
+        <v>76.445645359975842</v>
       </c>
     </row>
     <row r="94" spans="2:28">
@@ -19005,16 +19005,16 @@
         <v>694</v>
       </c>
       <c r="Y94" t="s">
-        <v>424</v>
+        <v>466</v>
       </c>
       <c r="Z94" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="AA94">
-        <v>0.99732405475730812</v>
+        <v>0.99239852233389214</v>
       </c>
       <c r="AB94">
-        <v>49.058996116017695</v>
+        <v>139.36042387864416</v>
       </c>
     </row>
     <row r="95" spans="2:28">
@@ -19079,16 +19079,16 @@
         <v>696</v>
       </c>
       <c r="Y95" t="s">
-        <v>425</v>
+        <v>511</v>
       </c>
       <c r="Z95" t="s">
-        <v>815</v>
+        <v>769</v>
       </c>
       <c r="AA95">
-        <v>0.99730161188979438</v>
+        <v>0.99008735429887684</v>
       </c>
       <c r="AB95">
-        <v>49.470448687103634</v>
+        <v>181.7318378539255</v>
       </c>
     </row>
     <row r="96" spans="2:28">
@@ -19153,16 +19153,16 @@
         <v>698</v>
       </c>
       <c r="Y96" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="Z96" t="s">
-        <v>816</v>
+        <v>805</v>
       </c>
       <c r="AA96">
-        <v>0.99634407688349669</v>
+        <v>0.98622431616682615</v>
       </c>
       <c r="AB96">
-        <v>67.025257135894208</v>
+        <v>252.55420360818721</v>
       </c>
     </row>
     <row r="97" spans="2:28">
@@ -19227,16 +19227,16 @@
         <v>700</v>
       </c>
       <c r="Y97" t="s">
-        <v>471</v>
+        <v>433</v>
       </c>
       <c r="Z97" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="AA97">
-        <v>0.9882785445805562</v>
+        <v>0.98732531824996883</v>
       </c>
       <c r="AB97">
-        <v>214.89334935647034</v>
+        <v>232.36916541723792</v>
       </c>
     </row>
     <row r="98" spans="2:28">
@@ -19301,16 +19301,16 @@
         <v>702</v>
       </c>
       <c r="Y98" t="s">
-        <v>441</v>
+        <v>409</v>
       </c>
       <c r="Z98" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="AA98">
-        <v>0.99633066933811909</v>
+        <v>0.99468658155318235</v>
       </c>
       <c r="AB98">
-        <v>67.271062134483344</v>
+        <v>97.412671524990884</v>
       </c>
     </row>
     <row r="99" spans="2:28">
@@ -19375,16 +19375,16 @@
         <v>704</v>
       </c>
       <c r="Y99" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="Z99" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="AA99">
-        <v>0.99497952870756723</v>
+        <v>0.99713964204801786</v>
       </c>
       <c r="AB99">
-        <v>92.041973694600031</v>
+        <v>52.439895786339292</v>
       </c>
     </row>
     <row r="100" spans="2:28">
@@ -19449,16 +19449,16 @@
         <v>706</v>
       </c>
       <c r="Y100" t="s">
-        <v>518</v>
+        <v>461</v>
       </c>
       <c r="Z100" t="s">
-        <v>768</v>
+        <v>815</v>
       </c>
       <c r="AA100">
-        <v>0.96988338866662871</v>
+        <v>0.99321915112555448</v>
       </c>
       <c r="AB100">
-        <v>552.13787444514003</v>
+        <v>124.31556269816713</v>
       </c>
     </row>
     <row r="101" spans="2:28">
@@ -19523,16 +19523,16 @@
         <v>708</v>
       </c>
       <c r="Y101" t="s">
-        <v>513</v>
+        <v>443</v>
       </c>
       <c r="Z101" t="s">
-        <v>768</v>
+        <v>816</v>
       </c>
       <c r="AA101">
-        <v>0.99645766237006306</v>
+        <v>0.99651573552934036</v>
       </c>
       <c r="AB101">
-        <v>64.942856548844617</v>
+        <v>63.878181962093116</v>
       </c>
     </row>
     <row r="102" spans="2:28">
@@ -19597,16 +19597,16 @@
         <v>710</v>
       </c>
       <c r="Y102" t="s">
-        <v>509</v>
+        <v>454</v>
       </c>
       <c r="Z102" t="s">
-        <v>768</v>
+        <v>817</v>
       </c>
       <c r="AA102">
-        <v>0.98951603395057575</v>
+        <v>0.99710492314704047</v>
       </c>
       <c r="AB102">
-        <v>192.20604423944565</v>
+        <v>53.07640897092412</v>
       </c>
     </row>
     <row r="103" spans="2:28">
@@ -19671,16 +19671,16 @@
         <v>712</v>
       </c>
       <c r="Y103" t="s">
-        <v>414</v>
+        <v>498</v>
       </c>
       <c r="Z103" t="s">
-        <v>819</v>
+        <v>760</v>
       </c>
       <c r="AA103">
-        <v>0.99315041369049573</v>
+        <v>0.99020196511745218</v>
       </c>
       <c r="AB103">
-        <v>125.57574900757763</v>
+        <v>179.63063951337628</v>
       </c>
     </row>
     <row r="104" spans="2:28">
@@ -19745,16 +19745,16 @@
         <v>714</v>
       </c>
       <c r="Y104" t="s">
-        <v>475</v>
+        <v>430</v>
       </c>
       <c r="Z104" t="s">
-        <v>798</v>
+        <v>818</v>
       </c>
       <c r="AA104">
-        <v>0.99417318459860438</v>
+        <v>0.97046710847823026</v>
       </c>
       <c r="AB104">
-        <v>106.82494902558629</v>
+        <v>541.43634456577831</v>
       </c>
     </row>
     <row r="105" spans="2:28">
@@ -19819,16 +19819,16 @@
         <v>716</v>
       </c>
       <c r="Y105" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="Z105" t="s">
-        <v>801</v>
+        <v>819</v>
       </c>
       <c r="AA105">
-        <v>0.99771856082351684</v>
+        <v>0.97537850670549553</v>
       </c>
       <c r="AB105">
-        <v>41.826384902191116</v>
+        <v>451.39404373258168</v>
       </c>
     </row>
     <row r="106" spans="2:28">
@@ -19893,16 +19893,16 @@
         <v>718</v>
       </c>
       <c r="Y106" t="s">
-        <v>437</v>
+        <v>492</v>
       </c>
       <c r="Z106" t="s">
-        <v>820</v>
+        <v>793</v>
       </c>
       <c r="AA106">
-        <v>0.9951333541612547</v>
+        <v>0.98289281118622185</v>
       </c>
       <c r="AB106">
-        <v>89.221840376997676</v>
+        <v>313.63179491926536</v>
       </c>
     </row>
     <row r="107" spans="2:28">
@@ -19967,16 +19967,16 @@
         <v>720</v>
       </c>
       <c r="Y107" t="s">
-        <v>498</v>
+        <v>423</v>
       </c>
       <c r="Z107" t="s">
-        <v>760</v>
+        <v>820</v>
       </c>
       <c r="AA107">
-        <v>0.99020196511745218</v>
+        <v>0.99777342334799435</v>
       </c>
       <c r="AB107">
-        <v>179.63063951337628</v>
+        <v>40.820571953437025</v>
       </c>
     </row>
     <row r="108" spans="2:28">
@@ -20041,16 +20041,16 @@
         <v>722</v>
       </c>
       <c r="Y108" t="s">
-        <v>430</v>
+        <v>459</v>
       </c>
       <c r="Z108" t="s">
         <v>821</v>
       </c>
       <c r="AA108">
-        <v>0.97046710847823026</v>
+        <v>0.99456845174856667</v>
       </c>
       <c r="AB108">
-        <v>541.43634456577831</v>
+        <v>99.578384609610097</v>
       </c>
     </row>
     <row r="109" spans="2:28">
@@ -20115,16 +20115,16 @@
         <v>724</v>
       </c>
       <c r="Y109" t="s">
-        <v>429</v>
+        <v>465</v>
       </c>
       <c r="Z109" t="s">
         <v>822</v>
       </c>
       <c r="AA109">
-        <v>0.97537850670549553</v>
+        <v>0.99302343871187126</v>
       </c>
       <c r="AB109">
-        <v>451.39404373258168</v>
+        <v>127.90362361569299</v>
       </c>
     </row>
     <row r="110" spans="2:28">
@@ -20189,16 +20189,16 @@
         <v>726</v>
       </c>
       <c r="Y110" t="s">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="Z110" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="AA110">
-        <v>0.98289281118622185</v>
+        <v>0.98823673546715696</v>
       </c>
       <c r="AB110">
-        <v>313.63179491926536</v>
+        <v>215.65984976878829</v>
       </c>
     </row>
     <row r="111" spans="2:28">
@@ -20263,16 +20263,16 @@
         <v>728</v>
       </c>
       <c r="Y111" t="s">
-        <v>423</v>
+        <v>503</v>
       </c>
       <c r="Z111" t="s">
-        <v>823</v>
+        <v>760</v>
       </c>
       <c r="AA111">
-        <v>0.99777342334799435</v>
+        <v>0.96316770855847034</v>
       </c>
       <c r="AB111">
-        <v>40.820571953437025</v>
+        <v>675.25867642804383</v>
       </c>
     </row>
     <row r="112" spans="2:28">
@@ -20337,16 +20337,16 @@
         <v>730</v>
       </c>
       <c r="Y112" t="s">
-        <v>459</v>
+        <v>507</v>
       </c>
       <c r="Z112" t="s">
-        <v>824</v>
+        <v>760</v>
       </c>
       <c r="AA112">
-        <v>0.99456845174856667</v>
+        <v>0.97244982574001193</v>
       </c>
       <c r="AB112">
-        <v>99.578384609610097</v>
+        <v>505.08652809978111</v>
       </c>
     </row>
     <row r="113" spans="2:28">
@@ -20411,16 +20411,16 @@
         <v>732</v>
       </c>
       <c r="Y113" t="s">
-        <v>465</v>
+        <v>495</v>
       </c>
       <c r="Z113" t="s">
-        <v>825</v>
+        <v>769</v>
       </c>
       <c r="AA113">
-        <v>0.99302343871187126</v>
+        <v>0.97762911532019692</v>
       </c>
       <c r="AB113">
-        <v>127.90362361569299</v>
+        <v>410.13288579638987</v>
       </c>
     </row>
     <row r="114" spans="2:28">
@@ -20485,16 +20485,16 @@
         <v>734</v>
       </c>
       <c r="Y114" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="Z114" t="s">
-        <v>768</v>
+        <v>823</v>
       </c>
       <c r="AA114">
-        <v>0.96192701971480499</v>
+        <v>0.98810065757436949</v>
       </c>
       <c r="AB114">
-        <v>698.00463856190902</v>
+        <v>218.15461113655846</v>
       </c>
     </row>
     <row r="115" spans="2:28">
@@ -20559,16 +20559,16 @@
         <v>736</v>
       </c>
       <c r="Y115" t="s">
-        <v>491</v>
+        <v>413</v>
       </c>
       <c r="Z115" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="AA115">
-        <v>0.98117083928229931</v>
+        <v>0.98762529884261907</v>
       </c>
       <c r="AB115">
-        <v>345.20127982451362</v>
+        <v>226.8695212186509</v>
       </c>
     </row>
     <row r="116" spans="2:28">
@@ -20633,16 +20633,16 @@
         <v>738</v>
       </c>
       <c r="Y116" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="Z116" t="s">
-        <v>783</v>
+        <v>793</v>
       </c>
       <c r="AA116">
-        <v>0.99395651765584936</v>
+        <v>0.97765910024833902</v>
       </c>
       <c r="AB116">
-        <v>110.79717630942883</v>
+        <v>409.58316211378531</v>
       </c>
     </row>
     <row r="117" spans="2:28">
@@ -20707,16 +20707,16 @@
         <v>740</v>
       </c>
       <c r="Y117" t="s">
-        <v>488</v>
+        <v>419</v>
       </c>
       <c r="Z117" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="AA117">
-        <v>0.98563153879963317</v>
+        <v>0.99660741093787208</v>
       </c>
       <c r="AB117">
-        <v>263.42178867339101</v>
+        <v>62.197466139011929</v>
       </c>
     </row>
     <row r="118" spans="2:28">
@@ -20781,16 +20781,16 @@
         <v>742</v>
       </c>
       <c r="Y118" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="Z118" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="AA118">
-        <v>0.99558181127270129</v>
+        <v>0.99755601192869059</v>
       </c>
       <c r="AB118">
-        <v>81.000126667143434</v>
+        <v>44.806447974006502</v>
       </c>
     </row>
     <row r="119" spans="2:28">
@@ -20855,16 +20855,16 @@
         <v>744</v>
       </c>
       <c r="Y119" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="Z119" t="s">
-        <v>772</v>
+        <v>826</v>
       </c>
       <c r="AA119">
-        <v>0.99476729801312358</v>
+        <v>0.9938212728279423</v>
       </c>
       <c r="AB119">
-        <v>95.932869759401342</v>
+        <v>113.27666482105715</v>
       </c>
     </row>
     <row r="120" spans="2:28">
@@ -20929,16 +20929,16 @@
         <v>746</v>
       </c>
       <c r="Y120" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="Z120" t="s">
-        <v>828</v>
+        <v>782</v>
       </c>
       <c r="AA120">
-        <v>0.99549647084304327</v>
+        <v>0.99529213309817555</v>
       </c>
       <c r="AB120">
-        <v>82.564701210872954</v>
+        <v>86.310893200114194</v>
       </c>
     </row>
     <row r="121" spans="2:28">
@@ -21003,16 +21003,16 @@
         <v>748</v>
       </c>
       <c r="Y121" t="s">
-        <v>517</v>
+        <v>469</v>
       </c>
       <c r="Z121" t="s">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="AA121">
-        <v>0.97432735774114165</v>
+        <v>0.99156696838886027</v>
       </c>
       <c r="AB121">
-        <v>470.66510807906917</v>
+        <v>154.60557953756208</v>
       </c>
     </row>
     <row r="122" spans="2:28">
@@ -21077,16 +21077,16 @@
         <v>750</v>
       </c>
       <c r="Y122" t="s">
-        <v>494</v>
+        <v>444</v>
       </c>
       <c r="Z122" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="AA122">
-        <v>0.98092062608337349</v>
+        <v>0.99401688555089329</v>
       </c>
       <c r="AB122">
-        <v>349.78852180481954</v>
+        <v>109.69043156695554</v>
       </c>
     </row>
     <row r="123" spans="2:28">
@@ -21151,16 +21151,16 @@
         <v>752</v>
       </c>
       <c r="Y123" t="s">
-        <v>410</v>
+        <v>453</v>
       </c>
       <c r="Z123" t="s">
-        <v>784</v>
+        <v>828</v>
       </c>
       <c r="AA123">
-        <v>0.99511502462858281</v>
+        <v>0.99519181845511939</v>
       </c>
       <c r="AB123">
-        <v>89.557881809315646</v>
+        <v>88.149994989478557</v>
       </c>
     </row>
     <row r="124" spans="2:28">
@@ -21225,16 +21225,16 @@
         <v>754</v>
       </c>
       <c r="Y124" t="s">
-        <v>411</v>
+        <v>452</v>
       </c>
       <c r="Z124" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AA124">
-        <v>0.99569496806116964</v>
+        <v>0.99559756506177444</v>
       </c>
       <c r="AB124">
-        <v>78.92558554522391</v>
+        <v>80.711307200801741</v>
       </c>
     </row>
     <row r="125" spans="2:28">
@@ -21299,16 +21299,16 @@
         <v>756</v>
       </c>
       <c r="Y125" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="Z125" t="s">
-        <v>787</v>
+        <v>830</v>
       </c>
       <c r="AA125">
-        <v>0.99324534320140812</v>
+        <v>0.99703099037584386</v>
       </c>
       <c r="AB125">
-        <v>123.83537464085195</v>
+        <v>54.431843109528238</v>
       </c>
     </row>
   </sheetData>
@@ -21317,7 +21317,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37159ED9-656A-4C7C-BE48-294B8B43BFBE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{164CC67A-1769-459E-BEDC-080DB62BC439}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -21429,7 +21429,7 @@
         <v>1157</v>
       </c>
       <c r="K11" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="L11">
         <v>10.563746678268352</v>
@@ -21462,7 +21462,7 @@
         <v>1295</v>
       </c>
       <c r="X11" t="s">
-        <v>1143</v>
+        <v>1131</v>
       </c>
       <c r="Y11">
         <v>54.979500000000002</v>
@@ -21497,7 +21497,7 @@
         <v>1159</v>
       </c>
       <c r="K12" t="s">
-        <v>1032</v>
+        <v>1048</v>
       </c>
       <c r="L12">
         <v>7.4816578037471135</v>
@@ -21530,7 +21530,7 @@
         <v>1297</v>
       </c>
       <c r="X12" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="Y12">
         <v>0.74099999999999999</v>
@@ -21565,7 +21565,7 @@
         <v>1161</v>
       </c>
       <c r="K13" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="L13">
         <v>4.7713910333636482</v>
@@ -21598,7 +21598,7 @@
         <v>1299</v>
       </c>
       <c r="X13" t="s">
-        <v>1127</v>
+        <v>1152</v>
       </c>
       <c r="Y13">
         <v>36.586500000000001</v>
@@ -21633,7 +21633,7 @@
         <v>1163</v>
       </c>
       <c r="K14" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="L14">
         <v>12.404103898825962</v>
@@ -21666,7 +21666,7 @@
         <v>1301</v>
       </c>
       <c r="X14" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="Y14">
         <v>53.094000000000001</v>
@@ -21701,7 +21701,7 @@
         <v>1165</v>
       </c>
       <c r="K15" t="s">
-        <v>1019</v>
+        <v>1029</v>
       </c>
       <c r="L15">
         <v>6.1276234637439133</v>
@@ -21734,7 +21734,7 @@
         <v>1303</v>
       </c>
       <c r="X15" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="Y15">
         <v>55.56</v>
@@ -21769,7 +21769,7 @@
         <v>1167</v>
       </c>
       <c r="K16" t="s">
-        <v>1056</v>
+        <v>998</v>
       </c>
       <c r="L16">
         <v>2.2195844391122765</v>
@@ -21802,7 +21802,7 @@
         <v>1305</v>
       </c>
       <c r="X16" t="s">
-        <v>1156</v>
+        <v>1122</v>
       </c>
       <c r="Y16">
         <v>43.858499999999999</v>
@@ -21837,7 +21837,7 @@
         <v>1169</v>
       </c>
       <c r="K17" t="s">
-        <v>990</v>
+        <v>1045</v>
       </c>
       <c r="L17">
         <v>3.7614311754340659</v>
@@ -21870,7 +21870,7 @@
         <v>1307</v>
       </c>
       <c r="X17" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="Y17">
         <v>42.080249999999999</v>
@@ -21905,7 +21905,7 @@
         <v>1171</v>
       </c>
       <c r="K18" t="s">
-        <v>1033</v>
+        <v>1049</v>
       </c>
       <c r="L18">
         <v>2.5051779960501728</v>
@@ -21938,7 +21938,7 @@
         <v>1309</v>
       </c>
       <c r="X18" t="s">
-        <v>1144</v>
+        <v>1156</v>
       </c>
       <c r="Y18">
         <v>19.922999999999998</v>
@@ -21973,7 +21973,7 @@
         <v>1173</v>
       </c>
       <c r="K19" t="s">
-        <v>1034</v>
+        <v>1050</v>
       </c>
       <c r="L19">
         <v>1.8110172385939969</v>
@@ -22006,7 +22006,7 @@
         <v>1311</v>
       </c>
       <c r="X19" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="Y19">
         <v>51.427500000000002</v>
@@ -22041,7 +22041,7 @@
         <v>1175</v>
       </c>
       <c r="K20" t="s">
-        <v>989</v>
+        <v>1044</v>
       </c>
       <c r="L20">
         <v>11.884376191048085</v>
@@ -22074,7 +22074,7 @@
         <v>1313</v>
       </c>
       <c r="X20" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="Y20">
         <v>40.677</v>
@@ -22109,7 +22109,7 @@
         <v>1177</v>
       </c>
       <c r="K21" t="s">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="L21">
         <v>12.246676572623375</v>
@@ -22142,7 +22142,7 @@
         <v>1315</v>
       </c>
       <c r="X21" t="s">
-        <v>1150</v>
+        <v>1123</v>
       </c>
       <c r="Y21">
         <v>60.146250000000002</v>
@@ -22177,7 +22177,7 @@
         <v>1179</v>
       </c>
       <c r="K22" t="s">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="L22">
         <v>10.179607104535382</v>
@@ -22210,7 +22210,7 @@
         <v>1317</v>
       </c>
       <c r="X22" t="s">
-        <v>1154</v>
+        <v>1137</v>
       </c>
       <c r="Y22">
         <v>39.273000000000003</v>
@@ -22245,7 +22245,7 @@
         <v>1181</v>
       </c>
       <c r="K23" t="s">
-        <v>1028</v>
+        <v>1058</v>
       </c>
       <c r="L23">
         <v>7.6463375414566821</v>
@@ -22278,7 +22278,7 @@
         <v>1319</v>
       </c>
       <c r="X23" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="Y23">
         <v>44.889749999999999</v>
@@ -22313,7 +22313,7 @@
         <v>1183</v>
       </c>
       <c r="K24" t="s">
-        <v>1036</v>
+        <v>1018</v>
       </c>
       <c r="L24">
         <v>48.571266974214375</v>
@@ -22346,7 +22346,7 @@
         <v>1321</v>
       </c>
       <c r="X24" t="s">
-        <v>1151</v>
+        <v>1124</v>
       </c>
       <c r="Y24">
         <v>27.66375</v>
@@ -22381,7 +22381,7 @@
         <v>1185</v>
       </c>
       <c r="K25" t="s">
-        <v>1007</v>
+        <v>1039</v>
       </c>
       <c r="L25">
         <v>1.6757541426674882</v>
@@ -22414,7 +22414,7 @@
         <v>1323</v>
       </c>
       <c r="X25" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="Y25">
         <v>21.581250000000001</v>
@@ -22449,7 +22449,7 @@
         <v>1187</v>
       </c>
       <c r="K26" t="s">
-        <v>1029</v>
+        <v>1059</v>
       </c>
       <c r="L26">
         <v>0.39959553615654331</v>
@@ -22482,7 +22482,7 @@
         <v>1325</v>
       </c>
       <c r="X26" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="Y26">
         <v>56.094749999999998</v>
@@ -22517,7 +22517,7 @@
         <v>1189</v>
       </c>
       <c r="K27" t="s">
-        <v>1002</v>
+        <v>985</v>
       </c>
       <c r="L27">
         <v>1.7832075556426605</v>
@@ -22550,7 +22550,7 @@
         <v>1327</v>
       </c>
       <c r="X27" t="s">
-        <v>1153</v>
+        <v>1136</v>
       </c>
       <c r="Y27">
         <v>43.631999999999998</v>
@@ -22585,7 +22585,7 @@
         <v>1191</v>
       </c>
       <c r="K28" t="s">
-        <v>977</v>
+        <v>1053</v>
       </c>
       <c r="L28">
         <v>0.35051099632091098</v>
@@ -22618,7 +22618,7 @@
         <v>1329</v>
       </c>
       <c r="X28" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="Y28">
         <v>3.4402499999999998</v>
@@ -22653,7 +22653,7 @@
         <v>1193</v>
       </c>
       <c r="K29" t="s">
-        <v>1045</v>
+        <v>1026</v>
       </c>
       <c r="L29">
         <v>5.5005105319204732</v>
@@ -22686,7 +22686,7 @@
         <v>1331</v>
       </c>
       <c r="X29" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="Y29">
         <v>13.389749999999999</v>
@@ -22721,7 +22721,7 @@
         <v>1195</v>
       </c>
       <c r="K30" t="s">
-        <v>994</v>
+        <v>970</v>
       </c>
       <c r="L30">
         <v>0.34625959029864795</v>
@@ -22754,7 +22754,7 @@
         <v>1333</v>
       </c>
       <c r="X30" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="Y30">
         <v>6.9757499999999997</v>
@@ -22789,7 +22789,7 @@
         <v>1197</v>
       </c>
       <c r="K31" t="s">
-        <v>1051</v>
+        <v>1014</v>
       </c>
       <c r="L31">
         <v>0.65440271382024695</v>
@@ -22822,7 +22822,7 @@
         <v>1335</v>
       </c>
       <c r="X31" t="s">
-        <v>1128</v>
+        <v>1153</v>
       </c>
       <c r="Y31">
         <v>38.154000000000003</v>
@@ -22857,7 +22857,7 @@
         <v>1199</v>
       </c>
       <c r="K32" t="s">
-        <v>991</v>
+        <v>1046</v>
       </c>
       <c r="L32">
         <v>0.5190595734350465</v>
@@ -22890,7 +22890,7 @@
         <v>1337</v>
       </c>
       <c r="X32" t="s">
-        <v>1152</v>
+        <v>1125</v>
       </c>
       <c r="Y32">
         <v>26.765999999999998</v>
@@ -22925,7 +22925,7 @@
         <v>1201</v>
       </c>
       <c r="K33" t="s">
-        <v>1057</v>
+        <v>999</v>
       </c>
       <c r="L33">
         <v>0.29505146981926272</v>
@@ -22958,7 +22958,7 @@
         <v>1339</v>
       </c>
       <c r="X33" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="Y33">
         <v>35.325000000000003</v>
@@ -22993,7 +22993,7 @@
         <v>1203</v>
       </c>
       <c r="K34" t="s">
-        <v>1055</v>
+        <v>996</v>
       </c>
       <c r="L34">
         <v>0.28737649325389003</v>
@@ -23026,7 +23026,7 @@
         <v>1341</v>
       </c>
       <c r="X34" t="s">
-        <v>1132</v>
+        <v>1142</v>
       </c>
       <c r="Y34">
         <v>38.589750000000002</v>
@@ -23061,7 +23061,7 @@
         <v>1205</v>
       </c>
       <c r="K35" t="s">
-        <v>1048</v>
+        <v>1011</v>
       </c>
       <c r="L35">
         <v>0.85621181691755843</v>
@@ -23094,7 +23094,7 @@
         <v>1343</v>
       </c>
       <c r="X35" t="s">
-        <v>1133</v>
+        <v>1143</v>
       </c>
       <c r="Y35">
         <v>28.707000000000001</v>
@@ -23129,7 +23129,7 @@
         <v>1207</v>
       </c>
       <c r="K36" t="s">
-        <v>1037</v>
+        <v>1019</v>
       </c>
       <c r="L36">
         <v>2.2628760328229185</v>
@@ -23162,7 +23162,7 @@
         <v>1345</v>
       </c>
       <c r="X36" t="s">
-        <v>1135</v>
+        <v>1145</v>
       </c>
       <c r="Y36">
         <v>2.6655000000000002</v>
@@ -23197,7 +23197,7 @@
         <v>1209</v>
       </c>
       <c r="K37" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="L37">
         <v>0.43370118574988076</v>
@@ -23230,7 +23230,7 @@
         <v>1347</v>
       </c>
       <c r="X37" t="s">
-        <v>1131</v>
+        <v>1155</v>
       </c>
       <c r="Y37">
         <v>11.651999999999999</v>
@@ -23265,7 +23265,7 @@
         <v>1211</v>
       </c>
       <c r="K38" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="L38">
         <v>2.5150267058852811</v>
@@ -23298,7 +23298,7 @@
         <v>1349</v>
       </c>
       <c r="X38" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="Y38">
         <v>10.619249999999999</v>
@@ -23333,7 +23333,7 @@
         <v>1213</v>
       </c>
       <c r="K39" t="s">
-        <v>1039</v>
+        <v>1021</v>
       </c>
       <c r="L39">
         <v>2.2677057834637031</v>
@@ -23366,7 +23366,7 @@
         <v>1351</v>
       </c>
       <c r="X39" t="s">
-        <v>1136</v>
+        <v>1146</v>
       </c>
       <c r="Y39">
         <v>21.260999999999999</v>
@@ -23401,7 +23401,7 @@
         <v>1215</v>
       </c>
       <c r="K40" t="s">
-        <v>1021</v>
+        <v>1031</v>
       </c>
       <c r="L40">
         <v>3.9696443596880591</v>
@@ -23434,7 +23434,7 @@
         <v>1353</v>
       </c>
       <c r="X40" t="s">
-        <v>1155</v>
+        <v>1138</v>
       </c>
       <c r="Y40">
         <v>1.7955000000000001</v>
@@ -23469,7 +23469,7 @@
         <v>1217</v>
       </c>
       <c r="K41" t="s">
-        <v>1050</v>
+        <v>1013</v>
       </c>
       <c r="L41">
         <v>2.4836923620575391</v>
@@ -23502,7 +23502,7 @@
         <v>1355</v>
       </c>
       <c r="X41" t="s">
-        <v>1129</v>
+        <v>1154</v>
       </c>
       <c r="Y41">
         <v>26.880749999999999</v>
@@ -23537,7 +23537,7 @@
         <v>1219</v>
       </c>
       <c r="K42" t="s">
-        <v>993</v>
+        <v>969</v>
       </c>
       <c r="L42">
         <v>2.885493974180005</v>
@@ -23572,7 +23572,7 @@
         <v>1221</v>
       </c>
       <c r="K43" t="s">
-        <v>1006</v>
+        <v>1038</v>
       </c>
       <c r="L43">
         <v>4.0763322608214585</v>
@@ -23607,7 +23607,7 @@
         <v>1223</v>
       </c>
       <c r="K44" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="L44">
         <v>18.379523073310825</v>
@@ -23642,7 +23642,7 @@
         <v>1225</v>
       </c>
       <c r="K45" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="L45">
         <v>1.4999429400795936</v>
@@ -23677,7 +23677,7 @@
         <v>1227</v>
       </c>
       <c r="K46" t="s">
-        <v>1046</v>
+        <v>1027</v>
       </c>
       <c r="L46">
         <v>51.336595002990194</v>
@@ -23712,7 +23712,7 @@
         <v>1229</v>
       </c>
       <c r="K47" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
       <c r="L47">
         <v>16.978804920122926</v>
@@ -23747,7 +23747,7 @@
         <v>1231</v>
       </c>
       <c r="K48" t="s">
-        <v>1005</v>
+        <v>988</v>
       </c>
       <c r="L48">
         <v>12.678684297219551</v>
@@ -23782,7 +23782,7 @@
         <v>1233</v>
       </c>
       <c r="K49" t="s">
-        <v>1059</v>
+        <v>1002</v>
       </c>
       <c r="L49">
         <v>3.0756142181007986</v>
@@ -23817,7 +23817,7 @@
         <v>1235</v>
       </c>
       <c r="K50" t="s">
-        <v>1000</v>
+        <v>976</v>
       </c>
       <c r="L50">
         <v>17.749707845203876</v>
@@ -23852,7 +23852,7 @@
         <v>1237</v>
       </c>
       <c r="K51" t="s">
-        <v>971</v>
+        <v>980</v>
       </c>
       <c r="L51">
         <v>2.3372365278937242</v>
@@ -23887,7 +23887,7 @@
         <v>1239</v>
       </c>
       <c r="K52" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="L52">
         <v>4.2648673086521249</v>
@@ -23922,7 +23922,7 @@
         <v>1241</v>
       </c>
       <c r="K53" t="s">
-        <v>981</v>
+        <v>1043</v>
       </c>
       <c r="L53">
         <v>2.462861606818517</v>
@@ -23957,7 +23957,7 @@
         <v>1243</v>
       </c>
       <c r="K54" t="s">
-        <v>1031</v>
+        <v>1057</v>
       </c>
       <c r="L54">
         <v>9.435033539909309</v>
@@ -23992,7 +23992,7 @@
         <v>1245</v>
       </c>
       <c r="K55" t="s">
-        <v>998</v>
+        <v>974</v>
       </c>
       <c r="L55">
         <v>26.420384248371558</v>
@@ -24027,7 +24027,7 @@
         <v>1247</v>
       </c>
       <c r="K56" t="s">
-        <v>1054</v>
+        <v>1017</v>
       </c>
       <c r="L56">
         <v>18.510958868579117</v>
@@ -24062,7 +24062,7 @@
         <v>1249</v>
       </c>
       <c r="K57" t="s">
-        <v>1025</v>
+        <v>1035</v>
       </c>
       <c r="L57">
         <v>15.228130347836801</v>
@@ -24097,7 +24097,7 @@
         <v>1251</v>
       </c>
       <c r="K58" t="s">
-        <v>976</v>
+        <v>1052</v>
       </c>
       <c r="L58">
         <v>14.176079891703212</v>
@@ -24132,7 +24132,7 @@
         <v>1253</v>
       </c>
       <c r="K59" t="s">
-        <v>1030</v>
+        <v>1056</v>
       </c>
       <c r="L59">
         <v>0.80973624203950822</v>
@@ -24167,7 +24167,7 @@
         <v>1255</v>
       </c>
       <c r="K60" t="s">
-        <v>975</v>
+        <v>984</v>
       </c>
       <c r="L60">
         <v>3.2067222321080848</v>
@@ -24202,7 +24202,7 @@
         <v>1257</v>
       </c>
       <c r="K61" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="L61">
         <v>0.66271354737797783</v>
@@ -24237,7 +24237,7 @@
         <v>1259</v>
       </c>
       <c r="K62" t="s">
-        <v>979</v>
+        <v>1055</v>
       </c>
       <c r="L62">
         <v>1.8096926976599874</v>
@@ -24272,7 +24272,7 @@
         <v>1261</v>
       </c>
       <c r="K63" t="s">
-        <v>973</v>
+        <v>982</v>
       </c>
       <c r="L63">
         <v>0.23974319237866104</v>
@@ -24307,7 +24307,7 @@
         <v>1263</v>
       </c>
       <c r="K64" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="L64">
         <v>8.2047875916663029E-2</v>
@@ -24342,7 +24342,7 @@
         <v>1265</v>
       </c>
       <c r="K65" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="L65">
         <v>11.861012832193515</v>
@@ -24377,7 +24377,7 @@
         <v>1267</v>
       </c>
       <c r="K66" t="s">
-        <v>1052</v>
+        <v>1015</v>
       </c>
       <c r="L66">
         <v>0.74143826937354373</v>
@@ -24412,7 +24412,7 @@
         <v>1269</v>
       </c>
       <c r="K67" t="s">
-        <v>996</v>
+        <v>972</v>
       </c>
       <c r="L67">
         <v>5.5201095579611916</v>
@@ -24447,7 +24447,7 @@
         <v>1271</v>
       </c>
       <c r="K68" t="s">
-        <v>1043</v>
+        <v>1025</v>
       </c>
       <c r="L68">
         <v>6.8285247240880329</v>
@@ -24482,7 +24482,7 @@
         <v>1273</v>
       </c>
       <c r="K69" t="s">
-        <v>1003</v>
+        <v>986</v>
       </c>
       <c r="L69">
         <v>14.065249575687433</v>
@@ -24517,7 +24517,7 @@
         <v>1275</v>
       </c>
       <c r="K70" t="s">
-        <v>980</v>
+        <v>1042</v>
       </c>
       <c r="L70">
         <v>9.3799037679336319</v>
@@ -24552,7 +24552,7 @@
         <v>1277</v>
       </c>
       <c r="K71" t="s">
-        <v>1058</v>
+        <v>1000</v>
       </c>
       <c r="L71">
         <v>39.014264277919466</v>
@@ -24587,7 +24587,7 @@
         <v>1279</v>
       </c>
       <c r="K72" t="s">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="L72">
         <v>7.8693705940085819</v>
@@ -24622,7 +24622,7 @@
         <v>1281</v>
       </c>
       <c r="K73" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="L73">
         <v>19.787589902082505</v>
@@ -24657,7 +24657,7 @@
         <v>1283</v>
       </c>
       <c r="K74" t="s">
-        <v>1035</v>
+        <v>1051</v>
       </c>
       <c r="L74">
         <v>18.319832830101969</v>
@@ -24692,7 +24692,7 @@
         <v>1285</v>
       </c>
       <c r="K75" t="s">
-        <v>1053</v>
+        <v>1016</v>
       </c>
       <c r="L75">
         <v>6.6426756478058007</v>
@@ -24727,7 +24727,7 @@
         <v>1287</v>
       </c>
       <c r="K76" t="s">
-        <v>1023</v>
+        <v>1033</v>
       </c>
       <c r="L76">
         <v>0.78969451031655336</v>
@@ -24762,7 +24762,7 @@
         <v>1289</v>
       </c>
       <c r="K77" t="s">
-        <v>1008</v>
+        <v>1040</v>
       </c>
       <c r="L77">
         <v>3.5275797249830152</v>
@@ -24797,7 +24797,7 @@
         <v>1291</v>
       </c>
       <c r="K78" t="s">
-        <v>1040</v>
+        <v>1022</v>
       </c>
       <c r="L78">
         <v>0.89663971235601181</v>
@@ -24832,7 +24832,7 @@
         <v>1293</v>
       </c>
       <c r="K79" t="s">
-        <v>1041</v>
+        <v>1023</v>
       </c>
       <c r="L79">
         <v>5.9305458091691294</v>
@@ -24847,7 +24847,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039E6A45-3F64-4C89-85F4-F7D97D6CB733}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F270A5-73B1-474E-B9E4-9A8001C4CE84}">
   <dimension ref="B9:S120"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C1ED26B-EB79-46C9-B489-636B32A6FDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6831B280-D3D1-4746-B087-8D3F83798057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1707,18 +1707,138 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_BRA_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_111</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_099</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 99</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_102</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 102</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_BRA_091</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 91</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_BRA_020</t>
   </si>
   <si>
@@ -1767,6 +1887,450 @@
     <t>connecting solar to buses in cluster 42</t>
   </si>
   <si>
+    <t>distr_solelc_spv_BRA_114</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 114</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_115</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 115</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_101</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 101</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_113</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 113</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_108</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_103</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 103</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_109</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 109</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_106</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 106</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_096</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BRA_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_BRA_112</t>
   </si>
   <si>
@@ -1839,579 +2403,69 @@
     <t>connecting solar to buses in cluster 47</t>
   </si>
   <si>
-    <t>distr_solelc_spv_BRA_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_109</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 109</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_115</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 115</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_114</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 114</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_110</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 110</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_101</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 101</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_108</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_106</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 106</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_096</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_113</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 113</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_103</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 103</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_111</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 111</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_099</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 99</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_102</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 102</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BRA_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w466973262-525_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA,e_BR435-500_BRA,e_BR485-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR485-500_BRA,e_w537470701-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w954122148-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR273-230_BRA</t>
+  </si>
+  <si>
     <t>e_BR21-500_BRA</t>
   </si>
   <si>
+    <t>e_BR273-230_BRA,e_BR357-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR357-500_BRA,e_BR273-230_BRA,e_BR487-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w32300871-500_BRA,e_w466973262-525_BRA</t>
+  </si>
+  <si>
+    <t>e_BR21-500_BRA,e_w515552863-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w188465343-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w537470701-500_BRA,e_w202622375-765_BRA</t>
+  </si>
+  <si>
+    <t>e_BR435-500_BRA,e_w271191830-500_BRA,e_BR254-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR141-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR141-500_BRA,e_BR72-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w954122148-500_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR254-500_BRA,e_BR282-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR282-500_BRA,e_BR148-500_BRA,e_BR204-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR282-500_BRA,e_BR204-500_BRA,e_BR148-500_BRA</t>
+  </si>
+  <si>
     <t>e_BR357-500_BRA,e_BR487-500_BRA</t>
   </si>
   <si>
@@ -2433,10 +2487,127 @@
     <t>e_w954122148-500_BRA,e_BR669-500_BRA,e_BR282-500_BRA</t>
   </si>
   <si>
-    <t>e_BR273-230_BRA</t>
-  </si>
-  <si>
-    <t>e_BR273-230_BRA,e_BR357-500_BRA</t>
+    <t>e_BR273-230_BRA,e_BR21-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR357-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR254-500_BRA,e_BR141-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR580-500_BRA,e_w954122148-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA,e_BR357-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA,e_w537470701-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w188465343-500_BRA,e_w125761912-500_BRA,e_w202622375-765_BRA</t>
+  </si>
+  <si>
+    <t>e_w188465343-500_BRA,e_w202622375-765_BRA</t>
+  </si>
+  <si>
+    <t>e_BR141-500_BRA,e_w271191830-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w32300871-500_BRA,e_BR357-500_BRA,e_BR487-500_BRA,e_w125761912-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA,e_BR357-500_BRA,e_w125761912-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w202622375-765_BRA,e_w537470701-500_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR435-500_BRA,e_BR254-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR72-500_BRA,e_BR148-500_BRA,e_BR282-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w32300871-500_BRA,e_w466973262-525_BRA,e_w188465343-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w537470701-500_BRA,e_BR580-500_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w954122148-500_BRA,e_BR485-500_BRA,e_BR580-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR669-500_BRA,e_BR580-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w954122148-500_BRA,e_BR254-500_BRA,e_BR282-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w32300871-500_BRA,e_w125761912-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w537470701-500_BRA,e_BR580-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR21-500_BRA,e_BR357-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w202622375-765_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR580-500_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w125761912-500_BRA,e_w537470701-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w466973262-525_BRA,e_w188465343-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w125761912-500_BRA,e_w202622375-765_BRA,e_w537470701-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w271191830-500_BRA,e_BR141-500_BRA,e_BR254-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR669-500_BRA,e_w954122148-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR282-500_BRA,e_BR204-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR21-500_BRA,e_BR273-230_BRA</t>
+  </si>
+  <si>
+    <t>e_w188465343-500_BRA,e_w466973262-525_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA,e_BR357-500_BRA,e_BR435-500_BRA,e_w271191830-500_BRA</t>
+  </si>
+  <si>
+    <t>e_w515552863-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR141-500_BRA,e_BR72-500_BRA,e_BR254-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR254-500_BRA,e_w954122148-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR254-500_BRA,e_BR72-500_BRA,e_BR282-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR487-500_BRA,e_w537470701-500_BRA,e_BR485-500_BRA</t>
+  </si>
+  <si>
+    <t>e_BR435-500_BRA,e_w271191830-500_BRA</t>
   </si>
   <si>
     <t>e_w32300871-500_BRA,e_w188465343-500_BRA,e_w125761912-500_BRA</t>
@@ -2445,181 +2616,256 @@
     <t>e_w515552863-500_BRA,e_BR357-500_BRA,e_BR141-500_BRA</t>
   </si>
   <si>
-    <t>e_BR487-500_BRA,e_w537470701-500_BRA</t>
-  </si>
-  <si>
     <t>e_BR141-500_BRA,e_w515552863-500_BRA</t>
   </si>
   <si>
     <t>e_BR282-500_BRA,e_BR254-500_BRA</t>
   </si>
   <si>
-    <t>e_w466973262-525_BRA</t>
-  </si>
-  <si>
-    <t>e_BR487-500_BRA,e_BR435-500_BRA,e_BR485-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR485-500_BRA,e_w537470701-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w954122148-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR21-500_BRA,e_BR273-230_BRA</t>
-  </si>
-  <si>
-    <t>e_w188465343-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w188465343-500_BRA,e_w466973262-525_BRA</t>
-  </si>
-  <si>
-    <t>e_BR141-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR141-500_BRA,e_w271191830-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR580-500_BRA,e_w954122148-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR273-230_BRA,e_BR21-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR357-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR254-500_BRA,e_BR141-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w32300871-500_BRA,e_w466973262-525_BRA,e_w188465343-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR487-500_BRA,e_BR357-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w188465343-500_BRA,e_w202622375-765_BRA</t>
-  </si>
-  <si>
-    <t>e_w537470701-500_BRA,e_BR580-500_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR21-500_BRA,e_BR357-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR21-500_BRA,e_w515552863-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w202622375-765_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR580-500_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w954122148-500_BRA,e_BR485-500_BRA,e_BR580-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR141-500_BRA,e_BR72-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR669-500_BRA,e_BR580-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w954122148-500_BRA,e_BR254-500_BRA,e_BR282-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w125761912-500_BRA,e_w537470701-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR487-500_BRA,e_w537470701-500_BRA,e_BR485-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR435-500_BRA,e_w271191830-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR487-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w188465343-500_BRA,e_w125761912-500_BRA,e_w202622375-765_BRA</t>
-  </si>
-  <si>
-    <t>e_w32300871-500_BRA,e_w125761912-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w537470701-500_BRA,e_BR580-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR487-500_BRA,e_BR357-500_BRA,e_BR435-500_BRA,e_w271191830-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w515552863-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR141-500_BRA,e_BR72-500_BRA,e_BR254-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR254-500_BRA,e_w954122148-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR254-500_BRA,e_BR72-500_BRA,e_BR282-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w466973262-525_BRA,e_w188465343-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w125761912-500_BRA,e_w202622375-765_BRA,e_w537470701-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w271191830-500_BRA,e_BR141-500_BRA,e_BR254-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR669-500_BRA,e_w954122148-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR282-500_BRA,e_BR204-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w32300871-500_BRA,e_BR357-500_BRA,e_BR487-500_BRA,e_w125761912-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR487-500_BRA,e_BR357-500_BRA,e_w125761912-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w202622375-765_BRA,e_w537470701-500_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR435-500_BRA,e_BR254-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR72-500_BRA,e_BR148-500_BRA,e_BR282-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR357-500_BRA,e_BR273-230_BRA,e_BR487-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w32300871-500_BRA,e_w466973262-525_BRA</t>
-  </si>
-  <si>
-    <t>e_w537470701-500_BRA,e_w202622375-765_BRA</t>
-  </si>
-  <si>
-    <t>e_BR435-500_BRA,e_w271191830-500_BRA,e_BR254-500_BRA</t>
-  </si>
-  <si>
-    <t>e_w954122148-500_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR254-500_BRA,e_BR282-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR282-500_BRA,e_BR148-500_BRA,e_BR204-500_BRA</t>
-  </si>
-  <si>
-    <t>e_BR282-500_BRA,e_BR204-500_BRA,e_BR148-500_BRA</t>
+    <t>distr_wonelc_won_BRA_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
   </si>
   <si>
     <t>distr_wonelc_won_BRA_032</t>
@@ -2652,52 +2898,112 @@
     <t>connecting wind onshore to buses in cluster 40</t>
   </si>
   <si>
-    <t>distr_wonelc_won_BRA_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
+    <t>distr_wonelc_won_BRA_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BRA_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
   </si>
   <si>
     <t>distr_wonelc_won_BRA_003</t>
@@ -2730,310 +3036,166 @@
     <t>connecting wind onshore to buses in cluster 34</t>
   </si>
   <si>
-    <t>distr_wonelc_won_BRA_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BRA_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
+    <t>elc_won_BRA_025</t>
+  </si>
+  <si>
+    <t>e_w125761912-500_BRA,e_BR487-500_BRA,e_w537470701-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_031</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_021</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_056</t>
+  </si>
+  <si>
+    <t>e_BR435-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_065</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_046</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_005</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_012</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_030</t>
+  </si>
+  <si>
+    <t>e_w32300871-500_BRA,e_w125761912-500_BRA,e_w188465343-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_066</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_037</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_047</t>
+  </si>
+  <si>
+    <t>e_BR72-500_BRA,e_BR254-500_BRA,e_BR148-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_051</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_014</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_026</t>
+  </si>
+  <si>
+    <t>e_w125761912-500_BRA,e_w537470701-500_BRA,e_BR487-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_029</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_068</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_069</t>
+  </si>
+  <si>
+    <t>e_BR485-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_058</t>
+  </si>
+  <si>
+    <t>e_BR254-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_019</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_036</t>
+  </si>
+  <si>
+    <t>e_BR254-500_BRA,e_BR282-500_BRA,e_BR204-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_017</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_059</t>
+  </si>
+  <si>
+    <t>e_BR254-500_BRA,e_BR72-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_038</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_060</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_043</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_010</t>
+  </si>
+  <si>
+    <t>e_w32300871-500_BRA,e_w188465343-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_007</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_022</t>
+  </si>
+  <si>
+    <t>e_w537470701-500_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_013</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_016</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_011</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_041</t>
+  </si>
+  <si>
+    <t>e_BR21-500_BRA,e_w515552863-500_BRA,e_BR141-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_053</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_054</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_050</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_048</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_018</t>
+  </si>
+  <si>
+    <t>e_BR580-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_052</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_049</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_044</t>
   </si>
   <si>
     <t>elc_won_BRA_032</t>
@@ -3048,9 +3210,6 @@
     <t>elc_won_BRA_057</t>
   </si>
   <si>
-    <t>e_BR435-500_BRA</t>
-  </si>
-  <si>
     <t>elc_won_BRA_045</t>
   </si>
   <si>
@@ -3063,37 +3222,70 @@
     <t>e_BR282-500_BRA</t>
   </si>
   <si>
-    <t>elc_won_BRA_011</t>
-  </si>
-  <si>
-    <t>e_w32300871-500_BRA,e_w188465343-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_041</t>
-  </si>
-  <si>
-    <t>e_BR21-500_BRA,e_w515552863-500_BRA,e_BR141-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_053</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_054</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_050</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_017</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_059</t>
-  </si>
-  <si>
-    <t>e_BR254-500_BRA,e_BR72-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_038</t>
+    <t>elc_won_BRA_004</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_028</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_027</t>
+  </si>
+  <si>
+    <t>e_w537470701-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_063</t>
+  </si>
+  <si>
+    <t>e_BR485-500_BRA,e_BR435-500_BRA,e_w954122148-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_062</t>
+  </si>
+  <si>
+    <t>e_w954122148-500_BRA,e_BR485-500_BRA,e_BR435-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_035</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_002</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_008</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_009</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_064</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_024</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_006</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_023</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_061</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_039</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_033</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_015</t>
+  </si>
+  <si>
+    <t>elc_won_BRA_067</t>
+  </si>
+  <si>
+    <t>e_w537470701-500_BRA,e_BR485-500_BRA,e_BR580-500_BRA,e_BR669-500_BRA</t>
   </si>
   <si>
     <t>elc_won_BRA_003</t>
@@ -3117,196 +3309,184 @@
     <t>e_w954122148-500_BRA,e_BR254-500_BRA</t>
   </si>
   <si>
-    <t>elc_won_BRA_024</t>
-  </si>
-  <si>
-    <t>e_w537470701-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_006</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_023</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_061</t>
-  </si>
-  <si>
-    <t>e_BR254-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_039</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_004</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_028</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_027</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_063</t>
-  </si>
-  <si>
-    <t>e_BR485-500_BRA,e_BR435-500_BRA,e_w954122148-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_062</t>
-  </si>
-  <si>
-    <t>e_w954122148-500_BRA,e_BR485-500_BRA,e_BR435-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_035</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_025</t>
-  </si>
-  <si>
-    <t>e_w125761912-500_BRA,e_BR487-500_BRA,e_w537470701-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_031</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_021</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_056</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_065</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_046</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_014</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_026</t>
-  </si>
-  <si>
-    <t>e_w125761912-500_BRA,e_w537470701-500_BRA,e_BR487-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_029</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_068</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_069</t>
-  </si>
-  <si>
-    <t>e_BR485-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_058</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_019</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_036</t>
-  </si>
-  <si>
-    <t>e_BR254-500_BRA,e_BR282-500_BRA,e_BR204-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_005</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_012</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_030</t>
-  </si>
-  <si>
-    <t>e_w32300871-500_BRA,e_w125761912-500_BRA,e_w188465343-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_066</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_037</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_047</t>
-  </si>
-  <si>
-    <t>e_BR72-500_BRA,e_BR254-500_BRA,e_BR148-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_051</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_033</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_015</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_067</t>
-  </si>
-  <si>
-    <t>e_w537470701-500_BRA,e_BR485-500_BRA,e_BR580-500_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_060</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_043</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_010</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_007</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_022</t>
-  </si>
-  <si>
-    <t>e_w537470701-500_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_002</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_008</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_009</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_064</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_048</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_018</t>
-  </si>
-  <si>
-    <t>e_BR580-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_052</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_049</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_044</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_013</t>
-  </si>
-  <si>
-    <t>elc_won_BRA_016</t>
+    <t>distr_wofelc_wof_BRA_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_BRA_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_BRA_006</t>
@@ -3315,289 +3495,109 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_BRA_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_BRA_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
+    <t>elc_wof_BRA_008</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_005</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_015</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_007</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_028</t>
+  </si>
+  <si>
+    <t>e_BR204-500_BRA,e_BR148-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_024</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_025</t>
+  </si>
+  <si>
+    <t>e_BR72-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_026</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_016</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_009</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_020</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_019</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_029</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_003</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_021</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_031</t>
+  </si>
+  <si>
+    <t>e_BR148-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_027</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_017</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_012</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_030</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_011</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_014</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_022</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_004</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_013</t>
+  </si>
+  <si>
+    <t>e_w188465343-500_BRA,e_BR669-500_BRA</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_023</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_018</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_002</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_010</t>
+  </si>
+  <si>
+    <t>elc_wof_BRA_001</t>
   </si>
   <si>
     <t>elc_wof_BRA_006</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_011</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_014</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_022</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_005</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_015</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_007</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_028</t>
-  </si>
-  <si>
-    <t>e_BR204-500_BRA,e_BR148-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_001</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_016</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_009</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_020</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_019</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_017</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_012</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_030</t>
-  </si>
-  <si>
-    <t>e_BR148-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_023</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_018</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_024</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_025</t>
-  </si>
-  <si>
-    <t>e_BR72-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_026</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_029</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_002</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_010</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_004</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_013</t>
-  </si>
-  <si>
-    <t>e_w188465343-500_BRA,e_BR669-500_BRA</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_003</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_021</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_031</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_027</t>
-  </si>
-  <si>
-    <t>elc_wof_BRA_008</t>
   </si>
   <si>
     <t>e_won_BRA_001</t>
@@ -9025,7 +9025,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11ACA86D-CB5A-4FBF-A51B-700F06B5D5AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846A9BF0-C15F-4EA8-B2B7-14832C5F1324}">
   <dimension ref="B9:BD125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9263,16 +9263,16 @@
         <v>526</v>
       </c>
       <c r="Y11" t="s">
-        <v>499</v>
+        <v>412</v>
       </c>
       <c r="Z11" t="s">
         <v>760</v>
       </c>
       <c r="AA11">
-        <v>0.99097794398489747</v>
+        <v>0.99634407688349669</v>
       </c>
       <c r="AB11">
-        <v>165.40436027688003</v>
+        <v>67.025257135894208</v>
       </c>
       <c r="AD11" t="s">
         <v>525</v>
@@ -9302,13 +9302,13 @@
         <v>969</v>
       </c>
       <c r="AN11" t="s">
-        <v>805</v>
+        <v>970</v>
       </c>
       <c r="AO11">
-        <v>0.98674094240398891</v>
+        <v>0.97651207122624506</v>
       </c>
       <c r="AP11">
-        <v>243.0827225935364</v>
+        <v>430.61202751883985</v>
       </c>
       <c r="AR11" t="s">
         <v>525</v>
@@ -9338,13 +9338,13 @@
         <v>1122</v>
       </c>
       <c r="BB11" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="BC11">
-        <v>0.99314574070258299</v>
+        <v>0.9959052853503485</v>
       </c>
       <c r="BD11">
-        <v>125.66142045264445</v>
+        <v>75.06976857694373</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -9409,16 +9409,16 @@
         <v>530</v>
       </c>
       <c r="Y12" t="s">
-        <v>428</v>
+        <v>471</v>
       </c>
       <c r="Z12" t="s">
         <v>761</v>
       </c>
       <c r="AA12">
-        <v>0.9921953803896254</v>
+        <v>0.9882785445805562</v>
       </c>
       <c r="AB12">
-        <v>143.08469285686789</v>
+        <v>214.89334935647034</v>
       </c>
       <c r="AD12" t="s">
         <v>525</v>
@@ -9445,16 +9445,16 @@
         <v>833</v>
       </c>
       <c r="AM12" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="AN12" t="s">
-        <v>971</v>
+        <v>806</v>
       </c>
       <c r="AO12">
-        <v>0.99776894175014486</v>
+        <v>0.99620534810300254</v>
       </c>
       <c r="AP12">
-        <v>40.90273458067751</v>
+        <v>69.568618111619969</v>
       </c>
       <c r="AR12" t="s">
         <v>525</v>
@@ -9484,13 +9484,13 @@
         <v>1123</v>
       </c>
       <c r="BB12" t="s">
-        <v>780</v>
+        <v>813</v>
       </c>
       <c r="BC12">
-        <v>0.99098965084511315</v>
+        <v>0.99203097418485064</v>
       </c>
       <c r="BD12">
-        <v>165.18973450625904</v>
+        <v>146.09880661107059</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -9555,16 +9555,16 @@
         <v>532</v>
       </c>
       <c r="Y13" t="s">
-        <v>497</v>
+        <v>441</v>
       </c>
       <c r="Z13" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="AA13">
-        <v>0.99299284379308983</v>
+        <v>0.99633066933811909</v>
       </c>
       <c r="AB13">
-        <v>128.46453046001977</v>
+        <v>67.271062134483344</v>
       </c>
       <c r="AD13" t="s">
         <v>525</v>
@@ -9594,13 +9594,13 @@
         <v>972</v>
       </c>
       <c r="AN13" t="s">
-        <v>973</v>
+        <v>812</v>
       </c>
       <c r="AO13">
-        <v>0.99374536027070226</v>
+        <v>0.99503039970536677</v>
       </c>
       <c r="AP13">
-        <v>114.668395037126</v>
+        <v>91.109338734942796</v>
       </c>
       <c r="AR13" t="s">
         <v>525</v>
@@ -9630,13 +9630,13 @@
         <v>1124</v>
       </c>
       <c r="BB13" t="s">
-        <v>790</v>
+        <v>770</v>
       </c>
       <c r="BC13">
-        <v>0.99053278045305837</v>
+        <v>0.99481196273061234</v>
       </c>
       <c r="BD13">
-        <v>173.56569169392964</v>
+        <v>95.114016605440895</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -9701,16 +9701,16 @@
         <v>534</v>
       </c>
       <c r="Y14" t="s">
-        <v>477</v>
+        <v>449</v>
       </c>
       <c r="Z14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AA14">
-        <v>0.97540090374045474</v>
+        <v>0.99497952870756723</v>
       </c>
       <c r="AB14">
-        <v>450.98343142499687</v>
+        <v>92.041973694600031</v>
       </c>
       <c r="AD14" t="s">
         <v>525</v>
@@ -9737,16 +9737,16 @@
         <v>837</v>
       </c>
       <c r="AM14" t="s">
+        <v>973</v>
+      </c>
+      <c r="AN14" t="s">
         <v>974</v>
       </c>
-      <c r="AN14" t="s">
-        <v>975</v>
-      </c>
       <c r="AO14">
-        <v>0.99733068647604728</v>
+        <v>0.99648541839873139</v>
       </c>
       <c r="AP14">
-        <v>48.937414605800647</v>
+        <v>64.433996023258757</v>
       </c>
       <c r="AR14" t="s">
         <v>525</v>
@@ -9776,13 +9776,13 @@
         <v>1125</v>
       </c>
       <c r="BB14" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="BC14">
-        <v>0.99420451954813838</v>
+        <v>0.98775115723917273</v>
       </c>
       <c r="BD14">
-        <v>106.25047495079694</v>
+        <v>224.56211728183334</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9847,16 +9847,16 @@
         <v>536</v>
       </c>
       <c r="Y15" t="s">
-        <v>417</v>
+        <v>519</v>
       </c>
       <c r="Z15" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AA15">
-        <v>0.99658165567225754</v>
+        <v>0.98823673546715696</v>
       </c>
       <c r="AB15">
-        <v>62.669646008611245</v>
+        <v>215.65984976878829</v>
       </c>
       <c r="AD15" t="s">
         <v>525</v>
@@ -9883,16 +9883,16 @@
         <v>839</v>
       </c>
       <c r="AM15" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="AN15" t="s">
-        <v>977</v>
+        <v>784</v>
       </c>
       <c r="AO15">
-        <v>0.99671693937496686</v>
+        <v>0.99681149341412811</v>
       </c>
       <c r="AP15">
-        <v>60.189444792275019</v>
+        <v>58.455954074317894</v>
       </c>
       <c r="AR15" t="s">
         <v>525</v>
@@ -9922,13 +9922,13 @@
         <v>1126</v>
       </c>
       <c r="BB15" t="s">
-        <v>813</v>
+        <v>1127</v>
       </c>
       <c r="BC15">
-        <v>0.99203097418485064</v>
+        <v>0.99538398111052984</v>
       </c>
       <c r="BD15">
-        <v>146.09880661107059</v>
+        <v>84.627012973619784</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9993,16 +9993,16 @@
         <v>538</v>
       </c>
       <c r="Y16" t="s">
-        <v>440</v>
+        <v>503</v>
       </c>
       <c r="Z16" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AA16">
-        <v>0.99587193000843988</v>
+        <v>0.96316770855847034</v>
       </c>
       <c r="AB16">
-        <v>75.681283178602214</v>
+        <v>675.25867642804383</v>
       </c>
       <c r="AD16" t="s">
         <v>525</v>
@@ -10029,16 +10029,16 @@
         <v>841</v>
       </c>
       <c r="AM16" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="AN16" t="s">
-        <v>979</v>
+        <v>777</v>
       </c>
       <c r="AO16">
-        <v>0.99473480482648013</v>
+        <v>0.99641899952784574</v>
       </c>
       <c r="AP16">
-        <v>96.528578181196991</v>
+        <v>65.65167532282868</v>
       </c>
       <c r="AR16" t="s">
         <v>525</v>
@@ -10065,16 +10065,16 @@
         <v>1070</v>
       </c>
       <c r="BA16" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="BB16" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="BC16">
-        <v>0.99481196273061234</v>
+        <v>0.98027195861782945</v>
       </c>
       <c r="BD16">
-        <v>95.114016605440895</v>
+        <v>361.68075867312689</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -10139,16 +10139,16 @@
         <v>540</v>
       </c>
       <c r="Y17" t="s">
-        <v>457</v>
+        <v>507</v>
       </c>
       <c r="Z17" t="s">
         <v>765</v>
       </c>
       <c r="AA17">
-        <v>0.9946890792776012</v>
+        <v>0.97244982574001193</v>
       </c>
       <c r="AB17">
-        <v>97.3668799106444</v>
+        <v>505.08652809978111</v>
       </c>
       <c r="AD17" t="s">
         <v>525</v>
@@ -10175,16 +10175,16 @@
         <v>843</v>
       </c>
       <c r="AM17" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="AN17" t="s">
-        <v>981</v>
+        <v>779</v>
       </c>
       <c r="AO17">
-        <v>0.98589595763902149</v>
+        <v>0.98599828568941739</v>
       </c>
       <c r="AP17">
-        <v>258.57410995127316</v>
+        <v>256.69809569401372</v>
       </c>
       <c r="AR17" t="s">
         <v>525</v>
@@ -10211,16 +10211,16 @@
         <v>1072</v>
       </c>
       <c r="BA17" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="BB17" t="s">
-        <v>807</v>
+        <v>1130</v>
       </c>
       <c r="BC17">
-        <v>0.98775115723917273</v>
+        <v>0.98488330873784669</v>
       </c>
       <c r="BD17">
-        <v>224.56211728183334</v>
+        <v>277.13933980614473</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -10285,16 +10285,16 @@
         <v>542</v>
       </c>
       <c r="Y18" t="s">
-        <v>458</v>
+        <v>495</v>
       </c>
       <c r="Z18" t="s">
         <v>766</v>
       </c>
       <c r="AA18">
-        <v>0.99318647897745582</v>
+        <v>0.97762911532019692</v>
       </c>
       <c r="AB18">
-        <v>124.91455207997609</v>
+        <v>410.13288579638987</v>
       </c>
       <c r="AD18" t="s">
         <v>525</v>
@@ -10321,16 +10321,16 @@
         <v>845</v>
       </c>
       <c r="AM18" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="AN18" t="s">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="AO18">
-        <v>0.99681451207345617</v>
+        <v>0.99679484751730962</v>
       </c>
       <c r="AP18">
-        <v>58.400611986637742</v>
+        <v>58.761128849323015</v>
       </c>
       <c r="AR18" t="s">
         <v>525</v>
@@ -10357,16 +10357,16 @@
         <v>1074</v>
       </c>
       <c r="BA18" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="BB18" t="s">
-        <v>1130</v>
+        <v>1030</v>
       </c>
       <c r="BC18">
-        <v>0.99538398111052984</v>
+        <v>0.99665799830099</v>
       </c>
       <c r="BD18">
-        <v>84.627012973619784</v>
+        <v>61.270031148516708</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -10431,16 +10431,16 @@
         <v>544</v>
       </c>
       <c r="Y19" t="s">
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="Z19" t="s">
         <v>767</v>
       </c>
       <c r="AA19">
-        <v>0.99198947556412609</v>
+        <v>0.98810065757436949</v>
       </c>
       <c r="AB19">
-        <v>146.85961465768753</v>
+        <v>218.15461113655846</v>
       </c>
       <c r="AD19" t="s">
         <v>525</v>
@@ -10467,16 +10467,16 @@
         <v>847</v>
       </c>
       <c r="AM19" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="AN19" t="s">
-        <v>807</v>
+        <v>980</v>
       </c>
       <c r="AO19">
-        <v>0.9976320377495026</v>
+        <v>0.9968708897783195</v>
       </c>
       <c r="AP19">
-        <v>43.412641259119624</v>
+        <v>57.367020730809493</v>
       </c>
       <c r="AR19" t="s">
         <v>525</v>
@@ -10503,16 +10503,16 @@
         <v>1076</v>
       </c>
       <c r="BA19" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="BB19" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="BC19">
-        <v>0.98890025255868685</v>
+        <v>0.95713629889852414</v>
       </c>
       <c r="BD19">
-        <v>203.49536975740753</v>
+        <v>785.83452019372396</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -10577,16 +10577,16 @@
         <v>546</v>
       </c>
       <c r="Y20" t="s">
-        <v>520</v>
+        <v>413</v>
       </c>
       <c r="Z20" t="s">
         <v>768</v>
       </c>
       <c r="AA20">
-        <v>0.99506650442525857</v>
+        <v>0.98762529884261907</v>
       </c>
       <c r="AB20">
-        <v>90.447418870259696</v>
+        <v>226.8695212186509</v>
       </c>
       <c r="AD20" t="s">
         <v>525</v>
@@ -10613,16 +10613,16 @@
         <v>849</v>
       </c>
       <c r="AM20" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="AN20" t="s">
-        <v>816</v>
+        <v>782</v>
       </c>
       <c r="AO20">
-        <v>0.99274560110857168</v>
+        <v>0.99352359657507616</v>
       </c>
       <c r="AP20">
-        <v>132.99731300951822</v>
+        <v>118.7340627902709</v>
       </c>
       <c r="AR20" t="s">
         <v>525</v>
@@ -10649,16 +10649,16 @@
         <v>1078</v>
       </c>
       <c r="BA20" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="BB20" t="s">
-        <v>762</v>
+        <v>808</v>
       </c>
       <c r="BC20">
-        <v>0.95713629889852414</v>
+        <v>0.99232494426983575</v>
       </c>
       <c r="BD20">
-        <v>785.83452019372396</v>
+        <v>140.70935505301131</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -10723,16 +10723,16 @@
         <v>548</v>
       </c>
       <c r="Y21" t="s">
-        <v>512</v>
+        <v>483</v>
       </c>
       <c r="Z21" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AA21">
-        <v>0.99751736863660534</v>
+        <v>0.97765910024833902</v>
       </c>
       <c r="AB21">
-        <v>45.514908328903012</v>
+        <v>409.58316211378531</v>
       </c>
       <c r="AD21" t="s">
         <v>525</v>
@@ -10759,16 +10759,16 @@
         <v>851</v>
       </c>
       <c r="AM21" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="AN21" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="AO21">
-        <v>0.99729761494442914</v>
+        <v>0.99527349340380789</v>
       </c>
       <c r="AP21">
-        <v>49.543726018799653</v>
+        <v>86.652620930188576</v>
       </c>
       <c r="AR21" t="s">
         <v>525</v>
@@ -10795,16 +10795,16 @@
         <v>1080</v>
       </c>
       <c r="BA21" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="BB21" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="BC21">
-        <v>0.99232494426983575</v>
+        <v>0.99418931598784899</v>
       </c>
       <c r="BD21">
-        <v>140.70935505301131</v>
+        <v>106.52920688943452</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10869,16 +10869,16 @@
         <v>550</v>
       </c>
       <c r="Y22" t="s">
-        <v>505</v>
+        <v>419</v>
       </c>
       <c r="Z22" t="s">
-        <v>760</v>
+        <v>770</v>
       </c>
       <c r="AA22">
-        <v>0.95679886695043703</v>
+        <v>0.99660741093787208</v>
       </c>
       <c r="AB22">
-        <v>792.02077257532187</v>
+        <v>62.197466139011929</v>
       </c>
       <c r="AD22" t="s">
         <v>525</v>
@@ -10905,16 +10905,16 @@
         <v>853</v>
       </c>
       <c r="AM22" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="AN22" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="AO22">
-        <v>0.99478775228549088</v>
+        <v>0.9916381908130667</v>
       </c>
       <c r="AP22">
-        <v>95.557874766001078</v>
+        <v>153.29983509377652</v>
       </c>
       <c r="AR22" t="s">
         <v>525</v>
@@ -10941,16 +10941,16 @@
         <v>1082</v>
       </c>
       <c r="BA22" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="BB22" t="s">
-        <v>807</v>
+        <v>775</v>
       </c>
       <c r="BC22">
-        <v>0.99418931598784899</v>
+        <v>0.97821242976023937</v>
       </c>
       <c r="BD22">
-        <v>106.52920688943452</v>
+        <v>399.43878772894504</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -11015,16 +11015,16 @@
         <v>552</v>
       </c>
       <c r="Y23" t="s">
-        <v>508</v>
+        <v>436</v>
       </c>
       <c r="Z23" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="AA23">
-        <v>0.98820023878766372</v>
+        <v>0.99755601192869059</v>
       </c>
       <c r="AB23">
-        <v>216.32895555949756</v>
+        <v>44.806447974006502</v>
       </c>
       <c r="AD23" t="s">
         <v>525</v>
@@ -11051,16 +11051,16 @@
         <v>855</v>
       </c>
       <c r="AM23" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="AN23" t="s">
-        <v>799</v>
+        <v>808</v>
       </c>
       <c r="AO23">
-        <v>0.99481362508126103</v>
+        <v>0.99729205446773184</v>
       </c>
       <c r="AP23">
-        <v>95.083540176881584</v>
+        <v>49.645668091582088</v>
       </c>
       <c r="AR23" t="s">
         <v>525</v>
@@ -11087,16 +11087,16 @@
         <v>1084</v>
       </c>
       <c r="BA23" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="BB23" t="s">
-        <v>827</v>
+        <v>1130</v>
       </c>
       <c r="BC23">
-        <v>0.97821242976023937</v>
+        <v>0.99401640271965719</v>
       </c>
       <c r="BD23">
-        <v>399.43878772894504</v>
+        <v>109.69928347295183</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -11161,16 +11161,16 @@
         <v>554</v>
       </c>
       <c r="Y24" t="s">
-        <v>506</v>
+        <v>456</v>
       </c>
       <c r="Z24" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="AA24">
-        <v>0.97404342257401955</v>
+        <v>0.9938212728279423</v>
       </c>
       <c r="AB24">
-        <v>475.8705861429753</v>
+        <v>113.27666482105715</v>
       </c>
       <c r="AD24" t="s">
         <v>525</v>
@@ -11197,16 +11197,16 @@
         <v>857</v>
       </c>
       <c r="AM24" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="AN24" t="s">
-        <v>761</v>
+        <v>801</v>
       </c>
       <c r="AO24">
-        <v>0.99244513691456471</v>
+        <v>0.99000303435887327</v>
       </c>
       <c r="AP24">
-        <v>138.50582323297994</v>
+        <v>183.27770342065742</v>
       </c>
       <c r="AR24" t="s">
         <v>525</v>
@@ -11233,16 +11233,16 @@
         <v>1086</v>
       </c>
       <c r="BA24" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="BB24" t="s">
-        <v>782</v>
+        <v>760</v>
       </c>
       <c r="BC24">
-        <v>0.96863461872110523</v>
+        <v>0.99054926914187857</v>
       </c>
       <c r="BD24">
-        <v>575.0319901130714</v>
+        <v>173.26339906555947</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -11307,16 +11307,16 @@
         <v>556</v>
       </c>
       <c r="Y25" t="s">
-        <v>426</v>
+        <v>462</v>
       </c>
       <c r="Z25" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="AA25">
-        <v>0.98784519281324712</v>
+        <v>0.99529213309817555</v>
       </c>
       <c r="AB25">
-        <v>222.83813175713675</v>
+        <v>86.310893200114194</v>
       </c>
       <c r="AD25" t="s">
         <v>525</v>
@@ -11343,16 +11343,16 @@
         <v>859</v>
       </c>
       <c r="AM25" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="AN25" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="AO25">
-        <v>0.97020178001960844</v>
+        <v>0.98452519237182756</v>
       </c>
       <c r="AP25">
-        <v>546.30069964051177</v>
+        <v>283.70480651649393</v>
       </c>
       <c r="AR25" t="s">
         <v>525</v>
@@ -11379,16 +11379,16 @@
         <v>1088</v>
       </c>
       <c r="BA25" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="BB25" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="BC25">
-        <v>0.98946506962487613</v>
+        <v>0.98574436213546524</v>
       </c>
       <c r="BD25">
-        <v>193.14039021060518</v>
+        <v>261.35336084980423</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -11453,16 +11453,16 @@
         <v>558</v>
       </c>
       <c r="Y26" t="s">
-        <v>415</v>
+        <v>469</v>
       </c>
       <c r="Z26" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="AA26">
-        <v>0.99679666622099095</v>
+        <v>0.99156696838886027</v>
       </c>
       <c r="AB26">
-        <v>58.72778594849845</v>
+        <v>154.60557953756208</v>
       </c>
       <c r="AD26" t="s">
         <v>525</v>
@@ -11489,16 +11489,16 @@
         <v>861</v>
       </c>
       <c r="AM26" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="AN26" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="AO26">
-        <v>0.99083036293819104</v>
+        <v>0.9974675531234084</v>
       </c>
       <c r="AP26">
-        <v>168.11001279983091</v>
+        <v>46.428192737512276</v>
       </c>
       <c r="AR26" t="s">
         <v>525</v>
@@ -11525,16 +11525,16 @@
         <v>1090</v>
       </c>
       <c r="BA26" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="BB26" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="BC26">
-        <v>0.98125520899414764</v>
+        <v>0.99374755699184159</v>
       </c>
       <c r="BD26">
-        <v>343.65450177395917</v>
+        <v>114.62812181623703</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -11599,16 +11599,16 @@
         <v>560</v>
       </c>
       <c r="Y27" t="s">
-        <v>493</v>
+        <v>444</v>
       </c>
       <c r="Z27" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="AA27">
-        <v>0.98775140142897844</v>
+        <v>0.99401688555089329</v>
       </c>
       <c r="AB27">
-        <v>224.55764046872929</v>
+        <v>109.69043156695554</v>
       </c>
       <c r="AD27" t="s">
         <v>525</v>
@@ -11635,16 +11635,16 @@
         <v>863</v>
       </c>
       <c r="AM27" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="AN27" t="s">
-        <v>821</v>
+        <v>782</v>
       </c>
       <c r="AO27">
-        <v>0.99175391794306234</v>
+        <v>0.99532453653339104</v>
       </c>
       <c r="AP27">
-        <v>151.17817104385733</v>
+        <v>85.716830221163534</v>
       </c>
       <c r="AR27" t="s">
         <v>525</v>
@@ -11671,16 +11671,16 @@
         <v>1092</v>
       </c>
       <c r="BA27" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="BB27" t="s">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="BC27">
-        <v>0.9933934749176847</v>
+        <v>0.99542890407822671</v>
       </c>
       <c r="BD27">
-        <v>121.11962650911367</v>
+        <v>83.803425232511387</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -11745,16 +11745,16 @@
         <v>562</v>
       </c>
       <c r="Y28" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="Z28" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="AA28">
-        <v>0.99149332428826786</v>
+        <v>0.99519181845511939</v>
       </c>
       <c r="AB28">
-        <v>155.95572138175513</v>
+        <v>88.149994989478557</v>
       </c>
       <c r="AD28" t="s">
         <v>525</v>
@@ -11781,16 +11781,16 @@
         <v>865</v>
       </c>
       <c r="AM28" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="AN28" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="AO28">
-        <v>0.99694189558126134</v>
+        <v>0.996795372708284</v>
       </c>
       <c r="AP28">
-        <v>56.065247676874698</v>
+        <v>58.751500348127372</v>
       </c>
       <c r="AR28" t="s">
         <v>525</v>
@@ -11817,16 +11817,16 @@
         <v>1094</v>
       </c>
       <c r="BA28" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="BB28" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="BC28">
-        <v>0.98163861082146986</v>
+        <v>0.96863461872110523</v>
       </c>
       <c r="BD28">
-        <v>336.62546827305243</v>
+        <v>575.0319901130714</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11891,16 +11891,16 @@
         <v>564</v>
       </c>
       <c r="Y29" t="s">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="Z29" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="AA29">
-        <v>0.99563753295513335</v>
+        <v>0.99559756506177444</v>
       </c>
       <c r="AB29">
-        <v>79.978562489222767</v>
+        <v>80.711307200801741</v>
       </c>
       <c r="AD29" t="s">
         <v>525</v>
@@ -11927,16 +11927,16 @@
         <v>867</v>
       </c>
       <c r="AM29" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="AN29" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="AO29">
-        <v>0.99760255773158468</v>
+        <v>0.99534886842510228</v>
       </c>
       <c r="AP29">
-        <v>43.953108254279897</v>
+        <v>85.270745539791065</v>
       </c>
       <c r="AR29" t="s">
         <v>525</v>
@@ -11963,16 +11963,16 @@
         <v>1096</v>
       </c>
       <c r="BA29" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="BB29" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="BC29">
-        <v>0.98027195861782945</v>
+        <v>0.98946506962487613</v>
       </c>
       <c r="BD29">
-        <v>361.68075867312689</v>
+        <v>193.14039021060518</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -12037,16 +12037,16 @@
         <v>566</v>
       </c>
       <c r="Y30" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="Z30" t="s">
-        <v>762</v>
+        <v>778</v>
       </c>
       <c r="AA30">
-        <v>0.99338737982948611</v>
+        <v>0.99703099037584386</v>
       </c>
       <c r="AB30">
-        <v>121.23136979275419</v>
+        <v>54.431843109528238</v>
       </c>
       <c r="AD30" t="s">
         <v>525</v>
@@ -12073,16 +12073,16 @@
         <v>869</v>
       </c>
       <c r="AM30" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="AN30" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="AO30">
-        <v>0.99694661611560498</v>
+        <v>0.99433447571906541</v>
       </c>
       <c r="AP30">
-        <v>55.978704547242401</v>
+        <v>103.86794515046822</v>
       </c>
       <c r="AR30" t="s">
         <v>525</v>
@@ -12109,16 +12109,16 @@
         <v>1098</v>
       </c>
       <c r="BA30" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="BB30" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="BC30">
-        <v>0.98488330873784669</v>
+        <v>0.98125520899414764</v>
       </c>
       <c r="BD30">
-        <v>277.13933980614473</v>
+        <v>343.65450177395917</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -12183,16 +12183,16 @@
         <v>568</v>
       </c>
       <c r="Y31" t="s">
-        <v>455</v>
+        <v>499</v>
       </c>
       <c r="Z31" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="AA31">
-        <v>0.99488652924851917</v>
+        <v>0.99097794398489747</v>
       </c>
       <c r="AB31">
-        <v>93.746963777149261</v>
+        <v>165.40436027688003</v>
       </c>
       <c r="AD31" t="s">
         <v>525</v>
@@ -12219,16 +12219,16 @@
         <v>871</v>
       </c>
       <c r="AM31" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="AN31" t="s">
         <v>997</v>
       </c>
       <c r="AO31">
-        <v>0.9959346869215373</v>
+        <v>0.99572830729593087</v>
       </c>
       <c r="AP31">
-        <v>74.530739771815789</v>
+        <v>78.31436624126674</v>
       </c>
       <c r="AR31" t="s">
         <v>525</v>
@@ -12258,13 +12258,13 @@
         <v>1145</v>
       </c>
       <c r="BB31" t="s">
-        <v>977</v>
+        <v>770</v>
       </c>
       <c r="BC31">
-        <v>0.99665799830099</v>
+        <v>0.99098965084511315</v>
       </c>
       <c r="BD31">
-        <v>61.270031148516708</v>
+        <v>165.18973450625904</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -12329,16 +12329,16 @@
         <v>570</v>
       </c>
       <c r="Y32" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="Z32" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="AA32">
-        <v>0.99634407688349669</v>
+        <v>0.9921953803896254</v>
       </c>
       <c r="AB32">
-        <v>67.025257135894208</v>
+        <v>143.08469285686789</v>
       </c>
       <c r="AD32" t="s">
         <v>525</v>
@@ -12365,16 +12365,16 @@
         <v>873</v>
       </c>
       <c r="AM32" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="AN32" t="s">
-        <v>1001</v>
+        <v>810</v>
       </c>
       <c r="AO32">
-        <v>0.99512778152424219</v>
+        <v>0.99729761494442914</v>
       </c>
       <c r="AP32">
-        <v>89.324005388893795</v>
+        <v>49.543726018799653</v>
       </c>
       <c r="AR32" t="s">
         <v>525</v>
@@ -12404,13 +12404,13 @@
         <v>1146</v>
       </c>
       <c r="BB32" t="s">
-        <v>1144</v>
+        <v>794</v>
       </c>
       <c r="BC32">
-        <v>0.99401640271965719</v>
+        <v>0.99053278045305837</v>
       </c>
       <c r="BD32">
-        <v>109.69928347295183</v>
+        <v>173.56569169392964</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -12475,16 +12475,16 @@
         <v>572</v>
       </c>
       <c r="Y33" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="Z33" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="AA33">
-        <v>0.9882785445805562</v>
+        <v>0.99299284379308983</v>
       </c>
       <c r="AB33">
-        <v>214.89334935647034</v>
+        <v>128.46453046001977</v>
       </c>
       <c r="AD33" t="s">
         <v>525</v>
@@ -12511,16 +12511,16 @@
         <v>875</v>
       </c>
       <c r="AM33" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="AN33" t="s">
-        <v>977</v>
+        <v>1000</v>
       </c>
       <c r="AO33">
-        <v>0.99759498179797546</v>
+        <v>0.99478775228549088</v>
       </c>
       <c r="AP33">
-        <v>44.092000370450322</v>
+        <v>95.557874766001078</v>
       </c>
       <c r="AR33" t="s">
         <v>525</v>
@@ -12550,13 +12550,13 @@
         <v>1147</v>
       </c>
       <c r="BB33" t="s">
-        <v>775</v>
+        <v>808</v>
       </c>
       <c r="BC33">
-        <v>0.99834679070917032</v>
+        <v>0.99420451954813838</v>
       </c>
       <c r="BD33">
-        <v>30.308836998544216</v>
+        <v>106.25047495079694</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -12621,16 +12621,16 @@
         <v>574</v>
       </c>
       <c r="Y34" t="s">
-        <v>441</v>
+        <v>477</v>
       </c>
       <c r="Z34" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="AA34">
-        <v>0.99633066933811909</v>
+        <v>0.97540090374045474</v>
       </c>
       <c r="AB34">
-        <v>67.271062134483344</v>
+        <v>450.98343142499687</v>
       </c>
       <c r="AD34" t="s">
         <v>525</v>
@@ -12657,16 +12657,16 @@
         <v>877</v>
       </c>
       <c r="AM34" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="AN34" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="AO34">
-        <v>0.98134982200735632</v>
+        <v>0.99481362508126103</v>
       </c>
       <c r="AP34">
-        <v>341.91992986513412</v>
+        <v>95.083540176881584</v>
       </c>
       <c r="AR34" t="s">
         <v>525</v>
@@ -12696,13 +12696,13 @@
         <v>1148</v>
       </c>
       <c r="BB34" t="s">
-        <v>813</v>
+        <v>760</v>
       </c>
       <c r="BC34">
-        <v>0.98806872821788805</v>
+        <v>0.99032129621526932</v>
       </c>
       <c r="BD34">
-        <v>218.73998267205184</v>
+        <v>177.44290272006148</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -12767,16 +12767,16 @@
         <v>576</v>
       </c>
       <c r="Y35" t="s">
-        <v>449</v>
+        <v>417</v>
       </c>
       <c r="Z35" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="AA35">
-        <v>0.99497952870756723</v>
+        <v>0.99658165567225754</v>
       </c>
       <c r="AB35">
-        <v>92.041973694600031</v>
+        <v>62.669646008611245</v>
       </c>
       <c r="AD35" t="s">
         <v>525</v>
@@ -12803,16 +12803,16 @@
         <v>879</v>
       </c>
       <c r="AM35" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="AN35" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="AO35">
-        <v>0.98934663566509429</v>
+        <v>0.99414234808301016</v>
       </c>
       <c r="AP35">
-        <v>195.31167947327185</v>
+        <v>107.39028514481463</v>
       </c>
       <c r="AR35" t="s">
         <v>525</v>
@@ -12842,13 +12842,13 @@
         <v>1149</v>
       </c>
       <c r="BB35" t="s">
-        <v>775</v>
+        <v>1150</v>
       </c>
       <c r="BC35">
-        <v>0.99032129621526932</v>
+        <v>0.98691003029105739</v>
       </c>
       <c r="BD35">
-        <v>177.44290272006148</v>
+        <v>239.98277799728109</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -12913,16 +12913,16 @@
         <v>578</v>
       </c>
       <c r="Y36" t="s">
-        <v>517</v>
+        <v>440</v>
       </c>
       <c r="Z36" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="AA36">
-        <v>0.97432735774114165</v>
+        <v>0.99587193000843988</v>
       </c>
       <c r="AB36">
-        <v>470.66510807906917</v>
+        <v>75.681283178602214</v>
       </c>
       <c r="AD36" t="s">
         <v>525</v>
@@ -12949,16 +12949,16 @@
         <v>881</v>
       </c>
       <c r="AM36" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="AN36" t="s">
-        <v>997</v>
+        <v>774</v>
       </c>
       <c r="AO36">
-        <v>0.99105808324017197</v>
+        <v>0.99676376447003934</v>
       </c>
       <c r="AP36">
-        <v>163.93514059684662</v>
+        <v>59.330984715944624</v>
       </c>
       <c r="AR36" t="s">
         <v>525</v>
@@ -12985,16 +12985,16 @@
         <v>1110</v>
       </c>
       <c r="BA36" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="BB36" t="s">
-        <v>1151</v>
+        <v>808</v>
       </c>
       <c r="BC36">
-        <v>0.98691003029105739</v>
+        <v>0.9933934749176847</v>
       </c>
       <c r="BD36">
-        <v>239.98277799728109</v>
+        <v>121.11962650911367</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -13059,16 +13059,16 @@
         <v>580</v>
       </c>
       <c r="Y37" t="s">
-        <v>494</v>
+        <v>457</v>
       </c>
       <c r="Z37" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="AA37">
-        <v>0.98092062608337349</v>
+        <v>0.9946890792776012</v>
       </c>
       <c r="AB37">
-        <v>349.78852180481954</v>
+        <v>97.3668799106444</v>
       </c>
       <c r="AD37" t="s">
         <v>525</v>
@@ -13095,16 +13095,16 @@
         <v>883</v>
       </c>
       <c r="AM37" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="AN37" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="AO37">
-        <v>0.99445933293330402</v>
+        <v>0.99424679200457</v>
       </c>
       <c r="AP37">
-        <v>101.57889622275951</v>
+        <v>105.47547991621673</v>
       </c>
       <c r="AR37" t="s">
         <v>525</v>
@@ -13134,13 +13134,13 @@
         <v>1152</v>
       </c>
       <c r="BB37" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="BC37">
-        <v>0.99054926914187857</v>
+        <v>0.98163861082146986</v>
       </c>
       <c r="BD37">
-        <v>173.26339906555947</v>
+        <v>336.62546827305243</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -13205,16 +13205,16 @@
         <v>582</v>
       </c>
       <c r="Y38" t="s">
-        <v>410</v>
+        <v>458</v>
       </c>
       <c r="Z38" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="AA38">
-        <v>0.99511502462858281</v>
+        <v>0.99318647897745582</v>
       </c>
       <c r="AB38">
-        <v>89.557881809315646</v>
+        <v>124.91455207997609</v>
       </c>
       <c r="AD38" t="s">
         <v>525</v>
@@ -13241,16 +13241,16 @@
         <v>885</v>
       </c>
       <c r="AM38" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="AN38" t="s">
-        <v>1009</v>
+        <v>770</v>
       </c>
       <c r="AO38">
-        <v>0.99336049451151065</v>
+        <v>0.99567626923235475</v>
       </c>
       <c r="AP38">
-        <v>121.72426728897108</v>
+        <v>79.268397406829976</v>
       </c>
       <c r="AR38" t="s">
         <v>525</v>
@@ -13280,13 +13280,13 @@
         <v>1153</v>
       </c>
       <c r="BB38" t="s">
-        <v>807</v>
+        <v>760</v>
       </c>
       <c r="BC38">
-        <v>0.98574436213546524</v>
+        <v>0.99834679070917032</v>
       </c>
       <c r="BD38">
-        <v>261.35336084980423</v>
+        <v>30.308836998544216</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -13351,16 +13351,16 @@
         <v>584</v>
       </c>
       <c r="Y39" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="Z39" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="AA39">
-        <v>0.99569496806116964</v>
+        <v>0.99198947556412609</v>
       </c>
       <c r="AB39">
-        <v>78.92558554522391</v>
+        <v>146.85961465768753</v>
       </c>
       <c r="AD39" t="s">
         <v>525</v>
@@ -13387,16 +13387,16 @@
         <v>887</v>
       </c>
       <c r="AM39" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="AN39" t="s">
-        <v>977</v>
+        <v>1008</v>
       </c>
       <c r="AO39">
-        <v>0.99569050067699549</v>
+        <v>0.99766813121902409</v>
       </c>
       <c r="AP39">
-        <v>79.007487588415231</v>
+        <v>42.750927651225993</v>
       </c>
       <c r="AR39" t="s">
         <v>525</v>
@@ -13426,13 +13426,13 @@
         <v>1154</v>
       </c>
       <c r="BB39" t="s">
-        <v>1139</v>
+        <v>813</v>
       </c>
       <c r="BC39">
-        <v>0.99374755699184159</v>
+        <v>0.98806872821788805</v>
       </c>
       <c r="BD39">
-        <v>114.62812181623703</v>
+        <v>218.73998267205184</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -13497,16 +13497,16 @@
         <v>586</v>
       </c>
       <c r="Y40" t="s">
-        <v>468</v>
+        <v>522</v>
       </c>
       <c r="Z40" t="s">
-        <v>782</v>
+        <v>764</v>
       </c>
       <c r="AA40">
-        <v>0.99324534320140812</v>
+        <v>0.98313106622136326</v>
       </c>
       <c r="AB40">
-        <v>123.83537464085195</v>
+        <v>309.26378594167363</v>
       </c>
       <c r="AD40" t="s">
         <v>525</v>
@@ -13533,16 +13533,16 @@
         <v>889</v>
       </c>
       <c r="AM40" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="AN40" t="s">
-        <v>1012</v>
+        <v>813</v>
       </c>
       <c r="AO40">
-        <v>0.97651207122624506</v>
+        <v>0.99403730604060547</v>
       </c>
       <c r="AP40">
-        <v>430.61202751883985</v>
+        <v>109.31605592223302</v>
       </c>
       <c r="AR40" t="s">
         <v>525</v>
@@ -13572,13 +13572,13 @@
         <v>1155</v>
       </c>
       <c r="BB40" t="s">
-        <v>817</v>
+        <v>760</v>
       </c>
       <c r="BC40">
-        <v>0.99542890407822671</v>
+        <v>0.98890025255868685</v>
       </c>
       <c r="BD40">
-        <v>83.803425232511387</v>
+        <v>203.49536975740753</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -13643,16 +13643,16 @@
         <v>588</v>
       </c>
       <c r="Y41" t="s">
-        <v>515</v>
+        <v>496</v>
       </c>
       <c r="Z41" t="s">
-        <v>768</v>
+        <v>786</v>
       </c>
       <c r="AA41">
-        <v>0.96260810713044742</v>
+        <v>0.98061830542009054</v>
       </c>
       <c r="AB41">
-        <v>685.51803594179648</v>
+        <v>355.3310672983406</v>
       </c>
       <c r="AD41" t="s">
         <v>525</v>
@@ -13679,16 +13679,16 @@
         <v>891</v>
       </c>
       <c r="AM41" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="AN41" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="AO41">
-        <v>0.99620534810300254</v>
+        <v>0.99760247912344124</v>
       </c>
       <c r="AP41">
-        <v>69.568618111619969</v>
+        <v>43.95454940357709</v>
       </c>
       <c r="AR41" t="s">
         <v>525</v>
@@ -13718,13 +13718,13 @@
         <v>1156</v>
       </c>
       <c r="BB41" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="BC41">
-        <v>0.9959052853503485</v>
+        <v>0.99314574070258299</v>
       </c>
       <c r="BD41">
-        <v>75.06976857694373</v>
+        <v>125.66142045264445</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -13789,16 +13789,16 @@
         <v>590</v>
       </c>
       <c r="Y42" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="Z42" t="s">
-        <v>768</v>
+        <v>787</v>
       </c>
       <c r="AA42">
-        <v>0.9952199348493368</v>
+        <v>0.99107116626800151</v>
       </c>
       <c r="AB42">
-        <v>87.634527762158285</v>
+        <v>163.69528508663959</v>
       </c>
       <c r="AD42" t="s">
         <v>525</v>
@@ -13825,16 +13825,16 @@
         <v>893</v>
       </c>
       <c r="AM42" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="AN42" t="s">
-        <v>800</v>
+        <v>1005</v>
       </c>
       <c r="AO42">
-        <v>0.99503039970536677</v>
+        <v>0.99473480482648013</v>
       </c>
       <c r="AP42">
-        <v>91.109338734942796</v>
+        <v>96.528578181196991</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -13899,16 +13899,16 @@
         <v>592</v>
       </c>
       <c r="Y43" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="Z43" t="s">
-        <v>760</v>
+        <v>787</v>
       </c>
       <c r="AA43">
-        <v>0.99458146009165993</v>
+        <v>0.99464340805826168</v>
       </c>
       <c r="AB43">
-        <v>99.339898319567055</v>
+        <v>98.204185598535332</v>
       </c>
       <c r="AD43" t="s">
         <v>525</v>
@@ -13935,16 +13935,16 @@
         <v>895</v>
       </c>
       <c r="AM43" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="AN43" t="s">
-        <v>973</v>
+        <v>1013</v>
       </c>
       <c r="AO43">
-        <v>0.99648541839873139</v>
+        <v>0.98589595763902149</v>
       </c>
       <c r="AP43">
-        <v>64.433996023258757</v>
+        <v>258.57410995127316</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -14009,16 +14009,16 @@
         <v>594</v>
       </c>
       <c r="Y44" t="s">
-        <v>487</v>
+        <v>463</v>
       </c>
       <c r="Z44" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="AA44">
-        <v>0.99379518324865879</v>
+        <v>0.99480863709915346</v>
       </c>
       <c r="AB44">
-        <v>113.75497377458942</v>
+        <v>95.174986515519862</v>
       </c>
       <c r="AD44" t="s">
         <v>525</v>
@@ -14045,16 +14045,16 @@
         <v>897</v>
       </c>
       <c r="AM44" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="AN44" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="AO44">
-        <v>0.99681149341412811</v>
+        <v>0.99681451207345617</v>
       </c>
       <c r="AP44">
-        <v>58.455954074317894</v>
+        <v>58.400611986637742</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -14119,16 +14119,16 @@
         <v>596</v>
       </c>
       <c r="Y45" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="Z45" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="AA45">
-        <v>0.99572772883333938</v>
+        <v>0.99377462362826907</v>
       </c>
       <c r="AB45">
-        <v>78.324971388777698</v>
+        <v>114.13190014840048</v>
       </c>
       <c r="AD45" t="s">
         <v>525</v>
@@ -14155,16 +14155,16 @@
         <v>899</v>
       </c>
       <c r="AM45" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="AN45" t="s">
-        <v>829</v>
+        <v>808</v>
       </c>
       <c r="AO45">
-        <v>0.99641899952784574</v>
+        <v>0.9976320377495026</v>
       </c>
       <c r="AP45">
-        <v>65.65167532282868</v>
+        <v>43.412641259119624</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -14229,16 +14229,16 @@
         <v>598</v>
       </c>
       <c r="Y46" t="s">
-        <v>522</v>
+        <v>476</v>
       </c>
       <c r="Z46" t="s">
-        <v>768</v>
+        <v>790</v>
       </c>
       <c r="AA46">
-        <v>0.98313106622136326</v>
+        <v>0.99283898738129273</v>
       </c>
       <c r="AB46">
-        <v>309.26378594167363</v>
+        <v>131.2852313429664</v>
       </c>
       <c r="AD46" t="s">
         <v>525</v>
@@ -14265,16 +14265,16 @@
         <v>901</v>
       </c>
       <c r="AM46" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="AN46" t="s">
-        <v>788</v>
+        <v>816</v>
       </c>
       <c r="AO46">
-        <v>0.99000303435887327</v>
+        <v>0.99274560110857168</v>
       </c>
       <c r="AP46">
-        <v>183.27770342065742</v>
+        <v>132.99731300951822</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -14339,16 +14339,16 @@
         <v>600</v>
       </c>
       <c r="Y47" t="s">
-        <v>496</v>
+        <v>474</v>
       </c>
       <c r="Z47" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="AA47">
-        <v>0.98061830542009054</v>
+        <v>0.99380730657517002</v>
       </c>
       <c r="AB47">
-        <v>355.3310672983406</v>
+        <v>113.53271278855006</v>
       </c>
       <c r="AD47" t="s">
         <v>525</v>
@@ -14375,16 +14375,16 @@
         <v>903</v>
       </c>
       <c r="AM47" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="AN47" t="s">
-        <v>1020</v>
+        <v>765</v>
       </c>
       <c r="AO47">
-        <v>0.98452519237182756</v>
+        <v>0.95532613069733086</v>
       </c>
       <c r="AP47">
-        <v>283.70480651649393</v>
+        <v>819.02093721560016</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -14449,16 +14449,16 @@
         <v>602</v>
       </c>
       <c r="Y48" t="s">
-        <v>490</v>
+        <v>432</v>
       </c>
       <c r="Z48" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="AA48">
-        <v>0.99107116626800151</v>
+        <v>0.9826276473097606</v>
       </c>
       <c r="AB48">
-        <v>163.69528508663959</v>
+        <v>318.4931326543898</v>
       </c>
       <c r="AD48" t="s">
         <v>525</v>
@@ -14485,16 +14485,16 @@
         <v>905</v>
       </c>
       <c r="AM48" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="AN48" t="s">
-        <v>763</v>
+        <v>1019</v>
       </c>
       <c r="AO48">
-        <v>0.9974675531234084</v>
+        <v>0.9961850470371636</v>
       </c>
       <c r="AP48">
-        <v>46.428192737512276</v>
+        <v>69.94080431866837</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -14559,16 +14559,16 @@
         <v>604</v>
       </c>
       <c r="Y49" t="s">
-        <v>489</v>
+        <v>420</v>
       </c>
       <c r="Z49" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="AA49">
-        <v>0.99464340805826168</v>
+        <v>0.9946346679588659</v>
       </c>
       <c r="AB49">
-        <v>98.204185598535332</v>
+        <v>98.364420754124808</v>
       </c>
       <c r="AD49" t="s">
         <v>525</v>
@@ -14595,16 +14595,16 @@
         <v>907</v>
       </c>
       <c r="AM49" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="AN49" t="s">
-        <v>764</v>
+        <v>808</v>
       </c>
       <c r="AO49">
-        <v>0.99532453653339104</v>
+        <v>0.99765219450274578</v>
       </c>
       <c r="AP49">
-        <v>85.716830221163534</v>
+        <v>43.043100782993086</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -14669,16 +14669,16 @@
         <v>606</v>
       </c>
       <c r="Y50" t="s">
-        <v>463</v>
+        <v>422</v>
       </c>
       <c r="Z50" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="AA50">
-        <v>0.99480863709915346</v>
+        <v>0.997058362423484</v>
       </c>
       <c r="AB50">
-        <v>95.174986515519862</v>
+        <v>53.930022236127087</v>
       </c>
       <c r="AD50" t="s">
         <v>525</v>
@@ -14705,16 +14705,16 @@
         <v>909</v>
       </c>
       <c r="AM50" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="AN50" t="s">
-        <v>1024</v>
+        <v>816</v>
       </c>
       <c r="AO50">
-        <v>0.996795372708284</v>
+        <v>0.98829989485605374</v>
       </c>
       <c r="AP50">
-        <v>58.751500348127372</v>
+        <v>214.50192763901472</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -14779,16 +14779,16 @@
         <v>608</v>
       </c>
       <c r="Y51" t="s">
-        <v>445</v>
+        <v>515</v>
       </c>
       <c r="Z51" t="s">
-        <v>784</v>
+        <v>764</v>
       </c>
       <c r="AA51">
-        <v>0.99377462362826907</v>
+        <v>0.96260810713044742</v>
       </c>
       <c r="AB51">
-        <v>114.13190014840048</v>
+        <v>685.51803594179648</v>
       </c>
       <c r="AD51" t="s">
         <v>525</v>
@@ -14815,16 +14815,16 @@
         <v>911</v>
       </c>
       <c r="AM51" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="AN51" t="s">
-        <v>1001</v>
+        <v>817</v>
       </c>
       <c r="AO51">
-        <v>0.99534886842510228</v>
+        <v>0.99661420625883024</v>
       </c>
       <c r="AP51">
-        <v>85.270745539791065</v>
+        <v>62.072885254778228</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -14889,16 +14889,16 @@
         <v>610</v>
       </c>
       <c r="Y52" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="Z52" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="AA52">
-        <v>0.96988338866662871</v>
+        <v>0.9952199348493368</v>
       </c>
       <c r="AB52">
-        <v>552.13787444514003</v>
+        <v>87.634527762158285</v>
       </c>
       <c r="AD52" t="s">
         <v>525</v>
@@ -14925,16 +14925,16 @@
         <v>913</v>
       </c>
       <c r="AM52" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="AN52" t="s">
-        <v>795</v>
+        <v>806</v>
       </c>
       <c r="AO52">
-        <v>0.99433447571906541</v>
+        <v>0.98674094240398891</v>
       </c>
       <c r="AP52">
-        <v>103.86794515046822</v>
+        <v>243.0827225935364</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -14999,16 +14999,16 @@
         <v>612</v>
       </c>
       <c r="Y53" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="Z53" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="AA53">
-        <v>0.99645766237006306</v>
+        <v>0.99458146009165993</v>
       </c>
       <c r="AB53">
-        <v>64.942856548844617</v>
+        <v>99.339898319567055</v>
       </c>
       <c r="AD53" t="s">
         <v>525</v>
@@ -15035,16 +15035,16 @@
         <v>915</v>
       </c>
       <c r="AM53" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="AN53" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="AO53">
-        <v>0.99572830729593087</v>
+        <v>0.99776894175014486</v>
       </c>
       <c r="AP53">
-        <v>78.31436624126674</v>
+        <v>40.90273458067751</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -15109,16 +15109,16 @@
         <v>614</v>
       </c>
       <c r="Y54" t="s">
-        <v>509</v>
+        <v>487</v>
       </c>
       <c r="Z54" t="s">
-        <v>768</v>
+        <v>795</v>
       </c>
       <c r="AA54">
-        <v>0.98951603395057575</v>
+        <v>0.99379518324865879</v>
       </c>
       <c r="AB54">
-        <v>192.20604423944565</v>
+        <v>113.75497377458942</v>
       </c>
       <c r="AD54" t="s">
         <v>525</v>
@@ -15145,16 +15145,16 @@
         <v>917</v>
       </c>
       <c r="AM54" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="AN54" t="s">
-        <v>761</v>
+        <v>974</v>
       </c>
       <c r="AO54">
-        <v>0.98599828568941739</v>
+        <v>0.99374536027070226</v>
       </c>
       <c r="AP54">
-        <v>256.69809569401372</v>
+        <v>114.668395037126</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -15219,16 +15219,16 @@
         <v>616</v>
       </c>
       <c r="Y55" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="Z55" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AA55">
-        <v>0.99315041369049573</v>
+        <v>0.99572772883333938</v>
       </c>
       <c r="AB55">
-        <v>125.57574900757763</v>
+        <v>78.324971388777698</v>
       </c>
       <c r="AD55" t="s">
         <v>525</v>
@@ -15255,16 +15255,16 @@
         <v>919</v>
       </c>
       <c r="AM55" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="AN55" t="s">
-        <v>775</v>
+        <v>1028</v>
       </c>
       <c r="AO55">
-        <v>0.99679484751730962</v>
+        <v>0.99733068647604728</v>
       </c>
       <c r="AP55">
-        <v>58.761128849323015</v>
+        <v>48.937414605800647</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -15329,16 +15329,16 @@
         <v>618</v>
       </c>
       <c r="Y56" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="Z56" t="s">
-        <v>789</v>
+        <v>765</v>
       </c>
       <c r="AA56">
-        <v>0.99417318459860438</v>
+        <v>0.99020196511745218</v>
       </c>
       <c r="AB56">
-        <v>106.82494902558629</v>
+        <v>179.63063951337628</v>
       </c>
       <c r="AD56" t="s">
         <v>525</v>
@@ -15365,16 +15365,16 @@
         <v>921</v>
       </c>
       <c r="AM56" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="AN56" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="AO56">
-        <v>0.9968708897783195</v>
+        <v>0.99671693937496686</v>
       </c>
       <c r="AP56">
-        <v>57.367020730809493</v>
+        <v>60.189444792275019</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -15439,16 +15439,16 @@
         <v>620</v>
       </c>
       <c r="Y57" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="Z57" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="AA57">
-        <v>0.99771856082351684</v>
+        <v>0.97046710847823026</v>
       </c>
       <c r="AB57">
-        <v>41.826384902191116</v>
+        <v>541.43634456577831</v>
       </c>
       <c r="AD57" t="s">
         <v>525</v>
@@ -15475,16 +15475,16 @@
         <v>923</v>
       </c>
       <c r="AM57" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="AN57" t="s">
-        <v>764</v>
+        <v>791</v>
       </c>
       <c r="AO57">
-        <v>0.99352359657507616</v>
+        <v>0.98134982200735632</v>
       </c>
       <c r="AP57">
-        <v>118.7340627902709</v>
+        <v>341.91992986513412</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -15549,16 +15549,16 @@
         <v>622</v>
       </c>
       <c r="Y58" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="Z58" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="AA58">
-        <v>0.9951333541612547</v>
+        <v>0.97537850670549553</v>
       </c>
       <c r="AB58">
-        <v>89.221840376997676</v>
+        <v>451.39404373258168</v>
       </c>
       <c r="AD58" t="s">
         <v>525</v>
@@ -15585,16 +15585,16 @@
         <v>925</v>
       </c>
       <c r="AM58" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="AN58" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="AO58">
-        <v>0.99527349340380789</v>
+        <v>0.98934663566509429</v>
       </c>
       <c r="AP58">
-        <v>86.652620930188576</v>
+        <v>195.31167947327185</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -15659,16 +15659,16 @@
         <v>624</v>
       </c>
       <c r="Y59" t="s">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="Z59" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AA59">
-        <v>0.96192701971480499</v>
+        <v>0.98289281118622185</v>
       </c>
       <c r="AB59">
-        <v>698.00463856190902</v>
+        <v>313.63179491926536</v>
       </c>
       <c r="AD59" t="s">
         <v>525</v>
@@ -15695,16 +15695,16 @@
         <v>927</v>
       </c>
       <c r="AM59" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="AN59" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="AO59">
-        <v>0.9916381908130667</v>
+        <v>0.99105808324017197</v>
       </c>
       <c r="AP59">
-        <v>153.29983509377652</v>
+        <v>163.93514059684662</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -15769,16 +15769,16 @@
         <v>626</v>
       </c>
       <c r="Y60" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="Z60" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="AA60">
-        <v>0.98117083928229931</v>
+        <v>0.99777342334799435</v>
       </c>
       <c r="AB60">
-        <v>345.20127982451362</v>
+        <v>40.820571953437025</v>
       </c>
       <c r="AD60" t="s">
         <v>525</v>
@@ -15805,16 +15805,16 @@
         <v>929</v>
       </c>
       <c r="AM60" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="AN60" t="s">
-        <v>807</v>
+        <v>1036</v>
       </c>
       <c r="AO60">
-        <v>0.99729205446773184</v>
+        <v>0.99445933293330402</v>
       </c>
       <c r="AP60">
-        <v>49.645668091582088</v>
+        <v>101.57889622275951</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -15879,16 +15879,16 @@
         <v>628</v>
       </c>
       <c r="Y61" t="s">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="Z61" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="AA61">
-        <v>0.99395651765584936</v>
+        <v>0.99456845174856667</v>
       </c>
       <c r="AB61">
-        <v>110.79717630942883</v>
+        <v>99.578384609610097</v>
       </c>
       <c r="AD61" t="s">
         <v>525</v>
@@ -15915,16 +15915,16 @@
         <v>931</v>
       </c>
       <c r="AM61" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AN61" t="s">
         <v>1038</v>
       </c>
-      <c r="AN61" t="s">
-        <v>979</v>
-      </c>
       <c r="AO61">
-        <v>0.99551365545858539</v>
+        <v>0.99336049451151065</v>
       </c>
       <c r="AP61">
-        <v>82.249649925934918</v>
+        <v>121.72426728897108</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -15989,16 +15989,16 @@
         <v>630</v>
       </c>
       <c r="Y62" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="Z62" t="s">
-        <v>783</v>
+        <v>800</v>
       </c>
       <c r="AA62">
-        <v>0.98563153879963317</v>
+        <v>0.99302343871187126</v>
       </c>
       <c r="AB62">
-        <v>263.42178867339101</v>
+        <v>127.90362361569299</v>
       </c>
       <c r="AD62" t="s">
         <v>525</v>
@@ -16028,13 +16028,13 @@
         <v>1039</v>
       </c>
       <c r="AN62" t="s">
-        <v>820</v>
+        <v>1030</v>
       </c>
       <c r="AO62">
-        <v>0.9972012891192491</v>
+        <v>0.99569050067699549</v>
       </c>
       <c r="AP62">
-        <v>51.309699480432613</v>
+        <v>79.007487588415231</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -16099,16 +16099,16 @@
         <v>632</v>
       </c>
       <c r="Y63" t="s">
-        <v>421</v>
+        <v>518</v>
       </c>
       <c r="Z63" t="s">
-        <v>794</v>
+        <v>764</v>
       </c>
       <c r="AA63">
-        <v>0.99558181127270129</v>
+        <v>0.96988338866662871</v>
       </c>
       <c r="AB63">
-        <v>81.000126667143434</v>
+        <v>552.13787444514003</v>
       </c>
       <c r="AD63" t="s">
         <v>525</v>
@@ -16138,13 +16138,13 @@
         <v>1040</v>
       </c>
       <c r="AN63" t="s">
-        <v>1041</v>
+        <v>797</v>
       </c>
       <c r="AO63">
-        <v>0.99554924619735208</v>
+        <v>0.97416725971121887</v>
       </c>
       <c r="AP63">
-        <v>81.597153048545437</v>
+        <v>473.60023862765331</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -16209,16 +16209,16 @@
         <v>634</v>
       </c>
       <c r="Y64" t="s">
-        <v>438</v>
+        <v>513</v>
       </c>
       <c r="Z64" t="s">
-        <v>784</v>
+        <v>764</v>
       </c>
       <c r="AA64">
-        <v>0.99476729801312358</v>
+        <v>0.99645766237006306</v>
       </c>
       <c r="AB64">
-        <v>95.932869759401342</v>
+        <v>64.942856548844617</v>
       </c>
       <c r="AD64" t="s">
         <v>525</v>
@@ -16245,16 +16245,16 @@
         <v>937</v>
       </c>
       <c r="AM64" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="AN64" t="s">
-        <v>821</v>
+        <v>770</v>
       </c>
       <c r="AO64">
-        <v>0.99414234808301016</v>
+        <v>0.99766717912296166</v>
       </c>
       <c r="AP64">
-        <v>107.39028514481463</v>
+        <v>42.768382745703043</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -16319,16 +16319,16 @@
         <v>636</v>
       </c>
       <c r="Y65" t="s">
-        <v>447</v>
+        <v>509</v>
       </c>
       <c r="Z65" t="s">
-        <v>795</v>
+        <v>764</v>
       </c>
       <c r="AA65">
-        <v>0.99549647084304327</v>
+        <v>0.98951603395057575</v>
       </c>
       <c r="AB65">
-        <v>82.564701210872954</v>
+        <v>192.20604423944565</v>
       </c>
       <c r="AD65" t="s">
         <v>525</v>
@@ -16355,16 +16355,16 @@
         <v>939</v>
       </c>
       <c r="AM65" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="AN65" t="s">
-        <v>797</v>
+        <v>813</v>
       </c>
       <c r="AO65">
-        <v>0.99676376447003934</v>
+        <v>0.99498027772893805</v>
       </c>
       <c r="AP65">
-        <v>59.330984715944624</v>
+        <v>92.02824163613559</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -16429,16 +16429,16 @@
         <v>638</v>
       </c>
       <c r="Y66" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="Z66" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="AA66">
-        <v>0.99219252851411011</v>
+        <v>0.99315041369049573</v>
       </c>
       <c r="AB66">
-        <v>143.13697724131458</v>
+        <v>125.57574900757763</v>
       </c>
       <c r="AD66" t="s">
         <v>525</v>
@@ -16465,16 +16465,16 @@
         <v>941</v>
       </c>
       <c r="AM66" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="AN66" t="s">
-        <v>979</v>
+        <v>789</v>
       </c>
       <c r="AO66">
-        <v>0.99424679200457</v>
+        <v>0.9955955730654259</v>
       </c>
       <c r="AP66">
-        <v>105.47547991621673</v>
+        <v>80.747827133859133</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -16539,16 +16539,16 @@
         <v>640</v>
       </c>
       <c r="Y67" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="Z67" t="s">
-        <v>776</v>
+        <v>790</v>
       </c>
       <c r="AA67">
-        <v>0.98460718356608945</v>
+        <v>0.99417318459860438</v>
       </c>
       <c r="AB67">
-        <v>282.20163462169398</v>
+        <v>106.82494902558629</v>
       </c>
       <c r="AD67" t="s">
         <v>525</v>
@@ -16575,16 +16575,16 @@
         <v>943</v>
       </c>
       <c r="AM67" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="AN67" t="s">
-        <v>780</v>
+        <v>1034</v>
       </c>
       <c r="AO67">
-        <v>0.99567626923235475</v>
+        <v>0.99760255773158468</v>
       </c>
       <c r="AP67">
-        <v>79.268397406829976</v>
+        <v>43.953108254279897</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -16649,16 +16649,16 @@
         <v>642</v>
       </c>
       <c r="Y68" t="s">
-        <v>439</v>
+        <v>418</v>
       </c>
       <c r="Z68" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="AA68">
-        <v>0.99472452677636702</v>
+        <v>0.99771856082351684</v>
       </c>
       <c r="AB68">
-        <v>96.717009099937485</v>
+        <v>41.826384902191116</v>
       </c>
       <c r="AD68" t="s">
         <v>525</v>
@@ -16685,16 +16685,16 @@
         <v>945</v>
       </c>
       <c r="AM68" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="AN68" t="s">
-        <v>1047</v>
+        <v>793</v>
       </c>
       <c r="AO68">
-        <v>0.99766813121902409</v>
+        <v>0.99694661611560498</v>
       </c>
       <c r="AP68">
-        <v>42.750927651225993</v>
+        <v>55.978704547242401</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -16759,16 +16759,16 @@
         <v>644</v>
       </c>
       <c r="Y69" t="s">
-        <v>467</v>
+        <v>437</v>
       </c>
       <c r="Z69" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="AA69">
-        <v>0.99427848954198372</v>
+        <v>0.9951333541612547</v>
       </c>
       <c r="AB69">
-        <v>104.89435839696445</v>
+        <v>89.221840376997676</v>
       </c>
       <c r="AD69" t="s">
         <v>525</v>
@@ -16795,16 +16795,16 @@
         <v>947</v>
       </c>
       <c r="AM69" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="AN69" t="s">
-        <v>819</v>
+        <v>1034</v>
       </c>
       <c r="AO69">
-        <v>0.97416725971121887</v>
+        <v>0.9959346869215373</v>
       </c>
       <c r="AP69">
-        <v>473.60023862765331</v>
+        <v>74.530739771815789</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -16869,16 +16869,16 @@
         <v>646</v>
       </c>
       <c r="Y70" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="Z70" t="s">
-        <v>798</v>
+        <v>787</v>
       </c>
       <c r="AA70">
-        <v>0.99491123944448234</v>
+        <v>0.99219252851411011</v>
       </c>
       <c r="AB70">
-        <v>93.293943517823692</v>
+        <v>143.13697724131458</v>
       </c>
       <c r="AD70" t="s">
         <v>525</v>
@@ -16905,16 +16905,16 @@
         <v>949</v>
       </c>
       <c r="AM70" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="AN70" t="s">
-        <v>780</v>
+        <v>994</v>
       </c>
       <c r="AO70">
-        <v>0.99766717912296166</v>
+        <v>0.99512778152424219</v>
       </c>
       <c r="AP70">
-        <v>42.768382745703043</v>
+        <v>89.324005388893795</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -16979,16 +16979,16 @@
         <v>648</v>
       </c>
       <c r="Y71" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="Z71" t="s">
-        <v>799</v>
+        <v>761</v>
       </c>
       <c r="AA71">
-        <v>0.99638451167998066</v>
+        <v>0.98460718356608945</v>
       </c>
       <c r="AB71">
-        <v>66.283952533688392</v>
+        <v>282.20163462169398</v>
       </c>
       <c r="AD71" t="s">
         <v>525</v>
@@ -17015,16 +17015,16 @@
         <v>951</v>
       </c>
       <c r="AM71" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="AN71" t="s">
-        <v>813</v>
+        <v>1030</v>
       </c>
       <c r="AO71">
-        <v>0.99498027772893805</v>
+        <v>0.99759498179797546</v>
       </c>
       <c r="AP71">
-        <v>92.02824163613559</v>
+        <v>44.092000370450322</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17089,16 +17089,16 @@
         <v>650</v>
       </c>
       <c r="Y72" t="s">
-        <v>514</v>
+        <v>439</v>
       </c>
       <c r="Z72" t="s">
-        <v>768</v>
+        <v>803</v>
       </c>
       <c r="AA72">
-        <v>0.96942910386940295</v>
+        <v>0.99472452677636702</v>
       </c>
       <c r="AB72">
-        <v>560.46642906094564</v>
+        <v>96.717009099937485</v>
       </c>
       <c r="AD72" t="s">
         <v>525</v>
@@ -17125,16 +17125,16 @@
         <v>953</v>
       </c>
       <c r="AM72" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="AN72" t="s">
-        <v>784</v>
+        <v>1005</v>
       </c>
       <c r="AO72">
-        <v>0.9955955730654259</v>
+        <v>0.99551365545858539</v>
       </c>
       <c r="AP72">
-        <v>80.747827133859133</v>
+        <v>82.249649925934918</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -17199,16 +17199,16 @@
         <v>652</v>
       </c>
       <c r="Y73" t="s">
-        <v>502</v>
+        <v>467</v>
       </c>
       <c r="Z73" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
       <c r="AA73">
-        <v>0.95261480241426988</v>
+        <v>0.99427848954198372</v>
       </c>
       <c r="AB73">
-        <v>868.72862240505196</v>
+        <v>104.89435839696445</v>
       </c>
       <c r="AD73" t="s">
         <v>525</v>
@@ -17235,16 +17235,16 @@
         <v>955</v>
       </c>
       <c r="AM73" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="AN73" t="s">
-        <v>760</v>
+        <v>798</v>
       </c>
       <c r="AO73">
-        <v>0.95532613069733086</v>
+        <v>0.9972012891192491</v>
       </c>
       <c r="AP73">
-        <v>819.02093721560016</v>
+        <v>51.309699480432613</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -17309,16 +17309,16 @@
         <v>654</v>
       </c>
       <c r="Y74" t="s">
-        <v>501</v>
+        <v>446</v>
       </c>
       <c r="Z74" t="s">
-        <v>760</v>
+        <v>804</v>
       </c>
       <c r="AA74">
-        <v>0.93980266520001188</v>
+        <v>0.99491123944448234</v>
       </c>
       <c r="AB74">
-        <v>1103.617804666449</v>
+        <v>93.293943517823692</v>
       </c>
       <c r="AD74" t="s">
         <v>525</v>
@@ -17345,16 +17345,16 @@
         <v>957</v>
       </c>
       <c r="AM74" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="AN74" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="AO74">
-        <v>0.9961850470371636</v>
+        <v>0.99554924619735208</v>
       </c>
       <c r="AP74">
-        <v>69.94080431866837</v>
+        <v>81.597153048545437</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -17419,16 +17419,16 @@
         <v>656</v>
       </c>
       <c r="Y75" t="s">
-        <v>504</v>
+        <v>448</v>
       </c>
       <c r="Z75" t="s">
-        <v>785</v>
+        <v>805</v>
       </c>
       <c r="AA75">
-        <v>0.96520767961718001</v>
+        <v>0.99638451167998066</v>
       </c>
       <c r="AB75">
-        <v>637.85920701836687</v>
+        <v>66.283952533688392</v>
       </c>
       <c r="AD75" t="s">
         <v>525</v>
@@ -17455,16 +17455,16 @@
         <v>959</v>
       </c>
       <c r="AM75" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="AN75" t="s">
-        <v>807</v>
+        <v>779</v>
       </c>
       <c r="AO75">
-        <v>0.99765219450274578</v>
+        <v>0.99244513691456471</v>
       </c>
       <c r="AP75">
-        <v>43.043100782993086</v>
+        <v>138.50582323297994</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -17529,16 +17529,16 @@
         <v>658</v>
       </c>
       <c r="Y76" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="Z76" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="AA76">
-        <v>0.9916427371040899</v>
+        <v>0.99295369446862825</v>
       </c>
       <c r="AB76">
-        <v>153.21648642501913</v>
+        <v>129.18226807514921</v>
       </c>
       <c r="AD76" t="s">
         <v>525</v>
@@ -17565,16 +17565,16 @@
         <v>961</v>
       </c>
       <c r="AM76" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="AN76" t="s">
-        <v>816</v>
+        <v>1055</v>
       </c>
       <c r="AO76">
-        <v>0.98829989485605374</v>
+        <v>0.97020178001960844</v>
       </c>
       <c r="AP76">
-        <v>214.50192763901472</v>
+        <v>546.30069964051177</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -17639,16 +17639,16 @@
         <v>660</v>
       </c>
       <c r="Y77" t="s">
-        <v>434</v>
+        <v>482</v>
       </c>
       <c r="Z77" t="s">
-        <v>800</v>
+        <v>769</v>
       </c>
       <c r="AA77">
-        <v>0.99506721859763492</v>
+        <v>0.99247189917622181</v>
       </c>
       <c r="AB77">
-        <v>90.434325710025817</v>
+        <v>138.01518176926754</v>
       </c>
       <c r="AD77" t="s">
         <v>525</v>
@@ -17675,16 +17675,16 @@
         <v>963</v>
       </c>
       <c r="AM77" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="AN77" t="s">
-        <v>817</v>
+        <v>774</v>
       </c>
       <c r="AO77">
-        <v>0.99661420625883024</v>
+        <v>0.99083036293819104</v>
       </c>
       <c r="AP77">
-        <v>62.072885254778228</v>
+        <v>168.11001279983091</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -17749,16 +17749,16 @@
         <v>662</v>
       </c>
       <c r="Y78" t="s">
-        <v>472</v>
+        <v>416</v>
       </c>
       <c r="Z78" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="AA78">
-        <v>0.99504955481764434</v>
+        <v>0.99654635223367616</v>
       </c>
       <c r="AB78">
-        <v>90.758161676519606</v>
+        <v>63.316875715936199</v>
       </c>
       <c r="AD78" t="s">
         <v>525</v>
@@ -17785,16 +17785,16 @@
         <v>965</v>
       </c>
       <c r="AM78" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="AN78" t="s">
-        <v>813</v>
+        <v>799</v>
       </c>
       <c r="AO78">
-        <v>0.99403730604060547</v>
+        <v>0.99175391794306234</v>
       </c>
       <c r="AP78">
-        <v>109.31605592223302</v>
+        <v>151.17817104385733</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -17859,16 +17859,16 @@
         <v>664</v>
       </c>
       <c r="Y79" t="s">
-        <v>486</v>
+        <v>424</v>
       </c>
       <c r="Z79" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="AA79">
-        <v>0.99267056664092235</v>
+        <v>0.99732405475730812</v>
       </c>
       <c r="AB79">
-        <v>134.37294491642297</v>
+        <v>49.058996116017695</v>
       </c>
       <c r="AD79" t="s">
         <v>525</v>
@@ -17895,16 +17895,16 @@
         <v>967</v>
       </c>
       <c r="AM79" t="s">
+        <v>1058</v>
+      </c>
+      <c r="AN79" t="s">
         <v>1059</v>
       </c>
-      <c r="AN79" t="s">
-        <v>794</v>
-      </c>
       <c r="AO79">
-        <v>0.99760247912344124</v>
+        <v>0.99694189558126134</v>
       </c>
       <c r="AP79">
-        <v>43.95454940357709</v>
+        <v>56.065247676874698</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -17969,16 +17969,16 @@
         <v>666</v>
       </c>
       <c r="Y80" t="s">
-        <v>476</v>
+        <v>425</v>
       </c>
       <c r="Z80" t="s">
-        <v>789</v>
+        <v>808</v>
       </c>
       <c r="AA80">
-        <v>0.99283898738129273</v>
+        <v>0.99730161188979438</v>
       </c>
       <c r="AB80">
-        <v>131.2852313429664</v>
+        <v>49.470448687103634</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -18043,16 +18043,16 @@
         <v>668</v>
       </c>
       <c r="Y81" t="s">
-        <v>474</v>
+        <v>516</v>
       </c>
       <c r="Z81" t="s">
-        <v>803</v>
+        <v>764</v>
       </c>
       <c r="AA81">
-        <v>0.99380730657517002</v>
+        <v>0.96192701971480499</v>
       </c>
       <c r="AB81">
-        <v>113.53271278855006</v>
+        <v>698.00463856190902</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -18117,16 +18117,16 @@
         <v>670</v>
       </c>
       <c r="Y82" t="s">
-        <v>432</v>
+        <v>491</v>
       </c>
       <c r="Z82" t="s">
-        <v>772</v>
+        <v>809</v>
       </c>
       <c r="AA82">
-        <v>0.9826276473097606</v>
+        <v>0.98117083928229931</v>
       </c>
       <c r="AB82">
-        <v>318.4931326543898</v>
+        <v>345.20127982451362</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -18191,16 +18191,16 @@
         <v>672</v>
       </c>
       <c r="Y83" t="s">
-        <v>420</v>
+        <v>481</v>
       </c>
       <c r="Z83" t="s">
-        <v>804</v>
+        <v>769</v>
       </c>
       <c r="AA83">
-        <v>0.9946346679588659</v>
+        <v>0.99395651765584936</v>
       </c>
       <c r="AB83">
-        <v>98.364420754124808</v>
+        <v>110.79717630942883</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -18265,16 +18265,16 @@
         <v>674</v>
       </c>
       <c r="Y84" t="s">
-        <v>422</v>
+        <v>488</v>
       </c>
       <c r="Z84" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="AA84">
-        <v>0.997058362423484</v>
+        <v>0.98563153879963317</v>
       </c>
       <c r="AB84">
-        <v>53.930022236127087</v>
+        <v>263.42178867339101</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -18339,16 +18339,16 @@
         <v>676</v>
       </c>
       <c r="Y85" t="s">
-        <v>521</v>
+        <v>421</v>
       </c>
       <c r="Z85" t="s">
-        <v>768</v>
+        <v>810</v>
       </c>
       <c r="AA85">
-        <v>0.99295369446862825</v>
+        <v>0.99558181127270129</v>
       </c>
       <c r="AB85">
-        <v>129.18226807514921</v>
+        <v>81.000126667143434</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -18413,16 +18413,16 @@
         <v>678</v>
       </c>
       <c r="Y86" t="s">
-        <v>482</v>
+        <v>438</v>
       </c>
       <c r="Z86" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="AA86">
-        <v>0.99247189917622181</v>
+        <v>0.99476729801312358</v>
       </c>
       <c r="AB86">
-        <v>138.01518176926754</v>
+        <v>95.932869759401342</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -18487,16 +18487,16 @@
         <v>680</v>
       </c>
       <c r="Y87" t="s">
-        <v>416</v>
+        <v>447</v>
       </c>
       <c r="Z87" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="AA87">
-        <v>0.99654635223367616</v>
+        <v>0.99549647084304327</v>
       </c>
       <c r="AB87">
-        <v>63.316875715936199</v>
+        <v>82.564701210872954</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -18561,16 +18561,16 @@
         <v>682</v>
       </c>
       <c r="Y88" t="s">
-        <v>424</v>
+        <v>511</v>
       </c>
       <c r="Z88" t="s">
-        <v>806</v>
+        <v>766</v>
       </c>
       <c r="AA88">
-        <v>0.99732405475730812</v>
+        <v>0.99008735429887684</v>
       </c>
       <c r="AB88">
-        <v>49.058996116017695</v>
+        <v>181.7318378539255</v>
       </c>
     </row>
     <row r="89" spans="2:28">
@@ -18635,16 +18635,16 @@
         <v>684</v>
       </c>
       <c r="Y89" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="Z89" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="AA89">
-        <v>0.99730161188979438</v>
+        <v>0.98622431616682615</v>
       </c>
       <c r="AB89">
-        <v>49.470448687103634</v>
+        <v>252.55420360818721</v>
       </c>
     </row>
     <row r="90" spans="2:28">
@@ -18709,16 +18709,16 @@
         <v>686</v>
       </c>
       <c r="Y90" t="s">
-        <v>484</v>
+        <v>433</v>
       </c>
       <c r="Z90" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="AA90">
-        <v>0.98322768674096572</v>
+        <v>0.98732531824996883</v>
       </c>
       <c r="AB90">
-        <v>307.49240974896213</v>
+        <v>232.36916541723792</v>
       </c>
     </row>
     <row r="91" spans="2:28">
@@ -18783,16 +18783,16 @@
         <v>688</v>
       </c>
       <c r="Y91" t="s">
-        <v>480</v>
+        <v>409</v>
       </c>
       <c r="Z91" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="AA91">
-        <v>0.99530040212667992</v>
+        <v>0.99468658155318235</v>
       </c>
       <c r="AB91">
-        <v>86.159294344200944</v>
+        <v>97.412671524990884</v>
       </c>
     </row>
     <row r="92" spans="2:28">
@@ -18857,16 +18857,16 @@
         <v>690</v>
       </c>
       <c r="Y92" t="s">
-        <v>464</v>
+        <v>435</v>
       </c>
       <c r="Z92" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="AA92">
-        <v>0.99420043109362022</v>
+        <v>0.99713964204801786</v>
       </c>
       <c r="AB92">
-        <v>106.32542995029682</v>
+        <v>52.439895786339292</v>
       </c>
     </row>
     <row r="93" spans="2:28">
@@ -18931,16 +18931,16 @@
         <v>692</v>
       </c>
       <c r="Y93" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z93" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="AA93">
-        <v>0.99583023752581945</v>
+        <v>0.99321915112555448</v>
       </c>
       <c r="AB93">
-        <v>76.445645359975842</v>
+        <v>124.31556269816713</v>
       </c>
     </row>
     <row r="94" spans="2:28">
@@ -19005,16 +19005,16 @@
         <v>694</v>
       </c>
       <c r="Y94" t="s">
-        <v>466</v>
+        <v>443</v>
       </c>
       <c r="Z94" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="AA94">
-        <v>0.99239852233389214</v>
+        <v>0.99651573552934036</v>
       </c>
       <c r="AB94">
-        <v>139.36042387864416</v>
+        <v>63.878181962093116</v>
       </c>
     </row>
     <row r="95" spans="2:28">
@@ -19079,16 +19079,16 @@
         <v>696</v>
       </c>
       <c r="Y95" t="s">
-        <v>511</v>
+        <v>454</v>
       </c>
       <c r="Z95" t="s">
-        <v>769</v>
+        <v>817</v>
       </c>
       <c r="AA95">
-        <v>0.99008735429887684</v>
+        <v>0.99710492314704047</v>
       </c>
       <c r="AB95">
-        <v>181.7318378539255</v>
+        <v>53.07640897092412</v>
       </c>
     </row>
     <row r="96" spans="2:28">
@@ -19153,16 +19153,16 @@
         <v>698</v>
       </c>
       <c r="Y96" t="s">
-        <v>431</v>
+        <v>517</v>
       </c>
       <c r="Z96" t="s">
-        <v>805</v>
+        <v>764</v>
       </c>
       <c r="AA96">
-        <v>0.98622431616682615</v>
+        <v>0.97432735774114165</v>
       </c>
       <c r="AB96">
-        <v>252.55420360818721</v>
+        <v>470.66510807906917</v>
       </c>
     </row>
     <row r="97" spans="2:28">
@@ -19227,16 +19227,16 @@
         <v>700</v>
       </c>
       <c r="Y97" t="s">
-        <v>433</v>
+        <v>494</v>
       </c>
       <c r="Z97" t="s">
-        <v>800</v>
+        <v>818</v>
       </c>
       <c r="AA97">
-        <v>0.98732531824996883</v>
+        <v>0.98092062608337349</v>
       </c>
       <c r="AB97">
-        <v>232.36916541723792</v>
+        <v>349.78852180481954</v>
       </c>
     </row>
     <row r="98" spans="2:28">
@@ -19301,16 +19301,16 @@
         <v>702</v>
       </c>
       <c r="Y98" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Z98" t="s">
-        <v>813</v>
+        <v>770</v>
       </c>
       <c r="AA98">
-        <v>0.99468658155318235</v>
+        <v>0.99511502462858281</v>
       </c>
       <c r="AB98">
-        <v>97.412671524990884</v>
+        <v>89.557881809315646</v>
       </c>
     </row>
     <row r="99" spans="2:28">
@@ -19375,16 +19375,16 @@
         <v>704</v>
       </c>
       <c r="Y99" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="Z99" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="AA99">
-        <v>0.99713964204801786</v>
+        <v>0.99569496806116964</v>
       </c>
       <c r="AB99">
-        <v>52.439895786339292</v>
+        <v>78.92558554522391</v>
       </c>
     </row>
     <row r="100" spans="2:28">
@@ -19449,16 +19449,16 @@
         <v>706</v>
       </c>
       <c r="Y100" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="Z100" t="s">
-        <v>815</v>
+        <v>773</v>
       </c>
       <c r="AA100">
-        <v>0.99321915112555448</v>
+        <v>0.99324534320140812</v>
       </c>
       <c r="AB100">
-        <v>124.31556269816713</v>
+        <v>123.83537464085195</v>
       </c>
     </row>
     <row r="101" spans="2:28">
@@ -19523,16 +19523,16 @@
         <v>708</v>
       </c>
       <c r="Y101" t="s">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="Z101" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="AA101">
-        <v>0.99651573552934036</v>
+        <v>0.98322768674096572</v>
       </c>
       <c r="AB101">
-        <v>63.878181962093116</v>
+        <v>307.49240974896213</v>
       </c>
     </row>
     <row r="102" spans="2:28">
@@ -19597,16 +19597,16 @@
         <v>710</v>
       </c>
       <c r="Y102" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="Z102" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="AA102">
-        <v>0.99710492314704047</v>
+        <v>0.99530040212667992</v>
       </c>
       <c r="AB102">
-        <v>53.07640897092412</v>
+        <v>86.159294344200944</v>
       </c>
     </row>
     <row r="103" spans="2:28">
@@ -19671,16 +19671,16 @@
         <v>712</v>
       </c>
       <c r="Y103" t="s">
-        <v>498</v>
+        <v>464</v>
       </c>
       <c r="Z103" t="s">
-        <v>760</v>
+        <v>822</v>
       </c>
       <c r="AA103">
-        <v>0.99020196511745218</v>
+        <v>0.99420043109362022</v>
       </c>
       <c r="AB103">
-        <v>179.63063951337628</v>
+        <v>106.32542995029682</v>
       </c>
     </row>
     <row r="104" spans="2:28">
@@ -19745,16 +19745,16 @@
         <v>714</v>
       </c>
       <c r="Y104" t="s">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="Z104" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="AA104">
-        <v>0.97046710847823026</v>
+        <v>0.99583023752581945</v>
       </c>
       <c r="AB104">
-        <v>541.43634456577831</v>
+        <v>76.445645359975842</v>
       </c>
     </row>
     <row r="105" spans="2:28">
@@ -19819,16 +19819,16 @@
         <v>716</v>
       </c>
       <c r="Y105" t="s">
-        <v>429</v>
+        <v>466</v>
       </c>
       <c r="Z105" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="AA105">
-        <v>0.97537850670549553</v>
+        <v>0.99239852233389214</v>
       </c>
       <c r="AB105">
-        <v>451.39404373258168</v>
+        <v>139.36042387864416</v>
       </c>
     </row>
     <row r="106" spans="2:28">
@@ -19893,16 +19893,16 @@
         <v>718</v>
       </c>
       <c r="Y106" t="s">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="Z106" t="s">
-        <v>793</v>
+        <v>764</v>
       </c>
       <c r="AA106">
-        <v>0.98289281118622185</v>
+        <v>0.96942910386940295</v>
       </c>
       <c r="AB106">
-        <v>313.63179491926536</v>
+        <v>560.46642906094564</v>
       </c>
     </row>
     <row r="107" spans="2:28">
@@ -19967,16 +19967,16 @@
         <v>720</v>
       </c>
       <c r="Y107" t="s">
-        <v>423</v>
+        <v>502</v>
       </c>
       <c r="Z107" t="s">
-        <v>820</v>
+        <v>786</v>
       </c>
       <c r="AA107">
-        <v>0.99777342334799435</v>
+        <v>0.95261480241426988</v>
       </c>
       <c r="AB107">
-        <v>40.820571953437025</v>
+        <v>868.72862240505196</v>
       </c>
     </row>
     <row r="108" spans="2:28">
@@ -20041,16 +20041,16 @@
         <v>722</v>
       </c>
       <c r="Y108" t="s">
-        <v>459</v>
+        <v>501</v>
       </c>
       <c r="Z108" t="s">
-        <v>821</v>
+        <v>765</v>
       </c>
       <c r="AA108">
-        <v>0.99456845174856667</v>
+        <v>0.93980266520001188</v>
       </c>
       <c r="AB108">
-        <v>99.578384609610097</v>
+        <v>1103.617804666449</v>
       </c>
     </row>
     <row r="109" spans="2:28">
@@ -20115,16 +20115,16 @@
         <v>724</v>
       </c>
       <c r="Y109" t="s">
-        <v>465</v>
+        <v>504</v>
       </c>
       <c r="Z109" t="s">
-        <v>822</v>
+        <v>786</v>
       </c>
       <c r="AA109">
-        <v>0.99302343871187126</v>
+        <v>0.96520767961718001</v>
       </c>
       <c r="AB109">
-        <v>127.90362361569299</v>
+        <v>637.85920701836687</v>
       </c>
     </row>
     <row r="110" spans="2:28">
@@ -20189,16 +20189,16 @@
         <v>726</v>
       </c>
       <c r="Y110" t="s">
-        <v>519</v>
+        <v>485</v>
       </c>
       <c r="Z110" t="s">
-        <v>768</v>
+        <v>779</v>
       </c>
       <c r="AA110">
-        <v>0.98823673546715696</v>
+        <v>0.9916427371040899</v>
       </c>
       <c r="AB110">
-        <v>215.65984976878829</v>
+        <v>153.21648642501913</v>
       </c>
     </row>
     <row r="111" spans="2:28">
@@ -20263,16 +20263,16 @@
         <v>728</v>
       </c>
       <c r="Y111" t="s">
-        <v>503</v>
+        <v>434</v>
       </c>
       <c r="Z111" t="s">
-        <v>760</v>
+        <v>812</v>
       </c>
       <c r="AA111">
-        <v>0.96316770855847034</v>
+        <v>0.99506721859763492</v>
       </c>
       <c r="AB111">
-        <v>675.25867642804383</v>
+        <v>90.434325710025817</v>
       </c>
     </row>
     <row r="112" spans="2:28">
@@ -20337,16 +20337,16 @@
         <v>730</v>
       </c>
       <c r="Y112" t="s">
-        <v>507</v>
+        <v>472</v>
       </c>
       <c r="Z112" t="s">
-        <v>760</v>
+        <v>825</v>
       </c>
       <c r="AA112">
-        <v>0.97244982574001193</v>
+        <v>0.99504955481764434</v>
       </c>
       <c r="AB112">
-        <v>505.08652809978111</v>
+        <v>90.758161676519606</v>
       </c>
     </row>
     <row r="113" spans="2:28">
@@ -20411,16 +20411,16 @@
         <v>732</v>
       </c>
       <c r="Y113" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="Z113" t="s">
-        <v>769</v>
+        <v>826</v>
       </c>
       <c r="AA113">
-        <v>0.97762911532019692</v>
+        <v>0.99267056664092235</v>
       </c>
       <c r="AB113">
-        <v>410.13288579638987</v>
+        <v>134.37294491642297</v>
       </c>
     </row>
     <row r="114" spans="2:28">
@@ -20485,16 +20485,16 @@
         <v>734</v>
       </c>
       <c r="Y114" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z114" t="s">
-        <v>823</v>
+        <v>764</v>
       </c>
       <c r="AA114">
-        <v>0.98810065757436949</v>
+        <v>0.99506650442525857</v>
       </c>
       <c r="AB114">
-        <v>218.15461113655846</v>
+        <v>90.447418870259696</v>
       </c>
     </row>
     <row r="115" spans="2:28">
@@ -20559,16 +20559,16 @@
         <v>736</v>
       </c>
       <c r="Y115" t="s">
-        <v>413</v>
+        <v>512</v>
       </c>
       <c r="Z115" t="s">
-        <v>824</v>
+        <v>764</v>
       </c>
       <c r="AA115">
-        <v>0.98762529884261907</v>
+        <v>0.99751736863660534</v>
       </c>
       <c r="AB115">
-        <v>226.8695212186509</v>
+        <v>45.514908328903012</v>
       </c>
     </row>
     <row r="116" spans="2:28">
@@ -20633,16 +20633,16 @@
         <v>738</v>
       </c>
       <c r="Y116" t="s">
-        <v>483</v>
+        <v>505</v>
       </c>
       <c r="Z116" t="s">
-        <v>793</v>
+        <v>765</v>
       </c>
       <c r="AA116">
-        <v>0.97765910024833902</v>
+        <v>0.95679886695043703</v>
       </c>
       <c r="AB116">
-        <v>409.58316211378531</v>
+        <v>792.02077257532187</v>
       </c>
     </row>
     <row r="117" spans="2:28">
@@ -20707,16 +20707,16 @@
         <v>740</v>
       </c>
       <c r="Y117" t="s">
-        <v>419</v>
+        <v>508</v>
       </c>
       <c r="Z117" t="s">
-        <v>780</v>
+        <v>766</v>
       </c>
       <c r="AA117">
-        <v>0.99660741093787208</v>
+        <v>0.98820023878766372</v>
       </c>
       <c r="AB117">
-        <v>62.197466139011929</v>
+        <v>216.32895555949756</v>
       </c>
     </row>
     <row r="118" spans="2:28">
@@ -20781,16 +20781,16 @@
         <v>742</v>
       </c>
       <c r="Y118" t="s">
-        <v>436</v>
+        <v>506</v>
       </c>
       <c r="Z118" t="s">
-        <v>825</v>
+        <v>765</v>
       </c>
       <c r="AA118">
-        <v>0.99755601192869059</v>
+        <v>0.97404342257401955</v>
       </c>
       <c r="AB118">
-        <v>44.806447974006502</v>
+        <v>475.8705861429753</v>
       </c>
     </row>
     <row r="119" spans="2:28">
@@ -20855,16 +20855,16 @@
         <v>744</v>
       </c>
       <c r="Y119" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="Z119" t="s">
-        <v>826</v>
+        <v>779</v>
       </c>
       <c r="AA119">
-        <v>0.9938212728279423</v>
+        <v>0.98784519281324712</v>
       </c>
       <c r="AB119">
-        <v>113.27666482105715</v>
+        <v>222.83813175713675</v>
       </c>
     </row>
     <row r="120" spans="2:28">
@@ -20929,16 +20929,16 @@
         <v>746</v>
       </c>
       <c r="Y120" t="s">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="Z120" t="s">
-        <v>782</v>
+        <v>827</v>
       </c>
       <c r="AA120">
-        <v>0.99529213309817555</v>
+        <v>0.99679666622099095</v>
       </c>
       <c r="AB120">
-        <v>86.310893200114194</v>
+        <v>58.72778594849845</v>
       </c>
     </row>
     <row r="121" spans="2:28">
@@ -21003,16 +21003,16 @@
         <v>748</v>
       </c>
       <c r="Y121" t="s">
-        <v>469</v>
+        <v>493</v>
       </c>
       <c r="Z121" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
       <c r="AA121">
-        <v>0.99156696838886027</v>
+        <v>0.98775140142897844</v>
       </c>
       <c r="AB121">
-        <v>154.60557953756208</v>
+        <v>224.55764046872929</v>
       </c>
     </row>
     <row r="122" spans="2:28">
@@ -21077,16 +21077,16 @@
         <v>750</v>
       </c>
       <c r="Y122" t="s">
-        <v>444</v>
+        <v>473</v>
       </c>
       <c r="Z122" t="s">
-        <v>827</v>
+        <v>792</v>
       </c>
       <c r="AA122">
-        <v>0.99401688555089329</v>
+        <v>0.99149332428826786</v>
       </c>
       <c r="AB122">
-        <v>109.69043156695554</v>
+        <v>155.95572138175513</v>
       </c>
     </row>
     <row r="123" spans="2:28">
@@ -21151,16 +21151,16 @@
         <v>752</v>
       </c>
       <c r="Y123" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="Z123" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AA123">
-        <v>0.99519181845511939</v>
+        <v>0.99563753295513335</v>
       </c>
       <c r="AB123">
-        <v>88.149994989478557</v>
+        <v>79.978562489222767</v>
       </c>
     </row>
     <row r="124" spans="2:28">
@@ -21225,16 +21225,16 @@
         <v>754</v>
       </c>
       <c r="Y124" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="Z124" t="s">
-        <v>829</v>
+        <v>780</v>
       </c>
       <c r="AA124">
-        <v>0.99559756506177444</v>
+        <v>0.99338737982948611</v>
       </c>
       <c r="AB124">
-        <v>80.711307200801741</v>
+        <v>121.23136979275419</v>
       </c>
     </row>
     <row r="125" spans="2:28">
@@ -21299,16 +21299,16 @@
         <v>756</v>
       </c>
       <c r="Y125" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="Z125" t="s">
         <v>830</v>
       </c>
       <c r="AA125">
-        <v>0.99703099037584386</v>
+        <v>0.99488652924851917</v>
       </c>
       <c r="AB125">
-        <v>54.431843109528238</v>
+        <v>93.746963777149261</v>
       </c>
     </row>
   </sheetData>
@@ -21317,7 +21317,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{164CC67A-1769-459E-BEDC-080DB62BC439}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1F413B-2EB2-46D2-B3B0-651887576710}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -21429,7 +21429,7 @@
         <v>1157</v>
       </c>
       <c r="K11" t="s">
-        <v>990</v>
+        <v>1054</v>
       </c>
       <c r="L11">
         <v>10.563746678268352</v>
@@ -21462,7 +21462,7 @@
         <v>1295</v>
       </c>
       <c r="X11" t="s">
-        <v>1131</v>
+        <v>1155</v>
       </c>
       <c r="Y11">
         <v>54.979500000000002</v>
@@ -21497,7 +21497,7 @@
         <v>1159</v>
       </c>
       <c r="K12" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="L12">
         <v>7.4816578037471135</v>
@@ -21530,7 +21530,7 @@
         <v>1297</v>
       </c>
       <c r="X12" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="Y12">
         <v>0.74099999999999999</v>
@@ -21565,7 +21565,7 @@
         <v>1161</v>
       </c>
       <c r="K13" t="s">
-        <v>989</v>
+        <v>1053</v>
       </c>
       <c r="L13">
         <v>4.7713910333636482</v>
@@ -21598,7 +21598,7 @@
         <v>1299</v>
       </c>
       <c r="X13" t="s">
-        <v>1152</v>
+        <v>1137</v>
       </c>
       <c r="Y13">
         <v>36.586500000000001</v>
@@ -21633,7 +21633,7 @@
         <v>1163</v>
       </c>
       <c r="K14" t="s">
-        <v>1003</v>
+        <v>1031</v>
       </c>
       <c r="L14">
         <v>12.404103898825962</v>
@@ -21666,7 +21666,7 @@
         <v>1301</v>
       </c>
       <c r="X14" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="Y14">
         <v>53.094000000000001</v>
@@ -21701,7 +21701,7 @@
         <v>1165</v>
       </c>
       <c r="K15" t="s">
-        <v>1029</v>
+        <v>977</v>
       </c>
       <c r="L15">
         <v>6.1276234637439133</v>
@@ -21734,7 +21734,7 @@
         <v>1303</v>
       </c>
       <c r="X15" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="Y15">
         <v>55.56</v>
@@ -21769,7 +21769,7 @@
         <v>1167</v>
       </c>
       <c r="K16" t="s">
-        <v>998</v>
+        <v>1045</v>
       </c>
       <c r="L16">
         <v>2.2195844391122765</v>
@@ -21802,7 +21802,7 @@
         <v>1305</v>
       </c>
       <c r="X16" t="s">
-        <v>1122</v>
+        <v>1156</v>
       </c>
       <c r="Y16">
         <v>43.858499999999999</v>
@@ -21837,7 +21837,7 @@
         <v>1169</v>
       </c>
       <c r="K17" t="s">
-        <v>1045</v>
+        <v>1006</v>
       </c>
       <c r="L17">
         <v>3.7614311754340659</v>
@@ -21870,7 +21870,7 @@
         <v>1307</v>
       </c>
       <c r="X17" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="Y17">
         <v>42.080249999999999</v>
@@ -21905,7 +21905,7 @@
         <v>1171</v>
       </c>
       <c r="K18" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
       <c r="L18">
         <v>2.5051779960501728</v>
@@ -21938,7 +21938,7 @@
         <v>1309</v>
       </c>
       <c r="X18" t="s">
-        <v>1156</v>
+        <v>1122</v>
       </c>
       <c r="Y18">
         <v>19.922999999999998</v>
@@ -21973,7 +21973,7 @@
         <v>1173</v>
       </c>
       <c r="K19" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="L19">
         <v>1.8110172385939969</v>
@@ -22041,7 +22041,7 @@
         <v>1175</v>
       </c>
       <c r="K20" t="s">
-        <v>1044</v>
+        <v>1004</v>
       </c>
       <c r="L20">
         <v>11.884376191048085</v>
@@ -22074,7 +22074,7 @@
         <v>1313</v>
       </c>
       <c r="X20" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="Y20">
         <v>40.677</v>
@@ -22109,7 +22109,7 @@
         <v>1177</v>
       </c>
       <c r="K21" t="s">
-        <v>978</v>
+        <v>1011</v>
       </c>
       <c r="L21">
         <v>12.246676572623375</v>
@@ -22142,7 +22142,7 @@
         <v>1315</v>
       </c>
       <c r="X21" t="s">
-        <v>1123</v>
+        <v>1145</v>
       </c>
       <c r="Y21">
         <v>60.146250000000002</v>
@@ -22177,7 +22177,7 @@
         <v>1179</v>
       </c>
       <c r="K22" t="s">
-        <v>1030</v>
+        <v>978</v>
       </c>
       <c r="L22">
         <v>10.179607104535382</v>
@@ -22210,7 +22210,7 @@
         <v>1317</v>
       </c>
       <c r="X22" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="Y22">
         <v>39.273000000000003</v>
@@ -22245,7 +22245,7 @@
         <v>1181</v>
       </c>
       <c r="K23" t="s">
-        <v>1058</v>
+        <v>1009</v>
       </c>
       <c r="L23">
         <v>7.6463375414566821</v>
@@ -22278,7 +22278,7 @@
         <v>1319</v>
       </c>
       <c r="X23" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="Y23">
         <v>44.889749999999999</v>
@@ -22313,7 +22313,7 @@
         <v>1183</v>
       </c>
       <c r="K24" t="s">
-        <v>1018</v>
+        <v>986</v>
       </c>
       <c r="L24">
         <v>48.571266974214375</v>
@@ -22346,7 +22346,7 @@
         <v>1321</v>
       </c>
       <c r="X24" t="s">
-        <v>1124</v>
+        <v>1146</v>
       </c>
       <c r="Y24">
         <v>27.66375</v>
@@ -22381,7 +22381,7 @@
         <v>1185</v>
       </c>
       <c r="K25" t="s">
-        <v>1039</v>
+        <v>1050</v>
       </c>
       <c r="L25">
         <v>1.6757541426674882</v>
@@ -22414,7 +22414,7 @@
         <v>1323</v>
       </c>
       <c r="X25" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="Y25">
         <v>21.581250000000001</v>
@@ -22449,7 +22449,7 @@
         <v>1187</v>
       </c>
       <c r="K26" t="s">
-        <v>1059</v>
+        <v>1010</v>
       </c>
       <c r="L26">
         <v>0.39959553615654331</v>
@@ -22517,7 +22517,7 @@
         <v>1189</v>
       </c>
       <c r="K27" t="s">
-        <v>985</v>
+        <v>998</v>
       </c>
       <c r="L27">
         <v>1.7832075556426605</v>
@@ -22550,7 +22550,7 @@
         <v>1327</v>
       </c>
       <c r="X27" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="Y27">
         <v>43.631999999999998</v>
@@ -22585,7 +22585,7 @@
         <v>1191</v>
       </c>
       <c r="K28" t="s">
-        <v>1053</v>
+        <v>1018</v>
       </c>
       <c r="L28">
         <v>0.35051099632091098</v>
@@ -22618,7 +22618,7 @@
         <v>1329</v>
       </c>
       <c r="X28" t="s">
-        <v>1141</v>
+        <v>1152</v>
       </c>
       <c r="Y28">
         <v>3.4402499999999998</v>
@@ -22653,7 +22653,7 @@
         <v>1193</v>
       </c>
       <c r="K29" t="s">
-        <v>1026</v>
+        <v>995</v>
       </c>
       <c r="L29">
         <v>5.5005105319204732</v>
@@ -22721,7 +22721,7 @@
         <v>1195</v>
       </c>
       <c r="K30" t="s">
-        <v>970</v>
+        <v>1024</v>
       </c>
       <c r="L30">
         <v>0.34625959029864795</v>
@@ -22789,7 +22789,7 @@
         <v>1197</v>
       </c>
       <c r="K31" t="s">
-        <v>1014</v>
+        <v>972</v>
       </c>
       <c r="L31">
         <v>0.65440271382024695</v>
@@ -22822,7 +22822,7 @@
         <v>1335</v>
       </c>
       <c r="X31" t="s">
-        <v>1153</v>
+        <v>1138</v>
       </c>
       <c r="Y31">
         <v>38.154000000000003</v>
@@ -22857,7 +22857,7 @@
         <v>1199</v>
       </c>
       <c r="K32" t="s">
-        <v>1046</v>
+        <v>1007</v>
       </c>
       <c r="L32">
         <v>0.5190595734350465</v>
@@ -22890,7 +22890,7 @@
         <v>1337</v>
       </c>
       <c r="X32" t="s">
-        <v>1125</v>
+        <v>1147</v>
       </c>
       <c r="Y32">
         <v>26.765999999999998</v>
@@ -22925,7 +22925,7 @@
         <v>1201</v>
       </c>
       <c r="K33" t="s">
-        <v>999</v>
+        <v>1046</v>
       </c>
       <c r="L33">
         <v>0.29505146981926272</v>
@@ -22958,7 +22958,7 @@
         <v>1339</v>
       </c>
       <c r="X33" t="s">
-        <v>1140</v>
+        <v>1151</v>
       </c>
       <c r="Y33">
         <v>35.325000000000003</v>
@@ -22993,7 +22993,7 @@
         <v>1203</v>
       </c>
       <c r="K34" t="s">
-        <v>996</v>
+        <v>1044</v>
       </c>
       <c r="L34">
         <v>0.28737649325389003</v>
@@ -23026,7 +23026,7 @@
         <v>1341</v>
       </c>
       <c r="X34" t="s">
-        <v>1142</v>
+        <v>1128</v>
       </c>
       <c r="Y34">
         <v>38.589750000000002</v>
@@ -23061,7 +23061,7 @@
         <v>1205</v>
       </c>
       <c r="K35" t="s">
-        <v>1011</v>
+        <v>969</v>
       </c>
       <c r="L35">
         <v>0.85621181691755843</v>
@@ -23094,7 +23094,7 @@
         <v>1343</v>
       </c>
       <c r="X35" t="s">
-        <v>1143</v>
+        <v>1129</v>
       </c>
       <c r="Y35">
         <v>28.707000000000001</v>
@@ -23129,7 +23129,7 @@
         <v>1207</v>
       </c>
       <c r="K36" t="s">
-        <v>1019</v>
+        <v>987</v>
       </c>
       <c r="L36">
         <v>2.2628760328229185</v>
@@ -23162,7 +23162,7 @@
         <v>1345</v>
       </c>
       <c r="X36" t="s">
-        <v>1145</v>
+        <v>1131</v>
       </c>
       <c r="Y36">
         <v>2.6655000000000002</v>
@@ -23197,7 +23197,7 @@
         <v>1209</v>
       </c>
       <c r="K37" t="s">
-        <v>1005</v>
+        <v>1033</v>
       </c>
       <c r="L37">
         <v>0.43370118574988076</v>
@@ -23230,7 +23230,7 @@
         <v>1347</v>
       </c>
       <c r="X37" t="s">
-        <v>1155</v>
+        <v>1141</v>
       </c>
       <c r="Y37">
         <v>11.651999999999999</v>
@@ -23265,7 +23265,7 @@
         <v>1211</v>
       </c>
       <c r="K38" t="s">
-        <v>1004</v>
+        <v>1032</v>
       </c>
       <c r="L38">
         <v>2.5150267058852811</v>
@@ -23298,7 +23298,7 @@
         <v>1349</v>
       </c>
       <c r="X38" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="Y38">
         <v>10.619249999999999</v>
@@ -23333,7 +23333,7 @@
         <v>1213</v>
       </c>
       <c r="K39" t="s">
-        <v>1021</v>
+        <v>989</v>
       </c>
       <c r="L39">
         <v>2.2677057834637031</v>
@@ -23366,7 +23366,7 @@
         <v>1351</v>
       </c>
       <c r="X39" t="s">
-        <v>1146</v>
+        <v>1136</v>
       </c>
       <c r="Y39">
         <v>21.260999999999999</v>
@@ -23401,7 +23401,7 @@
         <v>1215</v>
       </c>
       <c r="K40" t="s">
-        <v>1031</v>
+        <v>979</v>
       </c>
       <c r="L40">
         <v>3.9696443596880591</v>
@@ -23434,7 +23434,7 @@
         <v>1353</v>
       </c>
       <c r="X40" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="Y40">
         <v>1.7955000000000001</v>
@@ -23469,7 +23469,7 @@
         <v>1217</v>
       </c>
       <c r="K41" t="s">
-        <v>1013</v>
+        <v>971</v>
       </c>
       <c r="L41">
         <v>2.4836923620575391</v>
@@ -23502,7 +23502,7 @@
         <v>1355</v>
       </c>
       <c r="X41" t="s">
-        <v>1154</v>
+        <v>1139</v>
       </c>
       <c r="Y41">
         <v>26.880749999999999</v>
@@ -23537,7 +23537,7 @@
         <v>1219</v>
       </c>
       <c r="K42" t="s">
-        <v>969</v>
+        <v>1023</v>
       </c>
       <c r="L42">
         <v>2.885493974180005</v>
@@ -23572,7 +23572,7 @@
         <v>1221</v>
       </c>
       <c r="K43" t="s">
-        <v>1038</v>
+        <v>1049</v>
       </c>
       <c r="L43">
         <v>4.0763322608214585</v>
@@ -23607,7 +23607,7 @@
         <v>1223</v>
       </c>
       <c r="K44" t="s">
-        <v>994</v>
+        <v>1058</v>
       </c>
       <c r="L44">
         <v>18.379523073310825</v>
@@ -23642,7 +23642,7 @@
         <v>1225</v>
       </c>
       <c r="K45" t="s">
-        <v>1010</v>
+        <v>1039</v>
       </c>
       <c r="L45">
         <v>1.4999429400795936</v>
@@ -23677,7 +23677,7 @@
         <v>1227</v>
       </c>
       <c r="K46" t="s">
-        <v>1027</v>
+        <v>996</v>
       </c>
       <c r="L46">
         <v>51.336595002990194</v>
@@ -23712,7 +23712,7 @@
         <v>1229</v>
       </c>
       <c r="K47" t="s">
-        <v>1034</v>
+        <v>982</v>
       </c>
       <c r="L47">
         <v>16.978804920122926</v>
@@ -23747,7 +23747,7 @@
         <v>1231</v>
       </c>
       <c r="K48" t="s">
-        <v>988</v>
+        <v>1001</v>
       </c>
       <c r="L48">
         <v>12.678684297219551</v>
@@ -23782,7 +23782,7 @@
         <v>1233</v>
       </c>
       <c r="K49" t="s">
-        <v>1002</v>
+        <v>1048</v>
       </c>
       <c r="L49">
         <v>3.0756142181007986</v>
@@ -23817,7 +23817,7 @@
         <v>1235</v>
       </c>
       <c r="K50" t="s">
-        <v>976</v>
+        <v>1029</v>
       </c>
       <c r="L50">
         <v>17.749707845203876</v>
@@ -23852,7 +23852,7 @@
         <v>1237</v>
       </c>
       <c r="K51" t="s">
-        <v>980</v>
+        <v>1012</v>
       </c>
       <c r="L51">
         <v>2.3372365278937242</v>
@@ -23887,7 +23887,7 @@
         <v>1239</v>
       </c>
       <c r="K52" t="s">
-        <v>992</v>
+        <v>1056</v>
       </c>
       <c r="L52">
         <v>4.2648673086521249</v>
@@ -23922,7 +23922,7 @@
         <v>1241</v>
       </c>
       <c r="K53" t="s">
-        <v>1043</v>
+        <v>1003</v>
       </c>
       <c r="L53">
         <v>2.462861606818517</v>
@@ -23957,7 +23957,7 @@
         <v>1243</v>
       </c>
       <c r="K54" t="s">
-        <v>1057</v>
+        <v>1022</v>
       </c>
       <c r="L54">
         <v>9.435033539909309</v>
@@ -23992,7 +23992,7 @@
         <v>1245</v>
       </c>
       <c r="K55" t="s">
-        <v>974</v>
+        <v>1027</v>
       </c>
       <c r="L55">
         <v>26.420384248371558</v>
@@ -24027,7 +24027,7 @@
         <v>1247</v>
       </c>
       <c r="K56" t="s">
-        <v>1017</v>
+        <v>976</v>
       </c>
       <c r="L56">
         <v>18.510958868579117</v>
@@ -24062,7 +24062,7 @@
         <v>1249</v>
       </c>
       <c r="K57" t="s">
-        <v>1035</v>
+        <v>983</v>
       </c>
       <c r="L57">
         <v>15.228130347836801</v>
@@ -24097,7 +24097,7 @@
         <v>1251</v>
       </c>
       <c r="K58" t="s">
-        <v>1052</v>
+        <v>1017</v>
       </c>
       <c r="L58">
         <v>14.176079891703212</v>
@@ -24132,7 +24132,7 @@
         <v>1253</v>
       </c>
       <c r="K59" t="s">
-        <v>1056</v>
+        <v>1021</v>
       </c>
       <c r="L59">
         <v>0.80973624203950822</v>
@@ -24167,7 +24167,7 @@
         <v>1255</v>
       </c>
       <c r="K60" t="s">
-        <v>984</v>
+        <v>1016</v>
       </c>
       <c r="L60">
         <v>3.2067222321080848</v>
@@ -24202,7 +24202,7 @@
         <v>1257</v>
       </c>
       <c r="K61" t="s">
-        <v>1037</v>
+        <v>985</v>
       </c>
       <c r="L61">
         <v>0.66271354737797783</v>
@@ -24237,7 +24237,7 @@
         <v>1259</v>
       </c>
       <c r="K62" t="s">
-        <v>1055</v>
+        <v>1020</v>
       </c>
       <c r="L62">
         <v>1.8096926976599874</v>
@@ -24272,7 +24272,7 @@
         <v>1261</v>
       </c>
       <c r="K63" t="s">
-        <v>982</v>
+        <v>1014</v>
       </c>
       <c r="L63">
         <v>0.23974319237866104</v>
@@ -24307,7 +24307,7 @@
         <v>1263</v>
       </c>
       <c r="K64" t="s">
-        <v>983</v>
+        <v>1015</v>
       </c>
       <c r="L64">
         <v>8.2047875916663029E-2</v>
@@ -24342,7 +24342,7 @@
         <v>1265</v>
       </c>
       <c r="K65" t="s">
-        <v>993</v>
+        <v>1057</v>
       </c>
       <c r="L65">
         <v>11.861012832193515</v>
@@ -24377,7 +24377,7 @@
         <v>1267</v>
       </c>
       <c r="K66" t="s">
-        <v>1015</v>
+        <v>973</v>
       </c>
       <c r="L66">
         <v>0.74143826937354373</v>
@@ -24412,7 +24412,7 @@
         <v>1269</v>
       </c>
       <c r="K67" t="s">
-        <v>972</v>
+        <v>1026</v>
       </c>
       <c r="L67">
         <v>5.5201095579611916</v>
@@ -24447,7 +24447,7 @@
         <v>1271</v>
       </c>
       <c r="K68" t="s">
-        <v>1025</v>
+        <v>993</v>
       </c>
       <c r="L68">
         <v>6.8285247240880329</v>
@@ -24482,7 +24482,7 @@
         <v>1273</v>
       </c>
       <c r="K69" t="s">
-        <v>986</v>
+        <v>999</v>
       </c>
       <c r="L69">
         <v>14.065249575687433</v>
@@ -24517,7 +24517,7 @@
         <v>1275</v>
       </c>
       <c r="K70" t="s">
-        <v>1042</v>
+        <v>1002</v>
       </c>
       <c r="L70">
         <v>9.3799037679336319</v>
@@ -24552,7 +24552,7 @@
         <v>1277</v>
       </c>
       <c r="K71" t="s">
-        <v>1000</v>
+        <v>1047</v>
       </c>
       <c r="L71">
         <v>39.014264277919466</v>
@@ -24587,7 +24587,7 @@
         <v>1279</v>
       </c>
       <c r="K72" t="s">
-        <v>1008</v>
+        <v>1037</v>
       </c>
       <c r="L72">
         <v>7.8693705940085819</v>
@@ -24622,7 +24622,7 @@
         <v>1281</v>
       </c>
       <c r="K73" t="s">
-        <v>1006</v>
+        <v>1035</v>
       </c>
       <c r="L73">
         <v>19.787589902082505</v>
@@ -24657,7 +24657,7 @@
         <v>1283</v>
       </c>
       <c r="K74" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="L74">
         <v>18.319832830101969</v>
@@ -24692,7 +24692,7 @@
         <v>1285</v>
       </c>
       <c r="K75" t="s">
-        <v>1016</v>
+        <v>975</v>
       </c>
       <c r="L75">
         <v>6.6426756478058007</v>
@@ -24727,7 +24727,7 @@
         <v>1287</v>
       </c>
       <c r="K76" t="s">
-        <v>1033</v>
+        <v>981</v>
       </c>
       <c r="L76">
         <v>0.78969451031655336</v>
@@ -24762,7 +24762,7 @@
         <v>1289</v>
       </c>
       <c r="K77" t="s">
-        <v>1040</v>
+        <v>1051</v>
       </c>
       <c r="L77">
         <v>3.5275797249830152</v>
@@ -24797,7 +24797,7 @@
         <v>1291</v>
       </c>
       <c r="K78" t="s">
-        <v>1022</v>
+        <v>990</v>
       </c>
       <c r="L78">
         <v>0.89663971235601181</v>
@@ -24832,7 +24832,7 @@
         <v>1293</v>
       </c>
       <c r="K79" t="s">
-        <v>1023</v>
+        <v>991</v>
       </c>
       <c r="L79">
         <v>5.9305458091691294</v>
@@ -24847,7 +24847,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F270A5-73B1-474E-B9E4-9A8001C4CE84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE466A7-94F6-4780-A975-9A751402126F}">
   <dimension ref="B9:S120"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
